--- a/Mundial_2026_fuente_datos.xlsx
+++ b/Mundial_2026_fuente_datos.xlsx
@@ -986,8 +986,12 @@
           <t>CAF</t>
         </is>
       </c>
-      <c r="G4" s="10" t="n"/>
-      <c r="H4" s="12" t="n"/>
+      <c r="G4" s="10" t="n">
+        <v>61</v>
+      </c>
+      <c r="H4" s="12" t="n">
+        <v>1427.3</v>
+      </c>
       <c r="I4" s="10" t="inlineStr">
         <is>
           <t>No</t>
@@ -1170,8 +1174,12 @@
           <t>UEFA</t>
         </is>
       </c>
-      <c r="G8" s="10" t="n"/>
-      <c r="H8" s="12" t="n"/>
+      <c r="G8" s="10" t="n">
+        <v>71</v>
+      </c>
+      <c r="H8" s="12" t="n">
+        <v>1393.9</v>
+      </c>
       <c r="I8" s="10" t="inlineStr">
         <is>
           <t>No</t>
@@ -1404,7 +1412,9 @@
       <c r="G13" s="7" t="n">
         <v>84</v>
       </c>
-      <c r="H13" s="13" t="n"/>
+      <c r="H13" s="13" t="n">
+        <v>1350.5</v>
+      </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
           <t>No</t>
@@ -1731,7 +1741,9 @@
       <c r="G20" s="10" t="n">
         <v>82</v>
       </c>
-      <c r="H20" s="12" t="n"/>
+      <c r="H20" s="12" t="n">
+        <v>1357.1</v>
+      </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
           <t>No</t>
@@ -2196,8 +2208,12 @@
           <t>OFC</t>
         </is>
       </c>
-      <c r="G30" s="10" t="n"/>
-      <c r="H30" s="12" t="n"/>
+      <c r="G30" s="10" t="n">
+        <v>86</v>
+      </c>
+      <c r="H30" s="12" t="n">
+        <v>1343.8</v>
+      </c>
       <c r="I30" s="10" t="inlineStr">
         <is>
           <t>No</t>
@@ -2289,7 +2305,9 @@
       <c r="G32" s="10" t="n">
         <v>68</v>
       </c>
-      <c r="H32" s="12" t="n"/>
+      <c r="H32" s="12" t="n">
+        <v>1403.9</v>
+      </c>
       <c r="I32" s="10" t="inlineStr">
         <is>
           <t>No</t>
@@ -2331,8 +2349,12 @@
           <t>AFC</t>
         </is>
       </c>
-      <c r="G33" s="14" t="n"/>
-      <c r="H33" s="13" t="n"/>
+      <c r="G33" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="H33" s="13" t="n">
+        <v>1430.6</v>
+      </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
           <t>No</t>
@@ -2515,8 +2537,12 @@
           <t>AFC</t>
         </is>
       </c>
-      <c r="G37" s="14" t="n"/>
-      <c r="H37" s="13" t="n"/>
+      <c r="G37" s="14" t="n">
+        <v>58</v>
+      </c>
+      <c r="H37" s="13" t="n">
+        <v>1437.3</v>
+      </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
           <t>No</t>
@@ -2749,7 +2775,9 @@
       <c r="G42" s="10" t="n">
         <v>66</v>
       </c>
-      <c r="H42" s="12" t="n"/>
+      <c r="H42" s="12" t="n">
+        <v>1410.6</v>
+      </c>
       <c r="I42" s="10" t="inlineStr">
         <is>
           <t>No</t>
@@ -2885,8 +2913,12 @@
           <t>AFC</t>
         </is>
       </c>
-      <c r="G45" s="14" t="n"/>
-      <c r="H45" s="13" t="n"/>
+      <c r="G45" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="H45" s="13" t="n">
+        <v>1464</v>
+      </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
           <t>No</t>
@@ -3072,7 +3104,9 @@
       <c r="G49" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="H49" s="13" t="n"/>
+      <c r="H49" s="13" t="n">
+        <v>1390.5</v>
+      </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
           <t>No</t>
@@ -3134,6 +3168,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="51"/>
     <row r="52" ht="15" customHeight="1" s="32">
       <c r="B52" s="33" t="inlineStr">
         <is>
@@ -11451,7 +11486,6 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="51"/>
     <row r="52" ht="15" customHeight="1" s="32">
       <c r="B52" s="33" t="inlineStr">
         <is>

--- a/Mundial_2026_fuente_datos.xlsx
+++ b/Mundial_2026_fuente_datos.xlsx
@@ -15,6 +15,7 @@
     <sheet name="Fixture_Grupos" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Posiciones" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Eliminatorias" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Sedes" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
@@ -26,7 +27,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -97,6 +98,9 @@
       <name val="Arial"/>
       <color rgb="FF000000"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -170,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -269,6 +273,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -829,6 +834,369 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="36" t="inlineStr">
+        <is>
+          <t>Sedes del Mundial 2026 (referencia: ciudad, país, estadio, altitud aprox. en m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="36" t="inlineStr">
+        <is>
+          <t>Ciudad</t>
+        </is>
+      </c>
+      <c r="B2" s="36" t="inlineStr">
+        <is>
+          <t>País</t>
+        </is>
+      </c>
+      <c r="C2" s="36" t="inlineStr">
+        <is>
+          <t>Estadio</t>
+        </is>
+      </c>
+      <c r="D2" s="36" t="inlineStr">
+        <is>
+          <t>Altitud (m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ciudad de México</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Estadio Azteca</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Guadalajara</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Estadio Akron</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Monterrey</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Estadio BBVA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Toronto</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Canadá</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BMO Field</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Canadá</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BC Place</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Nueva York/Nueva Jersey</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Estados Unidos</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MetLife Stadium</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Estados Unidos</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AT&amp;T Stadium</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Los Ángeles</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Estados Unidos</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SoFi Stadium</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Kansas City</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Estados Unidos</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Arrowhead Stadium</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Bahía de San Francisco</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Estados Unidos</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Levi's Stadium</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Estados Unidos</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NRG Stadium</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Filadelfia</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Estados Unidos</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Lincoln Financial Field</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Estados Unidos</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz Stadium</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Estados Unidos</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Lumen Field</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Miami</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Estados Unidos</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Hard Rock Stadium</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Estados Unidos</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Gillette Stadium</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -3168,7 +3536,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51"/>
     <row r="52" ht="15" customHeight="1" s="32">
       <c r="B52" s="33" t="inlineStr">
         <is>
@@ -11509,7 +11876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="32" min="1" max="1"/>
@@ -11576,6 +11943,11 @@
       <c r="J2" s="6" t="inlineStr">
         <is>
           <t>Pts B</t>
+        </is>
+      </c>
+      <c r="K2" s="36" t="inlineStr">
+        <is>
+          <t>Sede</t>
         </is>
       </c>
     </row>
@@ -17025,7 +17397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="32" min="1" max="1"/>
@@ -17079,6 +17451,11 @@
           <t>Notas</t>
         </is>
       </c>
+      <c r="H2" s="36" t="inlineStr">
+        <is>
+          <t>Sede</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="32">
       <c r="A3" s="7" t="inlineStr">

--- a/Mundial_2026_fuente_datos.xlsx
+++ b/Mundial_2026_fuente_datos.xlsx
@@ -10625,7 +10625,9 @@
       <c r="G3" s="24" t="n">
         <v>191.85</v>
       </c>
-      <c r="H3" s="24" t="n"/>
+      <c r="H3" s="24" t="n">
+        <v>27.5</v>
+      </c>
       <c r="I3" s="24" t="n"/>
       <c r="J3" s="24" t="n">
         <v>2026</v>
@@ -10651,7 +10653,9 @@
       <c r="G4" s="24" t="n">
         <v>49.25</v>
       </c>
-      <c r="H4" s="24" t="n"/>
+      <c r="H4" s="24" t="n">
+        <v>26.35</v>
+      </c>
       <c r="I4" s="24" t="n"/>
       <c r="J4" s="24" t="n">
         <v>2026</v>
@@ -10677,7 +10681,9 @@
       <c r="G5" s="24" t="n">
         <v>139.05</v>
       </c>
-      <c r="H5" s="24" t="n"/>
+      <c r="H5" s="24" t="n">
+        <v>27.46</v>
+      </c>
       <c r="I5" s="24" t="n"/>
       <c r="J5" s="24" t="n">
         <v>2026</v>
@@ -10703,7 +10709,9 @@
       <c r="G6" s="24" t="n">
         <v>188.18</v>
       </c>
-      <c r="H6" s="24" t="n"/>
+      <c r="H6" s="24" t="n">
+        <v>27.23</v>
+      </c>
       <c r="I6" s="24" t="n"/>
       <c r="J6" s="24" t="n">
         <v>2026</v>
@@ -10729,7 +10737,9 @@
       <c r="G7" s="24" t="n">
         <v>198.65</v>
       </c>
-      <c r="H7" s="24" t="n"/>
+      <c r="H7" s="24" t="n">
+        <v>26.42</v>
+      </c>
       <c r="I7" s="24" t="n"/>
       <c r="J7" s="24" t="n">
         <v>2026</v>
@@ -10755,7 +10765,9 @@
       <c r="G8" s="24" t="n">
         <v>146.4</v>
       </c>
-      <c r="H8" s="24" t="n"/>
+      <c r="H8" s="24" t="n">
+        <v>25.92</v>
+      </c>
       <c r="I8" s="24" t="n"/>
       <c r="J8" s="24" t="n">
         <v>2026</v>
@@ -10781,7 +10793,9 @@
       <c r="G9" s="24" t="n">
         <v>19.93</v>
       </c>
-      <c r="H9" s="24" t="n"/>
+      <c r="H9" s="24" t="n">
+        <v>28.92</v>
+      </c>
       <c r="I9" s="24" t="n"/>
       <c r="J9" s="24" t="n">
         <v>2026</v>
@@ -10807,7 +10821,9 @@
       <c r="G10" s="24" t="n">
         <v>332.5</v>
       </c>
-      <c r="H10" s="24" t="n"/>
+      <c r="H10" s="24" t="n">
+        <v>27.81</v>
+      </c>
       <c r="I10" s="24" t="n"/>
       <c r="J10" s="24" t="n">
         <v>2026</v>
@@ -10833,7 +10849,9 @@
       <c r="G11" s="24" t="n">
         <v>928.2</v>
       </c>
-      <c r="H11" s="24" t="n"/>
+      <c r="H11" s="24" t="n">
+        <v>28.65</v>
+      </c>
       <c r="I11" s="24" t="n"/>
       <c r="J11" s="24" t="n">
         <v>2026</v>
@@ -10859,7 +10877,9 @@
       <c r="G12" s="24" t="n">
         <v>447.7</v>
       </c>
-      <c r="H12" s="24" t="n"/>
+      <c r="H12" s="24" t="n">
+        <v>25.92</v>
+      </c>
       <c r="I12" s="24" t="n"/>
       <c r="J12" s="24" t="n">
         <v>2026</v>
@@ -10885,7 +10905,9 @@
       <c r="G13" s="24" t="n">
         <v>55.9</v>
       </c>
-      <c r="H13" s="24" t="n"/>
+      <c r="H13" s="24" t="n">
+        <v>27.08</v>
+      </c>
       <c r="I13" s="24" t="n"/>
       <c r="J13" s="24" t="n">
         <v>2026</v>
@@ -10911,7 +10933,9 @@
       <c r="G14" s="24" t="n">
         <v>170.25</v>
       </c>
-      <c r="H14" s="24" t="n"/>
+      <c r="H14" s="24" t="n">
+        <v>28.73</v>
+      </c>
       <c r="I14" s="24" t="n"/>
       <c r="J14" s="24" t="n">
         <v>2026</v>
@@ -10937,7 +10961,9 @@
       <c r="G15" s="24" t="n">
         <v>385.6</v>
       </c>
-      <c r="H15" s="24" t="n"/>
+      <c r="H15" s="24" t="n">
+        <v>26.42</v>
+      </c>
       <c r="I15" s="24" t="n"/>
       <c r="J15" s="24" t="n">
         <v>2026</v>
@@ -10963,7 +10989,9 @@
       <c r="G16" s="24" t="n">
         <v>153.65</v>
       </c>
-      <c r="H16" s="24" t="n"/>
+      <c r="H16" s="24" t="n">
+        <v>28.54</v>
+      </c>
       <c r="I16" s="24" t="n"/>
       <c r="J16" s="24" t="n">
         <v>2026</v>
@@ -10989,7 +11017,9 @@
       <c r="G17" s="24" t="n">
         <v>77.45</v>
       </c>
-      <c r="H17" s="24" t="n"/>
+      <c r="H17" s="24" t="n">
+        <v>26.88</v>
+      </c>
       <c r="I17" s="24" t="n"/>
       <c r="J17" s="24" t="n">
         <v>2026</v>
@@ -11015,7 +11045,9 @@
       <c r="G18" s="24" t="n">
         <v>473.7</v>
       </c>
-      <c r="H18" s="24" t="n"/>
+      <c r="H18" s="24" t="n">
+        <v>27.23</v>
+      </c>
       <c r="I18" s="24" t="n"/>
       <c r="J18" s="24" t="n">
         <v>2026</v>
@@ -11041,7 +11073,9 @@
       <c r="G19" s="24" t="n">
         <v>947</v>
       </c>
-      <c r="H19" s="24" t="n"/>
+      <c r="H19" s="24" t="n">
+        <v>27.54</v>
+      </c>
       <c r="I19" s="24" t="n"/>
       <c r="J19" s="24" t="n">
         <v>2026</v>
@@ -11067,7 +11101,9 @@
       <c r="G20" s="24" t="n">
         <v>25.78</v>
       </c>
-      <c r="H20" s="24" t="n"/>
+      <c r="H20" s="24" t="n">
+        <v>27.54</v>
+      </c>
       <c r="I20" s="24" t="n"/>
       <c r="J20" s="24" t="n">
         <v>2026</v>
@@ -11093,7 +11129,9 @@
       <c r="G21" s="24" t="n">
         <v>522.1</v>
       </c>
-      <c r="H21" s="24" t="n"/>
+      <c r="H21" s="24" t="n">
+        <v>25.35</v>
+      </c>
       <c r="I21" s="24" t="n"/>
       <c r="J21" s="24" t="n">
         <v>2026</v>
@@ -11119,7 +11157,9 @@
       <c r="G22" s="24" t="n">
         <v>368.7</v>
       </c>
-      <c r="H22" s="24" t="n"/>
+      <c r="H22" s="24" t="n">
+        <v>25.58</v>
+      </c>
       <c r="I22" s="24" t="n"/>
       <c r="J22" s="24" t="n">
         <v>2026</v>
@@ -11145,7 +11185,9 @@
       <c r="G23" s="24" t="n">
         <v>754.2</v>
       </c>
-      <c r="H23" s="24" t="n"/>
+      <c r="H23" s="24" t="n">
+        <v>27.27</v>
+      </c>
       <c r="I23" s="24" t="n"/>
       <c r="J23" s="24" t="n">
         <v>2026</v>
@@ -11171,7 +11213,9 @@
       <c r="G24" s="24" t="n">
         <v>270.85</v>
       </c>
-      <c r="H24" s="24" t="n"/>
+      <c r="H24" s="24" t="n">
+        <v>27.19</v>
+      </c>
       <c r="I24" s="24" t="n"/>
       <c r="J24" s="24" t="n">
         <v>2026</v>
@@ -11197,7 +11241,9 @@
       <c r="G25" s="24" t="n">
         <v>406.08</v>
       </c>
-      <c r="H25" s="24" t="n"/>
+      <c r="H25" s="24" t="n">
+        <v>27</v>
+      </c>
       <c r="I25" s="24" t="n"/>
       <c r="J25" s="24" t="n">
         <v>2026</v>
@@ -11223,7 +11269,9 @@
       <c r="G26" s="24" t="n">
         <v>69.95</v>
       </c>
-      <c r="H26" s="24" t="n"/>
+      <c r="H26" s="24" t="n">
+        <v>26.15</v>
+      </c>
       <c r="I26" s="24" t="n"/>
       <c r="J26" s="24" t="n">
         <v>2026</v>
@@ -11249,7 +11297,9 @@
       <c r="G27" s="24" t="n">
         <v>547.5</v>
       </c>
-      <c r="H27" s="24" t="n"/>
+      <c r="H27" s="24" t="n">
+        <v>27.12</v>
+      </c>
       <c r="I27" s="24" t="n"/>
       <c r="J27" s="24" t="n">
         <v>2026</v>
@@ -11275,7 +11325,9 @@
       <c r="G28" s="24" t="n">
         <v>116.48</v>
       </c>
-      <c r="H28" s="24" t="n"/>
+      <c r="H28" s="24" t="n">
+        <v>28.69</v>
+      </c>
       <c r="I28" s="24" t="n"/>
       <c r="J28" s="24" t="n">
         <v>2026</v>
@@ -11301,7 +11353,9 @@
       <c r="G29" s="24" t="n">
         <v>32.05</v>
       </c>
-      <c r="H29" s="24" t="n"/>
+      <c r="H29" s="24" t="n">
+        <v>29.81</v>
+      </c>
       <c r="I29" s="24" t="n"/>
       <c r="J29" s="24" t="n">
         <v>2026</v>
@@ -11327,7 +11381,9 @@
       <c r="G30" s="24" t="n">
         <v>34.45</v>
       </c>
-      <c r="H30" s="24" t="n"/>
+      <c r="H30" s="24" t="n">
+        <v>27.62</v>
+      </c>
       <c r="I30" s="24" t="n"/>
       <c r="J30" s="24" t="n">
         <v>2026</v>
@@ -11353,7 +11409,9 @@
       <c r="G31" s="24" t="n">
         <v>1220</v>
       </c>
-      <c r="H31" s="24" t="n"/>
+      <c r="H31" s="24" t="n">
+        <v>26.19</v>
+      </c>
       <c r="I31" s="24" t="n"/>
       <c r="J31" s="24" t="n">
         <v>2026</v>
@@ -11379,7 +11437,9 @@
       <c r="G32" s="24" t="n">
         <v>49.25</v>
       </c>
-      <c r="H32" s="24" t="n"/>
+      <c r="H32" s="24" t="n">
+        <v>29.23</v>
+      </c>
       <c r="I32" s="24" t="n"/>
       <c r="J32" s="24" t="n">
         <v>2026</v>
@@ -11405,7 +11465,9 @@
       <c r="G33" s="24" t="n">
         <v>40.68</v>
       </c>
-      <c r="H33" s="24" t="n"/>
+      <c r="H33" s="24" t="n">
+        <v>27.96</v>
+      </c>
       <c r="I33" s="24" t="n"/>
       <c r="J33" s="24" t="n">
         <v>2026</v>
@@ -11431,7 +11493,9 @@
       <c r="G34" s="24" t="n">
         <v>359.3</v>
       </c>
-      <c r="H34" s="24" t="n"/>
+      <c r="H34" s="24" t="n">
+        <v>28.19</v>
+      </c>
       <c r="I34" s="24" t="n"/>
       <c r="J34" s="24" t="n">
         <v>2026</v>
@@ -11457,7 +11521,9 @@
       <c r="G35" s="24" t="n">
         <v>1520</v>
       </c>
-      <c r="H35" s="24" t="n"/>
+      <c r="H35" s="24" t="n">
+        <v>26.58</v>
+      </c>
       <c r="I35" s="24" t="n"/>
       <c r="J35" s="24" t="n">
         <v>2026</v>
@@ -11483,7 +11549,9 @@
       <c r="G36" s="24" t="n">
         <v>478.1</v>
       </c>
-      <c r="H36" s="24" t="n"/>
+      <c r="H36" s="24" t="n">
+        <v>26.62</v>
+      </c>
       <c r="I36" s="24" t="n"/>
       <c r="J36" s="24" t="n">
         <v>2026</v>
@@ -11509,7 +11577,9 @@
       <c r="G37" s="24" t="n">
         <v>21.2</v>
       </c>
-      <c r="H37" s="24" t="n"/>
+      <c r="H37" s="24" t="n">
+        <v>26.65</v>
+      </c>
       <c r="I37" s="24" t="n"/>
       <c r="J37" s="24" t="n">
         <v>2026</v>
@@ -11535,7 +11605,9 @@
       <c r="G38" s="24" t="n">
         <v>589.9</v>
       </c>
-      <c r="H38" s="24" t="n"/>
+      <c r="H38" s="24" t="n">
+        <v>26.35</v>
+      </c>
       <c r="I38" s="24" t="n"/>
       <c r="J38" s="24" t="n">
         <v>2026</v>
@@ -11561,7 +11633,9 @@
       <c r="G39" s="24" t="n">
         <v>807.5</v>
       </c>
-      <c r="H39" s="24" t="n"/>
+      <c r="H39" s="24" t="n">
+        <v>28.62</v>
+      </c>
       <c r="I39" s="24" t="n"/>
       <c r="J39" s="24" t="n">
         <v>2026</v>
@@ -11587,7 +11661,9 @@
       <c r="G40" s="24" t="n">
         <v>256.9</v>
       </c>
-      <c r="H40" s="24" t="n"/>
+      <c r="H40" s="24" t="n">
+        <v>26.46</v>
+      </c>
       <c r="I40" s="24" t="n"/>
       <c r="J40" s="24" t="n">
         <v>2026</v>
@@ -11613,7 +11689,9 @@
       <c r="G41" s="24" t="n">
         <v>245.2</v>
       </c>
-      <c r="H41" s="24" t="n"/>
+      <c r="H41" s="24" t="n">
+        <v>28.12</v>
+      </c>
       <c r="I41" s="24" t="n"/>
       <c r="J41" s="24" t="n">
         <v>2026</v>
@@ -11639,7 +11717,9 @@
       <c r="G42" s="24" t="n">
         <v>20.3</v>
       </c>
-      <c r="H42" s="24" t="n"/>
+      <c r="H42" s="24" t="n">
+        <v>28.08</v>
+      </c>
       <c r="I42" s="24" t="n"/>
       <c r="J42" s="24" t="n">
         <v>2026</v>
@@ -11665,7 +11745,9 @@
       <c r="G43" s="24" t="n">
         <v>1010</v>
       </c>
-      <c r="H43" s="24" t="n"/>
+      <c r="H43" s="24" t="n">
+        <v>27.54</v>
+      </c>
       <c r="I43" s="24" t="n"/>
       <c r="J43" s="24" t="n">
         <v>2026</v>
@@ -11691,7 +11773,9 @@
       <c r="G44" s="24" t="n">
         <v>143.9</v>
       </c>
-      <c r="H44" s="24" t="n"/>
+      <c r="H44" s="24" t="n">
+        <v>28.5</v>
+      </c>
       <c r="I44" s="24" t="n"/>
       <c r="J44" s="24" t="n">
         <v>2026</v>
@@ -11717,7 +11801,9 @@
       <c r="G45" s="24" t="n">
         <v>85.33</v>
       </c>
-      <c r="H45" s="24" t="n"/>
+      <c r="H45" s="24" t="n">
+        <v>27.96</v>
+      </c>
       <c r="I45" s="24" t="n"/>
       <c r="J45" s="24" t="n">
         <v>2026</v>
@@ -11743,7 +11829,9 @@
       <c r="G46" s="24" t="n">
         <v>302.35</v>
       </c>
-      <c r="H46" s="24" t="n"/>
+      <c r="H46" s="24" t="n">
+        <v>29.58</v>
+      </c>
       <c r="I46" s="24" t="n"/>
       <c r="J46" s="24" t="n">
         <v>2026</v>
@@ -11769,7 +11857,9 @@
       <c r="G47" s="24" t="n">
         <v>1360</v>
       </c>
-      <c r="H47" s="24" t="n"/>
+      <c r="H47" s="24" t="n">
+        <v>26.62</v>
+      </c>
       <c r="I47" s="24" t="n"/>
       <c r="J47" s="24" t="n">
         <v>2026</v>
@@ -11795,7 +11885,9 @@
       <c r="G48" s="24" t="n">
         <v>387.3</v>
       </c>
-      <c r="H48" s="24" t="n"/>
+      <c r="H48" s="24" t="n">
+        <v>27.88</v>
+      </c>
       <c r="I48" s="24" t="n"/>
       <c r="J48" s="24" t="n">
         <v>2026</v>
@@ -11821,7 +11913,9 @@
       <c r="G49" s="24" t="n">
         <v>234.5</v>
       </c>
-      <c r="H49" s="24" t="n"/>
+      <c r="H49" s="24" t="n">
+        <v>26.42</v>
+      </c>
       <c r="I49" s="24" t="n"/>
       <c r="J49" s="24" t="n">
         <v>2026</v>
@@ -11847,7 +11941,9 @@
       <c r="G50" s="24" t="n">
         <v>34.55</v>
       </c>
-      <c r="H50" s="24" t="n"/>
+      <c r="H50" s="24" t="n">
+        <v>30</v>
+      </c>
       <c r="I50" s="24" t="n"/>
       <c r="J50" s="24" t="n">
         <v>2026</v>
@@ -17397,7 +17493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="32" min="1" max="1"/>
@@ -17456,6 +17552,16 @@
           <t>Sede</t>
         </is>
       </c>
+      <c r="I2" s="36" t="inlineStr">
+        <is>
+          <t>Slot 1</t>
+        </is>
+      </c>
+      <c r="J2" s="36" t="inlineStr">
+        <is>
+          <t>Slot 2</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="32">
       <c r="A3" s="7" t="inlineStr">
@@ -17468,19 +17574,29 @@
       </c>
       <c r="C3" s="28" t="inlineStr">
         <is>
-          <t>2º A</t>
+          <t>Sudáfrica</t>
         </is>
       </c>
       <c r="D3" s="24" t="n"/>
       <c r="E3" s="24" t="n"/>
       <c r="F3" s="28" t="inlineStr">
         <is>
+          <t>Canadá</t>
+        </is>
+      </c>
+      <c r="G3" s="28" t="inlineStr">
+        <is>
+          <t>Cruce definido por posición de grupo (FIFA). Completar equipos al cerrar la fase de grupos.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2º A</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>2º B</t>
-        </is>
-      </c>
-      <c r="G3" s="28" t="inlineStr">
-        <is>
-          <t>Cruce definido por posición de grupo (FIFA). Completar equipos al cerrar la fase de grupos.</t>
         </is>
       </c>
     </row>
@@ -17495,19 +17611,29 @@
       </c>
       <c r="C4" s="28" t="inlineStr">
         <is>
-          <t>1º C</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D4" s="24" t="n"/>
       <c r="E4" s="24" t="n"/>
       <c r="F4" s="28" t="inlineStr">
         <is>
+          <t>Japón</t>
+        </is>
+      </c>
+      <c r="G4" s="28" t="inlineStr">
+        <is>
+          <t>Cruce definido por posición de grupo (FIFA). Completar equipos al cerrar la fase de grupos.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1º C</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>2º F</t>
-        </is>
-      </c>
-      <c r="G4" s="28" t="inlineStr">
-        <is>
-          <t>Cruce definido por posición de grupo (FIFA). Completar equipos al cerrar la fase de grupos.</t>
         </is>
       </c>
     </row>
@@ -17522,19 +17648,29 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>1º E</t>
+          <t>Alemania</t>
         </is>
       </c>
       <c r="D5" s="24" t="n"/>
       <c r="E5" s="24" t="n"/>
       <c r="F5" s="28" t="inlineStr">
         <is>
+          <t>Suecia</t>
+        </is>
+      </c>
+      <c r="G5" s="28" t="inlineStr">
+        <is>
+          <t>Cruce definido por posición de grupo (FIFA). Completar equipos al cerrar la fase de grupos.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1º E</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>3º A/B/C/D/F</t>
-        </is>
-      </c>
-      <c r="G5" s="28" t="inlineStr">
-        <is>
-          <t>Cruce definido por posición de grupo (FIFA). Completar equipos al cerrar la fase de grupos.</t>
         </is>
       </c>
     </row>
@@ -17549,19 +17685,29 @@
       </c>
       <c r="C6" s="28" t="inlineStr">
         <is>
-          <t>1º F</t>
+          <t>Países Bajos</t>
         </is>
       </c>
       <c r="D6" s="24" t="n"/>
       <c r="E6" s="24" t="n"/>
       <c r="F6" s="28" t="inlineStr">
         <is>
+          <t>Marruecos</t>
+        </is>
+      </c>
+      <c r="G6" s="28" t="inlineStr">
+        <is>
+          <t>Cruce definido por posición de grupo (FIFA). Completar equipos al cerrar la fase de grupos.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1º F</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>2º C</t>
-        </is>
-      </c>
-      <c r="G6" s="28" t="inlineStr">
-        <is>
-          <t>Cruce definido por posición de grupo (FIFA). Completar equipos al cerrar la fase de grupos.</t>
         </is>
       </c>
     </row>
@@ -17576,19 +17722,29 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>2º E</t>
+          <t>Costa de Marfil</t>
         </is>
       </c>
       <c r="D7" s="24" t="n"/>
       <c r="E7" s="24" t="n"/>
       <c r="F7" s="28" t="inlineStr">
         <is>
+          <t>Noruega</t>
+        </is>
+      </c>
+      <c r="G7" s="28" t="inlineStr">
+        <is>
+          <t>Cruce definido por posición de grupo (FIFA). Completar equipos al cerrar la fase de grupos.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2º E</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>2º I</t>
-        </is>
-      </c>
-      <c r="G7" s="28" t="inlineStr">
-        <is>
-          <t>Cruce definido por posición de grupo (FIFA). Completar equipos al cerrar la fase de grupos.</t>
         </is>
       </c>
     </row>
@@ -17603,19 +17759,29 @@
       </c>
       <c r="C8" s="28" t="inlineStr">
         <is>
-          <t>1º I</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="D8" s="24" t="n"/>
       <c r="E8" s="24" t="n"/>
       <c r="F8" s="28" t="inlineStr">
         <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="G8" s="28" t="inlineStr">
+        <is>
+          <t>Cruce definido por posición de grupo (FIFA). Completar equipos al cerrar la fase de grupos.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1º I</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>3º C/D/F/G/H</t>
-        </is>
-      </c>
-      <c r="G8" s="28" t="inlineStr">
-        <is>
-          <t>Cruce definido por posición de grupo (FIFA). Completar equipos al cerrar la fase de grupos.</t>
         </is>
       </c>
     </row>
@@ -17630,19 +17796,29 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>1º A</t>
+          <t>México</t>
         </is>
       </c>
       <c r="D9" s="24" t="n"/>
       <c r="E9" s="24" t="n"/>
       <c r="F9" s="28" t="inlineStr">
         <is>
+          <t>Cabo Verde</t>
+        </is>
+      </c>
+      <c r="G9" s="28" t="inlineStr">
+        <is>
+          <t>Cruce definido por posición de grupo (FIFA). Completar equipos al cerrar la fase de grupos.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1º A</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>3º C/E/F/H/I</t>
-        </is>
-      </c>
-      <c r="G9" s="28" t="inlineStr">
-        <is>
-          <t>Cruce definido por posición de grupo (FIFA). Completar equipos al cerrar la fase de grupos.</t>
         </is>
       </c>
     </row>
@@ -17657,19 +17833,29 @@
       </c>
       <c r="C10" s="28" t="inlineStr">
         <is>
-          <t>1º L</t>
+          <t>Inglaterra</t>
         </is>
       </c>
       <c r="D10" s="24" t="n"/>
       <c r="E10" s="24" t="n"/>
       <c r="F10" s="28" t="inlineStr">
         <is>
+          <t>Argelia</t>
+        </is>
+      </c>
+      <c r="G10" s="28" t="inlineStr">
+        <is>
+          <t>Cruce definido por posición de grupo (FIFA). Completar equipos al cerrar la fase de grupos.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1º L</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>3º E/H/I/J/K</t>
-        </is>
-      </c>
-      <c r="G10" s="28" t="inlineStr">
-        <is>
-          <t>Cruce definido por posición de grupo (FIFA). Completar equipos al cerrar la fase de grupos.</t>
         </is>
       </c>
     </row>
@@ -17684,19 +17870,29 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>1º G</t>
+          <t>Nueva Zelanda</t>
         </is>
       </c>
       <c r="D11" s="24" t="n"/>
       <c r="E11" s="24" t="n"/>
       <c r="F11" s="28" t="inlineStr">
         <is>
+          <t>Corea del Sur</t>
+        </is>
+      </c>
+      <c r="G11" s="28" t="inlineStr">
+        <is>
+          <t>Cruce definido por posición de grupo (FIFA). Completar equipos al cerrar la fase de grupos.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1º G</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>3º A/E/H/I/J</t>
-        </is>
-      </c>
-      <c r="G11" s="28" t="inlineStr">
-        <is>
-          <t>Cruce definido por posición de grupo (FIFA). Completar equipos al cerrar la fase de grupos.</t>
         </is>
       </c>
     </row>
@@ -17711,19 +17907,29 @@
       </c>
       <c r="C12" s="28" t="inlineStr">
         <is>
-          <t>1º D</t>
+          <t>Estados Unidos</t>
         </is>
       </c>
       <c r="D12" s="24" t="n"/>
       <c r="E12" s="24" t="n"/>
       <c r="F12" s="28" t="inlineStr">
         <is>
+          <t>Bosnia y Herzegovina</t>
+        </is>
+      </c>
+      <c r="G12" s="28" t="inlineStr">
+        <is>
+          <t>Cruce definido por posición de grupo (FIFA). Completar equipos al cerrar la fase de grupos.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1º D</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>3º B/E/F/I/J</t>
-        </is>
-      </c>
-      <c r="G12" s="28" t="inlineStr">
-        <is>
-          <t>Cruce definido por posición de grupo (FIFA). Completar equipos al cerrar la fase de grupos.</t>
         </is>
       </c>
     </row>
@@ -17738,19 +17944,29 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>1º H</t>
+          <t>España</t>
         </is>
       </c>
       <c r="D13" s="24" t="n"/>
       <c r="E13" s="24" t="n"/>
       <c r="F13" s="28" t="inlineStr">
         <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="G13" s="28" t="inlineStr">
+        <is>
+          <t>Cruce definido por posición de grupo (FIFA). Completar equipos al cerrar la fase de grupos.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1º H</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>2º J</t>
-        </is>
-      </c>
-      <c r="G13" s="28" t="inlineStr">
-        <is>
-          <t>Cruce definido por posición de grupo (FIFA). Completar equipos al cerrar la fase de grupos.</t>
         </is>
       </c>
     </row>
@@ -17765,19 +17981,29 @@
       </c>
       <c r="C14" s="28" t="inlineStr">
         <is>
-          <t>2º K</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D14" s="24" t="n"/>
       <c r="E14" s="24" t="n"/>
       <c r="F14" s="28" t="inlineStr">
         <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="G14" s="28" t="inlineStr">
+        <is>
+          <t>Cruce definido por posición de grupo (FIFA). Completar equipos al cerrar la fase de grupos.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2º K</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>2º L</t>
-        </is>
-      </c>
-      <c r="G14" s="28" t="inlineStr">
-        <is>
-          <t>Cruce definido por posición de grupo (FIFA). Completar equipos al cerrar la fase de grupos.</t>
         </is>
       </c>
     </row>
@@ -17792,19 +18018,29 @@
       </c>
       <c r="C15" s="28" t="inlineStr">
         <is>
-          <t>1º B</t>
+          <t>Suiza</t>
         </is>
       </c>
       <c r="D15" s="24" t="n"/>
       <c r="E15" s="24" t="n"/>
       <c r="F15" s="28" t="inlineStr">
         <is>
+          <t>Bélgica</t>
+        </is>
+      </c>
+      <c r="G15" s="28" t="inlineStr">
+        <is>
+          <t>Cruce definido por posición de grupo (FIFA). Completar equipos al cerrar la fase de grupos.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1º B</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>3º E/F/G/I/J</t>
-        </is>
-      </c>
-      <c r="G15" s="28" t="inlineStr">
-        <is>
-          <t>Cruce definido por posición de grupo (FIFA). Completar equipos al cerrar la fase de grupos.</t>
         </is>
       </c>
     </row>
@@ -17819,19 +18055,29 @@
       </c>
       <c r="C16" s="28" t="inlineStr">
         <is>
-          <t>2º D</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D16" s="24" t="n"/>
       <c r="E16" s="24" t="n"/>
       <c r="F16" s="28" t="inlineStr">
         <is>
+          <t>Irán</t>
+        </is>
+      </c>
+      <c r="G16" s="28" t="inlineStr">
+        <is>
+          <t>Cruce definido por posición de grupo (FIFA). Completar equipos al cerrar la fase de grupos.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2º D</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>2º G</t>
-        </is>
-      </c>
-      <c r="G16" s="28" t="inlineStr">
-        <is>
-          <t>Cruce definido por posición de grupo (FIFA). Completar equipos al cerrar la fase de grupos.</t>
         </is>
       </c>
     </row>
@@ -17846,19 +18092,29 @@
       </c>
       <c r="C17" s="28" t="inlineStr">
         <is>
-          <t>1º J</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D17" s="24" t="n"/>
       <c r="E17" s="24" t="n"/>
       <c r="F17" s="28" t="inlineStr">
         <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="G17" s="28" t="inlineStr">
+        <is>
+          <t>Cruce definido por posición de grupo (FIFA). Completar equipos al cerrar la fase de grupos.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1º J</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>2º H</t>
-        </is>
-      </c>
-      <c r="G17" s="28" t="inlineStr">
-        <is>
-          <t>Cruce definido por posición de grupo (FIFA). Completar equipos al cerrar la fase de grupos.</t>
         </is>
       </c>
     </row>
@@ -17873,19 +18129,29 @@
       </c>
       <c r="C18" s="28" t="inlineStr">
         <is>
-          <t>1º K</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="D18" s="24" t="n"/>
       <c r="E18" s="24" t="n"/>
       <c r="F18" s="28" t="inlineStr">
         <is>
+          <t>Croacia</t>
+        </is>
+      </c>
+      <c r="G18" s="28" t="inlineStr">
+        <is>
+          <t>Cruce definido por posición de grupo (FIFA). Completar equipos al cerrar la fase de grupos.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1º K</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>3º D/E/I/J/L</t>
-        </is>
-      </c>
-      <c r="G18" s="28" t="inlineStr">
-        <is>
-          <t>Cruce definido por posición de grupo (FIFA). Completar equipos al cerrar la fase de grupos.</t>
         </is>
       </c>
     </row>
@@ -18129,6 +18395,7 @@
       <c r="F34" s="28" t="n"/>
       <c r="G34" s="28" t="n"/>
     </row>
+    <row r="35"/>
     <row r="36" ht="15" customHeight="1" s="32">
       <c r="A36" s="33" t="inlineStr">
         <is>

--- a/Mundial_2026_fuente_datos.xlsx
+++ b/Mundial_2026_fuente_datos.xlsx
@@ -557,7 +557,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Cargados 34 resultados con marcador exacto verificado: fecha 1 completa de los 12 grupos + fecha 2 de A, B, C, D, Argelia-Jordania (J) e Inglaterra-Ghana (L). El resto de la fecha 2 y la fecha 3 estaban en juego/sin confirmar al 24-jun-2026: completalos vos o que tu Python los traiga en vivo. Fuente: Yahoo Sports / Wikipedia por grupo.</t>
+          <t>Cargados 54 resultados de fase de grupos (marcador exacto): fechas 1 y 2 completas de los 12 grupos + parte de la fecha 3. El resto se simula. Variables curadas agregadas: puntaje de DT, clasificatorias ponderadas por confederacion y % de jugadores en top-5 ligas (estimaciones ~early-2026). Fuente resultados: Yahoo Sports / Wikipedia por grupo.</t>
         </is>
       </c>
     </row>
@@ -6821,7 +6821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" style="32" min="1" max="1"/>
@@ -6875,6 +6875,21 @@
           <t>Trayectoria / notas</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Punt. selección (0-50)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Punt. clubes (0-50)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Puntaje DT (0-100)</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="23.85" customHeight="1" s="32">
       <c r="A3" s="7" t="n">
@@ -6908,6 +6923,15 @@
           <t>Tercera etapa en México; dirigió en los Mundiales 1994, 2002 y 2010</t>
         </is>
       </c>
+      <c r="H3" t="n">
+        <v>24</v>
+      </c>
+      <c r="I3" t="n">
+        <v>22</v>
+      </c>
+      <c r="J3" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="32">
       <c r="A4" s="7" t="n">
@@ -6941,6 +6965,15 @@
           <t>Campeón de la Copa Africana 2017 con Camerún</t>
         </is>
       </c>
+      <c r="H4" t="n">
+        <v>30</v>
+      </c>
+      <c r="I4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J4" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="32">
       <c r="A5" s="7" t="n">
@@ -6974,6 +7007,15 @@
           <t>Exjugador; dirigió a Corea en el Mundial 2014</t>
         </is>
       </c>
+      <c r="H5" t="n">
+        <v>18</v>
+      </c>
+      <c r="I5" t="n">
+        <v>12</v>
+      </c>
+      <c r="J5" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="32">
       <c r="A6" s="7" t="n">
@@ -7003,6 +7045,15 @@
         </is>
       </c>
       <c r="G6" s="8" t="n"/>
+      <c r="H6" t="n">
+        <v>8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>12</v>
+      </c>
+      <c r="J6" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="32">
       <c r="A7" s="10" t="n">
@@ -7036,6 +7087,15 @@
           <t>Ex RB Leipzig y RB Salzburg</t>
         </is>
       </c>
+      <c r="H7" t="n">
+        <v>14</v>
+      </c>
+      <c r="I7" t="n">
+        <v>22</v>
+      </c>
+      <c r="J7" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="8" ht="23.85" customHeight="1" s="32">
       <c r="A8" s="10" t="n">
@@ -7069,6 +7129,15 @@
           <t>Primer cargo importante como DT</t>
         </is>
       </c>
+      <c r="H8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="9" ht="23.85" customHeight="1" s="32">
       <c r="A9" s="10" t="n">
@@ -7102,6 +7171,15 @@
           <t>Exseleccionador de España; ex DT Real Madrid y Sevilla</t>
         </is>
       </c>
+      <c r="H9" t="n">
+        <v>18</v>
+      </c>
+      <c r="I9" t="n">
+        <v>30</v>
+      </c>
+      <c r="J9" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="32">
       <c r="A10" s="10" t="n">
@@ -7131,6 +7209,15 @@
         </is>
       </c>
       <c r="G10" s="11" t="n"/>
+      <c r="H10" t="n">
+        <v>20</v>
+      </c>
+      <c r="I10" t="n">
+        <v>16</v>
+      </c>
+      <c r="J10" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="11" ht="23.85" customHeight="1" s="32">
       <c r="A11" s="7" t="n">
@@ -7164,6 +7251,15 @@
           <t>5 Champions League como DT (récord); primer Mundial como entrenador</t>
         </is>
       </c>
+      <c r="H11" t="n">
+        <v>8</v>
+      </c>
+      <c r="I11" t="n">
+        <v>50</v>
+      </c>
+      <c r="J11" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="12" ht="23.85" customHeight="1" s="32">
       <c r="A12" s="7" t="n">
@@ -7197,6 +7293,15 @@
           <t>Campeón del Mundial sub-20 2025; asumió tras la Copa Africana 2025</t>
         </is>
       </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J12" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="32">
       <c r="A13" s="7" t="n">
@@ -7230,6 +7335,15 @@
           <t>Clasificó a Haití sin pisar el país por el conflicto interno</t>
         </is>
       </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="n">
+        <v>6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="32">
       <c r="A14" s="7" t="n">
@@ -7263,6 +7377,15 @@
           <t>Ex asistente de Mourinho en Chelsea</t>
         </is>
       </c>
+      <c r="H14" t="n">
+        <v>22</v>
+      </c>
+      <c r="I14" t="n">
+        <v>14</v>
+      </c>
+      <c r="J14" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="32">
       <c r="A15" s="10" t="n">
@@ -7296,6 +7419,15 @@
           <t>Ex Tottenham y PSG</t>
         </is>
       </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="n">
+        <v>36</v>
+      </c>
+      <c r="J15" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="32">
       <c r="A16" s="10" t="n">
@@ -7325,6 +7457,15 @@
         </is>
       </c>
       <c r="G16" s="11" t="n"/>
+      <c r="H16" t="n">
+        <v>24</v>
+      </c>
+      <c r="I16" t="n">
+        <v>20</v>
+      </c>
+      <c r="J16" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="32">
       <c r="A17" s="10" t="n">
@@ -7354,6 +7495,15 @@
         </is>
       </c>
       <c r="G17" s="11" t="n"/>
+      <c r="H17" t="n">
+        <v>16</v>
+      </c>
+      <c r="I17" t="n">
+        <v>16</v>
+      </c>
+      <c r="J17" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="32">
       <c r="A18" s="10" t="n">
@@ -7387,6 +7537,15 @@
           <t>Exjugador de Roma; ex DT Milan y Fiorentina</t>
         </is>
       </c>
+      <c r="H18" t="n">
+        <v>16</v>
+      </c>
+      <c r="I18" t="n">
+        <v>22</v>
+      </c>
+      <c r="J18" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="32">
       <c r="A19" s="7" t="n">
@@ -7420,6 +7579,15 @@
           <t>Ex RB Leipzig</t>
         </is>
       </c>
+      <c r="H19" t="n">
+        <v>22</v>
+      </c>
+      <c r="I19" t="n">
+        <v>30</v>
+      </c>
+      <c r="J19" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="20" ht="23.85" customHeight="1" s="32">
       <c r="A20" s="7" t="n">
@@ -7453,6 +7621,15 @@
           <t>Veterano; dirigió múltiples selecciones (Países Bajos, Rusia, etc.)</t>
         </is>
       </c>
+      <c r="H20" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" t="n">
+        <v>26</v>
+      </c>
+      <c r="J20" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="32">
       <c r="A21" s="7" t="n">
@@ -7486,6 +7663,15 @@
           <t>Campeón de la Copa Africana 2023</t>
         </is>
       </c>
+      <c r="H21" t="n">
+        <v>26</v>
+      </c>
+      <c r="I21" t="n">
+        <v>6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="32">
       <c r="A22" s="7" t="n">
@@ -7515,6 +7701,15 @@
         </is>
       </c>
       <c r="G22" s="8" t="n"/>
+      <c r="H22" t="n">
+        <v>16</v>
+      </c>
+      <c r="I22" t="n">
+        <v>16</v>
+      </c>
+      <c r="J22" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="23" ht="23.85" customHeight="1" s="32">
       <c r="A23" s="10" t="n">
@@ -7548,6 +7743,15 @@
           <t>Único en jugar y dirigir a Ajax, PSV y Feyenoord</t>
         </is>
       </c>
+      <c r="H23" t="n">
+        <v>26</v>
+      </c>
+      <c r="I23" t="n">
+        <v>30</v>
+      </c>
+      <c r="J23" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="32">
       <c r="A24" s="10" t="n">
@@ -7581,6 +7785,15 @@
           <t>Dirigió a Japón en el Mundial 2022</t>
         </is>
       </c>
+      <c r="H24" t="n">
+        <v>24</v>
+      </c>
+      <c r="I24" t="n">
+        <v>14</v>
+      </c>
+      <c r="J24" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="32">
       <c r="A25" s="10" t="n">
@@ -7614,6 +7827,15 @@
           <t>Ex Brighton</t>
         </is>
       </c>
+      <c r="H25" t="n">
+        <v>8</v>
+      </c>
+      <c r="I25" t="n">
+        <v>22</v>
+      </c>
+      <c r="J25" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="32">
       <c r="A26" s="10" t="n">
@@ -7647,6 +7869,15 @@
           <t>Cambio reciente en el banco tunecino</t>
         </is>
       </c>
+      <c r="H26" t="n">
+        <v>14</v>
+      </c>
+      <c r="I26" t="n">
+        <v>8</v>
+      </c>
+      <c r="J26" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="32">
       <c r="A27" s="7" t="n">
@@ -7680,6 +7911,15 @@
           <t>Ex Roma, Marsella y Lyon</t>
         </is>
       </c>
+      <c r="H27" t="n">
+        <v>8</v>
+      </c>
+      <c r="I27" t="n">
+        <v>30</v>
+      </c>
+      <c r="J27" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="32">
       <c r="A28" s="7" t="n">
@@ -7713,6 +7953,15 @@
           <t>Máximo goleador histórico de Egipto como jugador</t>
         </is>
       </c>
+      <c r="H28" t="n">
+        <v>16</v>
+      </c>
+      <c r="I28" t="n">
+        <v>14</v>
+      </c>
+      <c r="J28" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="32">
       <c r="A29" s="7" t="n">
@@ -7746,6 +7995,15 @@
           <t>Segunda etapa al frente de Irán</t>
         </is>
       </c>
+      <c r="H29" t="n">
+        <v>18</v>
+      </c>
+      <c r="I29" t="n">
+        <v>14</v>
+      </c>
+      <c r="J29" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="32">
       <c r="A30" s="7" t="n">
@@ -7775,6 +8033,15 @@
         </is>
       </c>
       <c r="G30" s="8" t="n"/>
+      <c r="H30" t="n">
+        <v>10</v>
+      </c>
+      <c r="I30" t="n">
+        <v>6</v>
+      </c>
+      <c r="J30" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="31" ht="23.85" customHeight="1" s="32">
       <c r="A31" s="10" t="n">
@@ -7808,6 +8075,15 @@
           <t>Campeón de la UEFA Nations League 2023 y la Euro 2024</t>
         </is>
       </c>
+      <c r="H31" t="n">
+        <v>34</v>
+      </c>
+      <c r="I31" t="n">
+        <v>6</v>
+      </c>
+      <c r="J31" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="32">
       <c r="A32" s="10" t="n">
@@ -7841,6 +8117,15 @@
           <t>Clasificó a Cabo Verde a su primer Mundial</t>
         </is>
       </c>
+      <c r="H32" t="n">
+        <v>14</v>
+      </c>
+      <c r="I32" t="n">
+        <v>6</v>
+      </c>
+      <c r="J32" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="32">
       <c r="A33" s="10" t="n">
@@ -7874,6 +8159,15 @@
           <t>Asumió en abril-2026 en reemplazo de Hervé Renard</t>
         </is>
       </c>
+      <c r="H33" t="n">
+        <v>8</v>
+      </c>
+      <c r="I33" t="n">
+        <v>14</v>
+      </c>
+      <c r="J33" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="32">
       <c r="A34" s="10" t="n">
@@ -7907,6 +8201,15 @@
           <t>Exseleccionador de Argentina y Chile</t>
         </is>
       </c>
+      <c r="H34" t="n">
+        <v>30</v>
+      </c>
+      <c r="I34" t="n">
+        <v>26</v>
+      </c>
+      <c r="J34" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="35" ht="23.85" customHeight="1" s="32">
       <c r="A35" s="7" t="n">
@@ -7940,6 +8243,15 @@
           <t>Campeón del Mundial 2018 y finalista 2022; última competencia en el cargo</t>
         </is>
       </c>
+      <c r="H35" t="n">
+        <v>50</v>
+      </c>
+      <c r="I35" t="n">
+        <v>28</v>
+      </c>
+      <c r="J35" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="32">
       <c r="A36" s="7" t="n">
@@ -7969,6 +8281,15 @@
         </is>
       </c>
       <c r="G36" s="8" t="n"/>
+      <c r="H36" t="n">
+        <v>12</v>
+      </c>
+      <c r="I36" t="n">
+        <v>8</v>
+      </c>
+      <c r="J36" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="32">
       <c r="A37" s="7" t="n">
@@ -8002,6 +8323,15 @@
           <t>Dos etapas al frente de Australia</t>
         </is>
       </c>
+      <c r="H37" t="n">
+        <v>20</v>
+      </c>
+      <c r="I37" t="n">
+        <v>14</v>
+      </c>
+      <c r="J37" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="32">
       <c r="A38" s="7" t="n">
@@ -8031,6 +8361,15 @@
         </is>
       </c>
       <c r="G38" s="8" t="n"/>
+      <c r="H38" t="n">
+        <v>18</v>
+      </c>
+      <c r="I38" t="n">
+        <v>20</v>
+      </c>
+      <c r="J38" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="39" ht="23.85" customHeight="1" s="32">
       <c r="A39" s="10" t="n">
@@ -8064,6 +8403,15 @@
           <t>Campeón del Mundial 2022 y de la Copa América 2021 y 2024</t>
         </is>
       </c>
+      <c r="H39" t="n">
+        <v>48</v>
+      </c>
+      <c r="I39" t="n">
+        <v>4</v>
+      </c>
+      <c r="J39" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="40" ht="23.85" customHeight="1" s="32">
       <c r="A40" s="10" t="n">
@@ -8097,6 +8445,15 @@
           <t>Ex DT de Lazio y Burdeos</t>
         </is>
       </c>
+      <c r="H40" t="n">
+        <v>26</v>
+      </c>
+      <c r="I40" t="n">
+        <v>18</v>
+      </c>
+      <c r="J40" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="32">
       <c r="A41" s="10" t="n">
@@ -8130,6 +8487,15 @@
           <t>Referente del pressing alemán moderno</t>
         </is>
       </c>
+      <c r="H41" t="n">
+        <v>22</v>
+      </c>
+      <c r="I41" t="n">
+        <v>32</v>
+      </c>
+      <c r="J41" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="32">
       <c r="A42" s="10" t="n">
@@ -8163,6 +8529,15 @@
           <t>Clasificó a Jordania a su primer Mundial</t>
         </is>
       </c>
+      <c r="H42" t="n">
+        <v>16</v>
+      </c>
+      <c r="I42" t="n">
+        <v>8</v>
+      </c>
+      <c r="J42" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="32">
       <c r="A43" s="7" t="n">
@@ -8196,6 +8571,15 @@
           <t>3er puesto en el Mundial 2018 con Bélgica</t>
         </is>
       </c>
+      <c r="H43" t="n">
+        <v>28</v>
+      </c>
+      <c r="I43" t="n">
+        <v>22</v>
+      </c>
+      <c r="J43" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="32">
       <c r="A44" s="7" t="n">
@@ -8225,6 +8609,15 @@
         </is>
       </c>
       <c r="G44" s="8" t="n"/>
+      <c r="H44" t="n">
+        <v>18</v>
+      </c>
+      <c r="I44" t="n">
+        <v>10</v>
+      </c>
+      <c r="J44" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="45" ht="23.85" customHeight="1" s="32">
       <c r="A45" s="7" t="n">
@@ -8258,6 +8651,15 @@
           <t>Campeón del Mundial 2006 y Balón de Oro como jugador; primer Mundial como DT</t>
         </is>
       </c>
+      <c r="H45" t="n">
+        <v>8</v>
+      </c>
+      <c r="I45" t="n">
+        <v>18</v>
+      </c>
+      <c r="J45" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="32">
       <c r="A46" s="7" t="n">
@@ -8291,6 +8693,15 @@
           <t>Siete años como asistente de Pékerman en Colombia</t>
         </is>
       </c>
+      <c r="H46" t="n">
+        <v>22</v>
+      </c>
+      <c r="I46" t="n">
+        <v>12</v>
+      </c>
+      <c r="J46" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="32">
       <c r="A47" s="10" t="n">
@@ -8324,6 +8735,15 @@
           <t>Campeón de la Champions 2021 con Chelsea</t>
         </is>
       </c>
+      <c r="H47" t="n">
+        <v>12</v>
+      </c>
+      <c r="I47" t="n">
+        <v>40</v>
+      </c>
+      <c r="J47" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="32">
       <c r="A48" s="10" t="n">
@@ -8357,6 +8777,15 @@
           <t>Subcampeón del Mundial 2018 y 3er puesto 2022</t>
         </is>
       </c>
+      <c r="H48" t="n">
+        <v>36</v>
+      </c>
+      <c r="I48" t="n">
+        <v>14</v>
+      </c>
+      <c r="J48" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="49" ht="23.85" customHeight="1" s="32">
       <c r="A49" s="10" t="n">
@@ -8390,6 +8819,15 @@
           <t>Asumió en abril-2026 tras la salida de Otto Addo; ex asistente del Man Utd</t>
         </is>
       </c>
+      <c r="H49" t="n">
+        <v>28</v>
+      </c>
+      <c r="I49" t="n">
+        <v>18</v>
+      </c>
+      <c r="J49" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="32">
       <c r="A50" s="10" t="n">
@@ -8422,6 +8860,15 @@
         <is>
           <t>Clasificó a Panamá a su segundo Mundial</t>
         </is>
+      </c>
+      <c r="H50" t="n">
+        <v>18</v>
+      </c>
+      <c r="I50" t="n">
+        <v>14</v>
+      </c>
+      <c r="J50" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="32">
@@ -8448,7 +8895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N52"/>
+  <dimension ref="A1:P52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" style="32" min="1" max="1"/>
@@ -8539,6 +8986,16 @@
           <t>GC/PJ</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Dificultad conf.</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Puntaje clasif. ponderado</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="32">
       <c r="A3" s="7" t="n">
@@ -8580,6 +9037,12 @@
         <f>IF(N(D3)=0,"",I3/D3)</f>
         <v/>
       </c>
+      <c r="O3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P3" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="32">
       <c r="A4" s="7" t="n">
@@ -8595,12 +9058,24 @@
           <t>CAF</t>
         </is>
       </c>
-      <c r="D4" s="24" t="n"/>
-      <c r="E4" s="24" t="n"/>
-      <c r="F4" s="24" t="n"/>
-      <c r="G4" s="24" t="n"/>
-      <c r="H4" s="24" t="n"/>
-      <c r="I4" s="24" t="n"/>
+      <c r="D4" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="I4" s="24" t="n">
+        <v>8</v>
+      </c>
       <c r="J4" s="7">
         <f>IF(COUNT(D4:G4)=0,"",3*E4+F4)</f>
         <v/>
@@ -8620,6 +9095,12 @@
       <c r="N4" s="9">
         <f>IF(N(D4)=0,"",I4/D4)</f>
         <v/>
+      </c>
+      <c r="O4" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="P4" t="n">
+        <v>34.7</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="32">
@@ -8636,12 +9117,24 @@
           <t>AFC</t>
         </is>
       </c>
-      <c r="D5" s="24" t="n"/>
-      <c r="E5" s="24" t="n"/>
-      <c r="F5" s="24" t="n"/>
-      <c r="G5" s="24" t="n"/>
-      <c r="H5" s="24" t="n"/>
-      <c r="I5" s="24" t="n"/>
+      <c r="D5" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="I5" s="24" t="n">
+        <v>6</v>
+      </c>
       <c r="J5" s="7">
         <f>IF(COUNT(D5:G5)=0,"",3*E5+F5)</f>
         <v/>
@@ -8661,6 +9154,12 @@
       <c r="N5" s="9">
         <f>IF(N(D5)=0,"",I5/D5)</f>
         <v/>
+      </c>
+      <c r="O5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="P5" t="n">
+        <v>38.4</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="32">
@@ -8677,12 +9176,24 @@
           <t>UEFA</t>
         </is>
       </c>
-      <c r="D6" s="24" t="n"/>
-      <c r="E6" s="24" t="n"/>
-      <c r="F6" s="24" t="n"/>
-      <c r="G6" s="24" t="n"/>
-      <c r="H6" s="24" t="n"/>
-      <c r="I6" s="24" t="n"/>
+      <c r="D6" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="I6" s="24" t="n">
+        <v>9</v>
+      </c>
       <c r="J6" s="7">
         <f>IF(COUNT(D6:G6)=0,"",3*E6+F6)</f>
         <v/>
@@ -8702,6 +9213,12 @@
       <c r="N6" s="9">
         <f>IF(N(D6)=0,"",I6/D6)</f>
         <v/>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>66.7</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="32">
@@ -8744,6 +9261,12 @@
         <f>IF(N(D7)=0,"",I7/D7)</f>
         <v/>
       </c>
+      <c r="O7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P7" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="32">
       <c r="A8" s="7" t="n">
@@ -8759,12 +9282,24 @@
           <t>UEFA</t>
         </is>
       </c>
-      <c r="D8" s="24" t="n"/>
-      <c r="E8" s="24" t="n"/>
-      <c r="F8" s="24" t="n"/>
-      <c r="G8" s="24" t="n"/>
-      <c r="H8" s="24" t="n"/>
-      <c r="I8" s="24" t="n"/>
+      <c r="D8" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="I8" s="24" t="n">
+        <v>8</v>
+      </c>
       <c r="J8" s="7">
         <f>IF(COUNT(D8:G8)=0,"",3*E8+F8)</f>
         <v/>
@@ -8784,6 +9319,12 @@
       <c r="N8" s="9">
         <f>IF(N(D8)=0,"",I8/D8)</f>
         <v/>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>70.8</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="32">
@@ -8800,12 +9341,24 @@
           <t>AFC</t>
         </is>
       </c>
-      <c r="D9" s="24" t="n"/>
-      <c r="E9" s="24" t="n"/>
-      <c r="F9" s="24" t="n"/>
-      <c r="G9" s="24" t="n"/>
-      <c r="H9" s="24" t="n"/>
-      <c r="I9" s="24" t="n"/>
+      <c r="D9" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="I9" s="24" t="n">
+        <v>9</v>
+      </c>
       <c r="J9" s="7">
         <f>IF(COUNT(D9:G9)=0,"",3*E9+F9)</f>
         <v/>
@@ -8825,6 +9378,12 @@
       <c r="N9" s="9">
         <f>IF(N(D9)=0,"",I9/D9)</f>
         <v/>
+      </c>
+      <c r="O9" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="P9" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="32">
@@ -8841,12 +9400,24 @@
           <t>UEFA</t>
         </is>
       </c>
-      <c r="D10" s="24" t="n"/>
-      <c r="E10" s="24" t="n"/>
-      <c r="F10" s="24" t="n"/>
-      <c r="G10" s="24" t="n"/>
-      <c r="H10" s="24" t="n"/>
-      <c r="I10" s="24" t="n"/>
+      <c r="D10" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="I10" s="24" t="n">
+        <v>6</v>
+      </c>
       <c r="J10" s="7">
         <f>IF(COUNT(D10:G10)=0,"",3*E10+F10)</f>
         <v/>
@@ -8866,6 +9437,12 @@
       <c r="N10" s="9">
         <f>IF(N(D10)=0,"",I10/D10)</f>
         <v/>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="32">
@@ -8882,12 +9459,24 @@
           <t>CONMEBOL</t>
         </is>
       </c>
-      <c r="D11" s="24" t="n"/>
-      <c r="E11" s="24" t="n"/>
-      <c r="F11" s="24" t="n"/>
-      <c r="G11" s="24" t="n"/>
-      <c r="H11" s="24" t="n"/>
-      <c r="I11" s="24" t="n"/>
+      <c r="D11" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="E11" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="H11" s="24" t="n">
+        <v>24</v>
+      </c>
+      <c r="I11" s="24" t="n">
+        <v>18</v>
+      </c>
       <c r="J11" s="7">
         <f>IF(COUNT(D11:G11)=0,"",3*E11+F11)</f>
         <v/>
@@ -8907,6 +9496,12 @@
       <c r="N11" s="9">
         <f>IF(N(D11)=0,"",I11/D11)</f>
         <v/>
+      </c>
+      <c r="O11" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="P11" t="n">
+        <v>49.3</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="32">
@@ -8923,12 +9518,24 @@
           <t>CAF</t>
         </is>
       </c>
-      <c r="D12" s="24" t="n"/>
-      <c r="E12" s="24" t="n"/>
-      <c r="F12" s="24" t="n"/>
-      <c r="G12" s="24" t="n"/>
-      <c r="H12" s="24" t="n"/>
-      <c r="I12" s="24" t="n"/>
+      <c r="D12" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="I12" s="24" t="n">
+        <v>5</v>
+      </c>
       <c r="J12" s="7">
         <f>IF(COUNT(D12:G12)=0,"",3*E12+F12)</f>
         <v/>
@@ -8948,6 +9555,12 @@
       <c r="N12" s="9">
         <f>IF(N(D12)=0,"",I12/D12)</f>
         <v/>
+      </c>
+      <c r="O12" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="P12" t="n">
+        <v>43.3</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="32">
@@ -8964,12 +9577,24 @@
           <t>CONCACAF</t>
         </is>
       </c>
-      <c r="D13" s="24" t="n"/>
-      <c r="E13" s="24" t="n"/>
-      <c r="F13" s="24" t="n"/>
-      <c r="G13" s="24" t="n"/>
-      <c r="H13" s="24" t="n"/>
-      <c r="I13" s="24" t="n"/>
+      <c r="D13" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" s="24" t="n">
+        <v>10</v>
+      </c>
       <c r="J13" s="7">
         <f>IF(COUNT(D13:G13)=0,"",3*E13+F13)</f>
         <v/>
@@ -8989,6 +9614,12 @@
       <c r="N13" s="9">
         <f>IF(N(D13)=0,"",I13/D13)</f>
         <v/>
+      </c>
+      <c r="O13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P13" t="n">
+        <v>28.3</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="32">
@@ -9005,12 +9636,24 @@
           <t>UEFA</t>
         </is>
       </c>
-      <c r="D14" s="24" t="n"/>
-      <c r="E14" s="24" t="n"/>
-      <c r="F14" s="24" t="n"/>
-      <c r="G14" s="24" t="n"/>
-      <c r="H14" s="24" t="n"/>
-      <c r="I14" s="24" t="n"/>
+      <c r="D14" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E14" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" s="24" t="n">
+        <v>8</v>
+      </c>
       <c r="J14" s="7">
         <f>IF(COUNT(D14:G14)=0,"",3*E14+F14)</f>
         <v/>
@@ -9030,6 +9673,12 @@
       <c r="N14" s="9">
         <f>IF(N(D14)=0,"",I14/D14)</f>
         <v/>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>70.8</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="32">
@@ -9072,6 +9721,12 @@
         <f>IF(N(D15)=0,"",I15/D15)</f>
         <v/>
       </c>
+      <c r="O15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P15" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="32">
       <c r="A16" s="7" t="n">
@@ -9087,12 +9742,24 @@
           <t>CONMEBOL</t>
         </is>
       </c>
-      <c r="D16" s="24" t="n"/>
-      <c r="E16" s="24" t="n"/>
-      <c r="F16" s="24" t="n"/>
-      <c r="G16" s="24" t="n"/>
-      <c r="H16" s="24" t="n"/>
-      <c r="I16" s="24" t="n"/>
+      <c r="D16" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="E16" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="F16" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="G16" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="I16" s="24" t="n">
+        <v>10</v>
+      </c>
       <c r="J16" s="7">
         <f>IF(COUNT(D16:G16)=0,"",3*E16+F16)</f>
         <v/>
@@ -9112,6 +9779,12 @@
       <c r="N16" s="9">
         <f>IF(N(D16)=0,"",I16/D16)</f>
         <v/>
+      </c>
+      <c r="O16" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="P16" t="n">
+        <v>49.3</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="32">
@@ -9128,12 +9801,24 @@
           <t>AFC</t>
         </is>
       </c>
-      <c r="D17" s="24" t="n"/>
-      <c r="E17" s="24" t="n"/>
-      <c r="F17" s="24" t="n"/>
-      <c r="G17" s="24" t="n"/>
-      <c r="H17" s="24" t="n"/>
-      <c r="I17" s="24" t="n"/>
+      <c r="D17" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="I17" s="24" t="n">
+        <v>8</v>
+      </c>
       <c r="J17" s="7">
         <f>IF(COUNT(D17:G17)=0,"",3*E17+F17)</f>
         <v/>
@@ -9153,6 +9838,12 @@
       <c r="N17" s="9">
         <f>IF(N(D17)=0,"",I17/D17)</f>
         <v/>
+      </c>
+      <c r="O17" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="P17" t="n">
+        <v>33.6</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="32">
@@ -9169,12 +9860,24 @@
           <t>UEFA</t>
         </is>
       </c>
-      <c r="D18" s="24" t="n"/>
-      <c r="E18" s="24" t="n"/>
-      <c r="F18" s="24" t="n"/>
-      <c r="G18" s="24" t="n"/>
-      <c r="H18" s="24" t="n"/>
-      <c r="I18" s="24" t="n"/>
+      <c r="D18" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="I18" s="24" t="n">
+        <v>9</v>
+      </c>
       <c r="J18" s="7">
         <f>IF(COUNT(D18:G18)=0,"",3*E18+F18)</f>
         <v/>
@@ -9194,6 +9897,12 @@
       <c r="N18" s="9">
         <f>IF(N(D18)=0,"",I18/D18)</f>
         <v/>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>70.8</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="32">
@@ -9210,12 +9919,24 @@
           <t>UEFA</t>
         </is>
       </c>
-      <c r="D19" s="24" t="n"/>
-      <c r="E19" s="24" t="n"/>
-      <c r="F19" s="24" t="n"/>
-      <c r="G19" s="24" t="n"/>
-      <c r="H19" s="24" t="n"/>
-      <c r="I19" s="24" t="n"/>
+      <c r="D19" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E19" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="I19" s="24" t="n">
+        <v>7</v>
+      </c>
       <c r="J19" s="7">
         <f>IF(COUNT(D19:G19)=0,"",3*E19+F19)</f>
         <v/>
@@ -9235,6 +9956,12 @@
       <c r="N19" s="9">
         <f>IF(N(D19)=0,"",I19/D19)</f>
         <v/>
+      </c>
+      <c r="O19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>79.2</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="32">
@@ -9251,12 +9978,24 @@
           <t>CONCACAF</t>
         </is>
       </c>
-      <c r="D20" s="24" t="n"/>
-      <c r="E20" s="24" t="n"/>
-      <c r="F20" s="24" t="n"/>
-      <c r="G20" s="24" t="n"/>
-      <c r="H20" s="24" t="n"/>
-      <c r="I20" s="24" t="n"/>
+      <c r="D20" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="G20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="I20" s="24" t="n">
+        <v>9</v>
+      </c>
       <c r="J20" s="7">
         <f>IF(COUNT(D20:G20)=0,"",3*E20+F20)</f>
         <v/>
@@ -9276,6 +10015,12 @@
       <c r="N20" s="9">
         <f>IF(N(D20)=0,"",I20/D20)</f>
         <v/>
+      </c>
+      <c r="O20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P20" t="n">
+        <v>26.7</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="32">
@@ -9292,12 +10037,24 @@
           <t>CAF</t>
         </is>
       </c>
-      <c r="D21" s="24" t="n"/>
-      <c r="E21" s="24" t="n"/>
-      <c r="F21" s="24" t="n"/>
-      <c r="G21" s="24" t="n"/>
-      <c r="H21" s="24" t="n"/>
-      <c r="I21" s="24" t="n"/>
+      <c r="D21" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="I21" s="24" t="n">
+        <v>8</v>
+      </c>
       <c r="J21" s="7">
         <f>IF(COUNT(D21:G21)=0,"",3*E21+F21)</f>
         <v/>
@@ -9317,6 +10074,12 @@
       <c r="N21" s="9">
         <f>IF(N(D21)=0,"",I21/D21)</f>
         <v/>
+      </c>
+      <c r="O21" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="P21" t="n">
+        <v>34.7</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="32">
@@ -9333,12 +10096,24 @@
           <t>CONMEBOL</t>
         </is>
       </c>
-      <c r="D22" s="24" t="n"/>
-      <c r="E22" s="24" t="n"/>
-      <c r="F22" s="24" t="n"/>
-      <c r="G22" s="24" t="n"/>
-      <c r="H22" s="24" t="n"/>
-      <c r="I22" s="24" t="n"/>
+      <c r="D22" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="E22" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="F22" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="H22" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="I22" s="24" t="n">
+        <v>14</v>
+      </c>
       <c r="J22" s="7">
         <f>IF(COUNT(D22:G22)=0,"",3*E22+F22)</f>
         <v/>
@@ -9358,6 +10133,12 @@
       <c r="N22" s="9">
         <f>IF(N(D22)=0,"",I22/D22)</f>
         <v/>
+      </c>
+      <c r="O22" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="P22" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="32">
@@ -9374,12 +10155,24 @@
           <t>UEFA</t>
         </is>
       </c>
-      <c r="D23" s="24" t="n"/>
-      <c r="E23" s="24" t="n"/>
-      <c r="F23" s="24" t="n"/>
-      <c r="G23" s="24" t="n"/>
-      <c r="H23" s="24" t="n"/>
-      <c r="I23" s="24" t="n"/>
+      <c r="D23" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E23" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F23" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="24" t="n">
+        <v>19</v>
+      </c>
+      <c r="I23" s="24" t="n">
+        <v>8</v>
+      </c>
       <c r="J23" s="7">
         <f>IF(COUNT(D23:G23)=0,"",3*E23+F23)</f>
         <v/>
@@ -9399,6 +10192,12 @@
       <c r="N23" s="9">
         <f>IF(N(D23)=0,"",I23/D23)</f>
         <v/>
+      </c>
+      <c r="O23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" t="n">
+        <v>83.3</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="32">
@@ -9415,12 +10214,24 @@
           <t>AFC</t>
         </is>
       </c>
-      <c r="D24" s="24" t="n"/>
-      <c r="E24" s="24" t="n"/>
-      <c r="F24" s="24" t="n"/>
-      <c r="G24" s="24" t="n"/>
-      <c r="H24" s="24" t="n"/>
-      <c r="I24" s="24" t="n"/>
+      <c r="D24" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="F24" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="I24" s="24" t="n">
+        <v>4</v>
+      </c>
       <c r="J24" s="7">
         <f>IF(COUNT(D24:G24)=0,"",3*E24+F24)</f>
         <v/>
@@ -9440,6 +10251,12 @@
       <c r="N24" s="9">
         <f>IF(N(D24)=0,"",I24/D24)</f>
         <v/>
+      </c>
+      <c r="O24" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="P24" t="n">
+        <v>41.6</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="32">
@@ -9456,12 +10273,24 @@
           <t>UEFA</t>
         </is>
       </c>
-      <c r="D25" s="24" t="n"/>
-      <c r="E25" s="24" t="n"/>
-      <c r="F25" s="24" t="n"/>
-      <c r="G25" s="24" t="n"/>
-      <c r="H25" s="24" t="n"/>
-      <c r="I25" s="24" t="n"/>
+      <c r="D25" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E25" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="I25" s="24" t="n">
+        <v>10</v>
+      </c>
       <c r="J25" s="7">
         <f>IF(COUNT(D25:G25)=0,"",3*E25+F25)</f>
         <v/>
@@ -9481,6 +10310,12 @@
       <c r="N25" s="9">
         <f>IF(N(D25)=0,"",I25/D25)</f>
         <v/>
+      </c>
+      <c r="O25" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" t="n">
+        <v>58.3</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="32">
@@ -9497,12 +10332,24 @@
           <t>CAF</t>
         </is>
       </c>
-      <c r="D26" s="24" t="n"/>
-      <c r="E26" s="24" t="n"/>
-      <c r="F26" s="24" t="n"/>
-      <c r="G26" s="24" t="n"/>
-      <c r="H26" s="24" t="n"/>
-      <c r="I26" s="24" t="n"/>
+      <c r="D26" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="I26" s="24" t="n">
+        <v>2</v>
+      </c>
       <c r="J26" s="7">
         <f>IF(COUNT(D26:G26)=0,"",3*E26+F26)</f>
         <v/>
@@ -9522,6 +10369,12 @@
       <c r="N26" s="9">
         <f>IF(N(D26)=0,"",I26/D26)</f>
         <v/>
+      </c>
+      <c r="O26" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="P26" t="n">
+        <v>36.4</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="32">
@@ -9538,12 +10391,24 @@
           <t>UEFA</t>
         </is>
       </c>
-      <c r="D27" s="24" t="n"/>
-      <c r="E27" s="24" t="n"/>
-      <c r="F27" s="24" t="n"/>
-      <c r="G27" s="24" t="n"/>
-      <c r="H27" s="24" t="n"/>
-      <c r="I27" s="24" t="n"/>
+      <c r="D27" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E27" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="I27" s="24" t="n">
+        <v>9</v>
+      </c>
       <c r="J27" s="7">
         <f>IF(COUNT(D27:G27)=0,"",3*E27+F27)</f>
         <v/>
@@ -9563,6 +10428,12 @@
       <c r="N27" s="9">
         <f>IF(N(D27)=0,"",I27/D27)</f>
         <v/>
+      </c>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="32">
@@ -9579,12 +10450,24 @@
           <t>CAF</t>
         </is>
       </c>
-      <c r="D28" s="24" t="n"/>
-      <c r="E28" s="24" t="n"/>
-      <c r="F28" s="24" t="n"/>
-      <c r="G28" s="24" t="n"/>
-      <c r="H28" s="24" t="n"/>
-      <c r="I28" s="24" t="n"/>
+      <c r="D28" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="F28" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="I28" s="24" t="n">
+        <v>5</v>
+      </c>
       <c r="J28" s="7">
         <f>IF(COUNT(D28:G28)=0,"",3*E28+F28)</f>
         <v/>
@@ -9604,6 +10487,12 @@
       <c r="N28" s="9">
         <f>IF(N(D28)=0,"",I28/D28)</f>
         <v/>
+      </c>
+      <c r="O28" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="P28" t="n">
+        <v>39.9</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="32">
@@ -9620,12 +10509,24 @@
           <t>AFC</t>
         </is>
       </c>
-      <c r="D29" s="24" t="n"/>
-      <c r="E29" s="24" t="n"/>
-      <c r="F29" s="24" t="n"/>
-      <c r="G29" s="24" t="n"/>
-      <c r="H29" s="24" t="n"/>
-      <c r="I29" s="24" t="n"/>
+      <c r="D29" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="F29" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="I29" s="24" t="n">
+        <v>4</v>
+      </c>
       <c r="J29" s="7">
         <f>IF(COUNT(D29:G29)=0,"",3*E29+F29)</f>
         <v/>
@@ -9645,6 +10546,12 @@
       <c r="N29" s="9">
         <f>IF(N(D29)=0,"",I29/D29)</f>
         <v/>
+      </c>
+      <c r="O29" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="P29" t="n">
+        <v>41.6</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="32">
@@ -9661,12 +10568,24 @@
           <t>OFC</t>
         </is>
       </c>
-      <c r="D30" s="24" t="n"/>
-      <c r="E30" s="24" t="n"/>
-      <c r="F30" s="24" t="n"/>
-      <c r="G30" s="24" t="n"/>
-      <c r="H30" s="24" t="n"/>
-      <c r="I30" s="24" t="n"/>
+      <c r="D30" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E30" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="F30" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="I30" s="24" t="n">
+        <v>3</v>
+      </c>
       <c r="J30" s="7">
         <f>IF(COUNT(D30:G30)=0,"",3*E30+F30)</f>
         <v/>
@@ -9686,6 +10605,12 @@
       <c r="N30" s="9">
         <f>IF(N(D30)=0,"",I30/D30)</f>
         <v/>
+      </c>
+      <c r="O30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P30" t="n">
+        <v>18.3</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="32">
@@ -9702,12 +10627,24 @@
           <t>UEFA</t>
         </is>
       </c>
-      <c r="D31" s="24" t="n"/>
-      <c r="E31" s="24" t="n"/>
-      <c r="F31" s="24" t="n"/>
-      <c r="G31" s="24" t="n"/>
-      <c r="H31" s="24" t="n"/>
-      <c r="I31" s="24" t="n"/>
+      <c r="D31" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E31" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="F31" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="24" t="n">
+        <v>21</v>
+      </c>
+      <c r="I31" s="24" t="n">
+        <v>4</v>
+      </c>
       <c r="J31" s="7">
         <f>IF(COUNT(D31:G31)=0,"",3*E31+F31)</f>
         <v/>
@@ -9727,6 +10664,12 @@
       <c r="N31" s="9">
         <f>IF(N(D31)=0,"",I31/D31)</f>
         <v/>
+      </c>
+      <c r="O31" t="n">
+        <v>1</v>
+      </c>
+      <c r="P31" t="n">
+        <v>91.7</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="32">
@@ -9743,12 +10686,24 @@
           <t>CAF</t>
         </is>
       </c>
-      <c r="D32" s="24" t="n"/>
-      <c r="E32" s="24" t="n"/>
-      <c r="F32" s="24" t="n"/>
-      <c r="G32" s="24" t="n"/>
-      <c r="H32" s="24" t="n"/>
-      <c r="I32" s="24" t="n"/>
+      <c r="D32" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F32" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="H32" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="I32" s="24" t="n">
+        <v>9</v>
+      </c>
       <c r="J32" s="7">
         <f>IF(COUNT(D32:G32)=0,"",3*E32+F32)</f>
         <v/>
@@ -9768,6 +10723,12 @@
       <c r="N32" s="9">
         <f>IF(N(D32)=0,"",I32/D32)</f>
         <v/>
+      </c>
+      <c r="O32" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="P32" t="n">
+        <v>32.9</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="32">
@@ -9784,12 +10745,24 @@
           <t>AFC</t>
         </is>
       </c>
-      <c r="D33" s="24" t="n"/>
-      <c r="E33" s="24" t="n"/>
-      <c r="F33" s="24" t="n"/>
-      <c r="G33" s="24" t="n"/>
-      <c r="H33" s="24" t="n"/>
-      <c r="I33" s="24" t="n"/>
+      <c r="D33" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="E33" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="G33" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="H33" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="I33" s="24" t="n">
+        <v>8</v>
+      </c>
       <c r="J33" s="7">
         <f>IF(COUNT(D33:G33)=0,"",3*E33+F33)</f>
         <v/>
@@ -9809,6 +10782,12 @@
       <c r="N33" s="9">
         <f>IF(N(D33)=0,"",I33/D33)</f>
         <v/>
+      </c>
+      <c r="O33" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="P33" t="n">
+        <v>25.3</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="32">
@@ -9825,12 +10804,24 @@
           <t>CONMEBOL</t>
         </is>
       </c>
-      <c r="D34" s="24" t="n"/>
-      <c r="E34" s="24" t="n"/>
-      <c r="F34" s="24" t="n"/>
-      <c r="G34" s="24" t="n"/>
-      <c r="H34" s="24" t="n"/>
-      <c r="I34" s="24" t="n"/>
+      <c r="D34" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="E34" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="F34" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="G34" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="H34" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="I34" s="24" t="n">
+        <v>16</v>
+      </c>
       <c r="J34" s="7">
         <f>IF(COUNT(D34:G34)=0,"",3*E34+F34)</f>
         <v/>
@@ -9850,6 +10841,12 @@
       <c r="N34" s="9">
         <f>IF(N(D34)=0,"",I34/D34)</f>
         <v/>
+      </c>
+      <c r="O34" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="P34" t="n">
+        <v>49.3</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="32">
@@ -9866,12 +10863,24 @@
           <t>UEFA</t>
         </is>
       </c>
-      <c r="D35" s="24" t="n"/>
-      <c r="E35" s="24" t="n"/>
-      <c r="F35" s="24" t="n"/>
-      <c r="G35" s="24" t="n"/>
-      <c r="H35" s="24" t="n"/>
-      <c r="I35" s="24" t="n"/>
+      <c r="D35" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E35" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="F35" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="I35" s="24" t="n">
+        <v>5</v>
+      </c>
       <c r="J35" s="7">
         <f>IF(COUNT(D35:G35)=0,"",3*E35+F35)</f>
         <v/>
@@ -9891,6 +10900,12 @@
       <c r="N35" s="9">
         <f>IF(N(D35)=0,"",I35/D35)</f>
         <v/>
+      </c>
+      <c r="O35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P35" t="n">
+        <v>91.7</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="32">
@@ -9907,12 +10922,24 @@
           <t>CAF</t>
         </is>
       </c>
-      <c r="D36" s="24" t="n"/>
-      <c r="E36" s="24" t="n"/>
-      <c r="F36" s="24" t="n"/>
-      <c r="G36" s="24" t="n"/>
-      <c r="H36" s="24" t="n"/>
-      <c r="I36" s="24" t="n"/>
+      <c r="D36" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F36" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G36" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="I36" s="24" t="n">
+        <v>6</v>
+      </c>
       <c r="J36" s="7">
         <f>IF(COUNT(D36:G36)=0,"",3*E36+F36)</f>
         <v/>
@@ -9932,6 +10959,12 @@
       <c r="N36" s="9">
         <f>IF(N(D36)=0,"",I36/D36)</f>
         <v/>
+      </c>
+      <c r="O36" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="P36" t="n">
+        <v>36.4</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="32">
@@ -9948,12 +10981,24 @@
           <t>AFC</t>
         </is>
       </c>
-      <c r="D37" s="24" t="n"/>
-      <c r="E37" s="24" t="n"/>
-      <c r="F37" s="24" t="n"/>
-      <c r="G37" s="24" t="n"/>
-      <c r="H37" s="24" t="n"/>
-      <c r="I37" s="24" t="n"/>
+      <c r="D37" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="E37" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="G37" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="H37" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="I37" s="24" t="n">
+        <v>10</v>
+      </c>
       <c r="J37" s="7">
         <f>IF(COUNT(D37:G37)=0,"",3*E37+F37)</f>
         <v/>
@@ -9973,6 +11018,12 @@
       <c r="N37" s="9">
         <f>IF(N(D37)=0,"",I37/D37)</f>
         <v/>
+      </c>
+      <c r="O37" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="P37" t="n">
+        <v>25.3</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="32">
@@ -9989,12 +11040,24 @@
           <t>UEFA</t>
         </is>
       </c>
-      <c r="D38" s="24" t="n"/>
-      <c r="E38" s="24" t="n"/>
-      <c r="F38" s="24" t="n"/>
-      <c r="G38" s="24" t="n"/>
-      <c r="H38" s="24" t="n"/>
-      <c r="I38" s="24" t="n"/>
+      <c r="D38" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E38" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="F38" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="24" t="n">
+        <v>28</v>
+      </c>
+      <c r="I38" s="24" t="n">
+        <v>5</v>
+      </c>
       <c r="J38" s="7">
         <f>IF(COUNT(D38:G38)=0,"",3*E38+F38)</f>
         <v/>
@@ -10014,6 +11077,12 @@
       <c r="N38" s="9">
         <f>IF(N(D38)=0,"",I38/D38)</f>
         <v/>
+      </c>
+      <c r="O38" t="n">
+        <v>1</v>
+      </c>
+      <c r="P38" t="n">
+        <v>91.7</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="32">
@@ -10030,12 +11099,24 @@
           <t>CONMEBOL</t>
         </is>
       </c>
-      <c r="D39" s="24" t="n"/>
-      <c r="E39" s="24" t="n"/>
-      <c r="F39" s="24" t="n"/>
-      <c r="G39" s="24" t="n"/>
-      <c r="H39" s="24" t="n"/>
-      <c r="I39" s="24" t="n"/>
+      <c r="D39" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="E39" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F39" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="H39" s="24" t="n">
+        <v>31</v>
+      </c>
+      <c r="I39" s="24" t="n">
+        <v>14</v>
+      </c>
       <c r="J39" s="7">
         <f>IF(COUNT(D39:G39)=0,"",3*E39+F39)</f>
         <v/>
@@ -10055,6 +11136,12 @@
       <c r="N39" s="9">
         <f>IF(N(D39)=0,"",I39/D39)</f>
         <v/>
+      </c>
+      <c r="O39" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="P39" t="n">
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="32">
@@ -10071,12 +11158,24 @@
           <t>CAF</t>
         </is>
       </c>
-      <c r="D40" s="24" t="n"/>
-      <c r="E40" s="24" t="n"/>
-      <c r="F40" s="24" t="n"/>
-      <c r="G40" s="24" t="n"/>
-      <c r="H40" s="24" t="n"/>
-      <c r="I40" s="24" t="n"/>
+      <c r="D40" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="F40" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="I40" s="24" t="n">
+        <v>8</v>
+      </c>
       <c r="J40" s="7">
         <f>IF(COUNT(D40:G40)=0,"",3*E40+F40)</f>
         <v/>
@@ -10096,6 +11195,12 @@
       <c r="N40" s="9">
         <f>IF(N(D40)=0,"",I40/D40)</f>
         <v/>
+      </c>
+      <c r="O40" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="P40" t="n">
+        <v>38.1</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="32">
@@ -10112,12 +11217,24 @@
           <t>UEFA</t>
         </is>
       </c>
-      <c r="D41" s="24" t="n"/>
-      <c r="E41" s="24" t="n"/>
-      <c r="F41" s="24" t="n"/>
-      <c r="G41" s="24" t="n"/>
-      <c r="H41" s="24" t="n"/>
-      <c r="I41" s="24" t="n"/>
+      <c r="D41" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E41" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="F41" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="I41" s="24" t="n">
+        <v>6</v>
+      </c>
       <c r="J41" s="7">
         <f>IF(COUNT(D41:G41)=0,"",3*E41+F41)</f>
         <v/>
@@ -10137,6 +11254,12 @@
       <c r="N41" s="9">
         <f>IF(N(D41)=0,"",I41/D41)</f>
         <v/>
+      </c>
+      <c r="O41" t="n">
+        <v>1</v>
+      </c>
+      <c r="P41" t="n">
+        <v>87.5</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="32">
@@ -10153,12 +11276,24 @@
           <t>AFC</t>
         </is>
       </c>
-      <c r="D42" s="24" t="n"/>
-      <c r="E42" s="24" t="n"/>
-      <c r="F42" s="24" t="n"/>
-      <c r="G42" s="24" t="n"/>
-      <c r="H42" s="24" t="n"/>
-      <c r="I42" s="24" t="n"/>
+      <c r="D42" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F42" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G42" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="I42" s="24" t="n">
+        <v>7</v>
+      </c>
       <c r="J42" s="7">
         <f>IF(COUNT(D42:G42)=0,"",3*E42+F42)</f>
         <v/>
@@ -10178,6 +11313,12 @@
       <c r="N42" s="9">
         <f>IF(N(D42)=0,"",I42/D42)</f>
         <v/>
+      </c>
+      <c r="O42" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="P42" t="n">
+        <v>33.6</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="32">
@@ -10194,12 +11335,24 @@
           <t>UEFA</t>
         </is>
       </c>
-      <c r="D43" s="24" t="n"/>
-      <c r="E43" s="24" t="n"/>
-      <c r="F43" s="24" t="n"/>
-      <c r="G43" s="24" t="n"/>
-      <c r="H43" s="24" t="n"/>
-      <c r="I43" s="24" t="n"/>
+      <c r="D43" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E43" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F43" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="I43" s="24" t="n">
+        <v>6</v>
+      </c>
       <c r="J43" s="7">
         <f>IF(COUNT(D43:G43)=0,"",3*E43+F43)</f>
         <v/>
@@ -10219,6 +11372,12 @@
       <c r="N43" s="9">
         <f>IF(N(D43)=0,"",I43/D43)</f>
         <v/>
+      </c>
+      <c r="O43" t="n">
+        <v>1</v>
+      </c>
+      <c r="P43" t="n">
+        <v>83.3</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="32">
@@ -10235,12 +11394,24 @@
           <t>CAF</t>
         </is>
       </c>
-      <c r="D44" s="24" t="n"/>
-      <c r="E44" s="24" t="n"/>
-      <c r="F44" s="24" t="n"/>
-      <c r="G44" s="24" t="n"/>
-      <c r="H44" s="24" t="n"/>
-      <c r="I44" s="24" t="n"/>
+      <c r="D44" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F44" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G44" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="I44" s="24" t="n">
+        <v>9</v>
+      </c>
       <c r="J44" s="7">
         <f>IF(COUNT(D44:G44)=0,"",3*E44+F44)</f>
         <v/>
@@ -10260,6 +11431,12 @@
       <c r="N44" s="9">
         <f>IF(N(D44)=0,"",I44/D44)</f>
         <v/>
+      </c>
+      <c r="O44" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="P44" t="n">
+        <v>31.2</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="32">
@@ -10276,12 +11453,24 @@
           <t>AFC</t>
         </is>
       </c>
-      <c r="D45" s="24" t="n"/>
-      <c r="E45" s="24" t="n"/>
-      <c r="F45" s="24" t="n"/>
-      <c r="G45" s="24" t="n"/>
-      <c r="H45" s="24" t="n"/>
-      <c r="I45" s="24" t="n"/>
+      <c r="D45" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F45" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G45" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="I45" s="24" t="n">
+        <v>6</v>
+      </c>
       <c r="J45" s="7">
         <f>IF(COUNT(D45:G45)=0,"",3*E45+F45)</f>
         <v/>
@@ -10301,6 +11490,12 @@
       <c r="N45" s="9">
         <f>IF(N(D45)=0,"",I45/D45)</f>
         <v/>
+      </c>
+      <c r="O45" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="P45" t="n">
+        <v>33.6</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="32">
@@ -10317,12 +11512,24 @@
           <t>CONMEBOL</t>
         </is>
       </c>
-      <c r="D46" s="24" t="n"/>
-      <c r="E46" s="24" t="n"/>
-      <c r="F46" s="24" t="n"/>
-      <c r="G46" s="24" t="n"/>
-      <c r="H46" s="24" t="n"/>
-      <c r="I46" s="24" t="n"/>
+      <c r="D46" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="E46" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="F46" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="G46" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="H46" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="I46" s="24" t="n">
+        <v>18</v>
+      </c>
       <c r="J46" s="7">
         <f>IF(COUNT(D46:G46)=0,"",3*E46+F46)</f>
         <v/>
@@ -10342,6 +11549,12 @@
       <c r="N46" s="9">
         <f>IF(N(D46)=0,"",I46/D46)</f>
         <v/>
+      </c>
+      <c r="O46" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="P46" t="n">
+        <v>49.3</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="32">
@@ -10358,12 +11571,24 @@
           <t>UEFA</t>
         </is>
       </c>
-      <c r="D47" s="24" t="n"/>
-      <c r="E47" s="24" t="n"/>
-      <c r="F47" s="24" t="n"/>
-      <c r="G47" s="24" t="n"/>
-      <c r="H47" s="24" t="n"/>
-      <c r="I47" s="24" t="n"/>
+      <c r="D47" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E47" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="F47" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="I47" s="24" t="n">
+        <v>3</v>
+      </c>
       <c r="J47" s="7">
         <f>IF(COUNT(D47:G47)=0,"",3*E47+F47)</f>
         <v/>
@@ -10383,6 +11608,12 @@
       <c r="N47" s="9">
         <f>IF(N(D47)=0,"",I47/D47)</f>
         <v/>
+      </c>
+      <c r="O47" t="n">
+        <v>1</v>
+      </c>
+      <c r="P47" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="32">
@@ -10399,12 +11630,24 @@
           <t>UEFA</t>
         </is>
       </c>
-      <c r="D48" s="24" t="n"/>
-      <c r="E48" s="24" t="n"/>
-      <c r="F48" s="24" t="n"/>
-      <c r="G48" s="24" t="n"/>
-      <c r="H48" s="24" t="n"/>
-      <c r="I48" s="24" t="n"/>
+      <c r="D48" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E48" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="F48" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="I48" s="24" t="n">
+        <v>5</v>
+      </c>
       <c r="J48" s="7">
         <f>IF(COUNT(D48:G48)=0,"",3*E48+F48)</f>
         <v/>
@@ -10424,6 +11667,12 @@
       <c r="N48" s="9">
         <f>IF(N(D48)=0,"",I48/D48)</f>
         <v/>
+      </c>
+      <c r="O48" t="n">
+        <v>1</v>
+      </c>
+      <c r="P48" t="n">
+        <v>91.7</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="32">
@@ -10440,12 +11689,24 @@
           <t>CAF</t>
         </is>
       </c>
-      <c r="D49" s="24" t="n"/>
-      <c r="E49" s="24" t="n"/>
-      <c r="F49" s="24" t="n"/>
-      <c r="G49" s="24" t="n"/>
-      <c r="H49" s="24" t="n"/>
-      <c r="I49" s="24" t="n"/>
+      <c r="D49" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F49" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="H49" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="I49" s="24" t="n">
+        <v>10</v>
+      </c>
       <c r="J49" s="7">
         <f>IF(COUNT(D49:G49)=0,"",3*E49+F49)</f>
         <v/>
@@ -10465,6 +11726,12 @@
       <c r="N49" s="9">
         <f>IF(N(D49)=0,"",I49/D49)</f>
         <v/>
+      </c>
+      <c r="O49" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="P49" t="n">
+        <v>32.9</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="32">
@@ -10481,12 +11748,24 @@
           <t>CONCACAF</t>
         </is>
       </c>
-      <c r="D50" s="24" t="n"/>
-      <c r="E50" s="24" t="n"/>
-      <c r="F50" s="24" t="n"/>
-      <c r="G50" s="24" t="n"/>
-      <c r="H50" s="24" t="n"/>
-      <c r="I50" s="24" t="n"/>
+      <c r="D50" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F50" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G50" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H50" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="I50" s="24" t="n">
+        <v>9</v>
+      </c>
       <c r="J50" s="7">
         <f>IF(COUNT(D50:G50)=0,"",3*E50+F50)</f>
         <v/>
@@ -10506,6 +11785,12 @@
       <c r="N50" s="9">
         <f>IF(N(D50)=0,"",I50/D50)</f>
         <v/>
+      </c>
+      <c r="O50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P50" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="32">
@@ -10628,7 +11913,9 @@
       <c r="H3" s="24" t="n">
         <v>27.5</v>
       </c>
-      <c r="I3" s="24" t="n"/>
+      <c r="I3" s="24" t="n">
+        <v>6</v>
+      </c>
       <c r="J3" s="24" t="n">
         <v>2026</v>
       </c>
@@ -10656,7 +11943,9 @@
       <c r="H4" s="24" t="n">
         <v>26.35</v>
       </c>
-      <c r="I4" s="24" t="n"/>
+      <c r="I4" s="24" t="n">
+        <v>4</v>
+      </c>
       <c r="J4" s="24" t="n">
         <v>2026</v>
       </c>
@@ -10684,7 +11973,9 @@
       <c r="H5" s="24" t="n">
         <v>27.46</v>
       </c>
-      <c r="I5" s="24" t="n"/>
+      <c r="I5" s="24" t="n">
+        <v>8</v>
+      </c>
       <c r="J5" s="24" t="n">
         <v>2026</v>
       </c>
@@ -10712,7 +12003,9 @@
       <c r="H6" s="24" t="n">
         <v>27.23</v>
       </c>
-      <c r="I6" s="24" t="n"/>
+      <c r="I6" s="24" t="n">
+        <v>9</v>
+      </c>
       <c r="J6" s="24" t="n">
         <v>2026</v>
       </c>
@@ -10740,7 +12033,9 @@
       <c r="H7" s="24" t="n">
         <v>26.42</v>
       </c>
-      <c r="I7" s="24" t="n"/>
+      <c r="I7" s="24" t="n">
+        <v>12</v>
+      </c>
       <c r="J7" s="24" t="n">
         <v>2026</v>
       </c>
@@ -10768,7 +12063,9 @@
       <c r="H8" s="24" t="n">
         <v>25.92</v>
       </c>
-      <c r="I8" s="24" t="n"/>
+      <c r="I8" s="24" t="n">
+        <v>13</v>
+      </c>
       <c r="J8" s="24" t="n">
         <v>2026</v>
       </c>
@@ -10796,7 +12093,9 @@
       <c r="H9" s="24" t="n">
         <v>28.92</v>
       </c>
-      <c r="I9" s="24" t="n"/>
+      <c r="I9" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="J9" s="24" t="n">
         <v>2026</v>
       </c>
@@ -10824,7 +12123,9 @@
       <c r="H10" s="24" t="n">
         <v>27.81</v>
       </c>
-      <c r="I10" s="24" t="n"/>
+      <c r="I10" s="24" t="n">
+        <v>17</v>
+      </c>
       <c r="J10" s="24" t="n">
         <v>2026</v>
       </c>
@@ -10852,7 +12153,9 @@
       <c r="H11" s="24" t="n">
         <v>28.65</v>
       </c>
-      <c r="I11" s="24" t="n"/>
+      <c r="I11" s="24" t="n">
+        <v>21</v>
+      </c>
       <c r="J11" s="24" t="n">
         <v>2026</v>
       </c>
@@ -10880,7 +12183,9 @@
       <c r="H12" s="24" t="n">
         <v>25.92</v>
       </c>
-      <c r="I12" s="24" t="n"/>
+      <c r="I12" s="24" t="n">
+        <v>19</v>
+      </c>
       <c r="J12" s="24" t="n">
         <v>2026</v>
       </c>
@@ -10908,7 +12213,9 @@
       <c r="H13" s="24" t="n">
         <v>27.08</v>
       </c>
-      <c r="I13" s="24" t="n"/>
+      <c r="I13" s="24" t="n">
+        <v>6</v>
+      </c>
       <c r="J13" s="24" t="n">
         <v>2026</v>
       </c>
@@ -10936,7 +12243,9 @@
       <c r="H14" s="24" t="n">
         <v>28.73</v>
       </c>
-      <c r="I14" s="24" t="n"/>
+      <c r="I14" s="24" t="n">
+        <v>13</v>
+      </c>
       <c r="J14" s="24" t="n">
         <v>2026</v>
       </c>
@@ -10964,7 +12273,9 @@
       <c r="H15" s="24" t="n">
         <v>26.42</v>
       </c>
-      <c r="I15" s="24" t="n"/>
+      <c r="I15" s="24" t="n">
+        <v>12</v>
+      </c>
       <c r="J15" s="24" t="n">
         <v>2026</v>
       </c>
@@ -10992,7 +12303,9 @@
       <c r="H16" s="24" t="n">
         <v>28.54</v>
       </c>
-      <c r="I16" s="24" t="n"/>
+      <c r="I16" s="24" t="n">
+        <v>8</v>
+      </c>
       <c r="J16" s="24" t="n">
         <v>2026</v>
       </c>
@@ -11020,7 +12333,9 @@
       <c r="H17" s="24" t="n">
         <v>26.88</v>
       </c>
-      <c r="I17" s="24" t="n"/>
+      <c r="I17" s="24" t="n">
+        <v>6</v>
+      </c>
       <c r="J17" s="24" t="n">
         <v>2026</v>
       </c>
@@ -11048,7 +12363,9 @@
       <c r="H18" s="24" t="n">
         <v>27.23</v>
       </c>
-      <c r="I18" s="24" t="n"/>
+      <c r="I18" s="24" t="n">
+        <v>12</v>
+      </c>
       <c r="J18" s="24" t="n">
         <v>2026</v>
       </c>
@@ -11076,7 +12393,9 @@
       <c r="H19" s="24" t="n">
         <v>27.54</v>
       </c>
-      <c r="I19" s="24" t="n"/>
+      <c r="I19" s="24" t="n">
+        <v>24</v>
+      </c>
       <c r="J19" s="24" t="n">
         <v>2026</v>
       </c>
@@ -11104,7 +12423,9 @@
       <c r="H20" s="24" t="n">
         <v>27.54</v>
       </c>
-      <c r="I20" s="24" t="n"/>
+      <c r="I20" s="24" t="n">
+        <v>7</v>
+      </c>
       <c r="J20" s="24" t="n">
         <v>2026</v>
       </c>
@@ -11132,7 +12453,9 @@
       <c r="H21" s="24" t="n">
         <v>25.35</v>
       </c>
-      <c r="I21" s="24" t="n"/>
+      <c r="I21" s="24" t="n">
+        <v>17</v>
+      </c>
       <c r="J21" s="24" t="n">
         <v>2026</v>
       </c>
@@ -11160,7 +12483,9 @@
       <c r="H22" s="24" t="n">
         <v>25.58</v>
       </c>
-      <c r="I22" s="24" t="n"/>
+      <c r="I22" s="24" t="n">
+        <v>12</v>
+      </c>
       <c r="J22" s="24" t="n">
         <v>2026</v>
       </c>
@@ -11188,7 +12513,9 @@
       <c r="H23" s="24" t="n">
         <v>27.27</v>
       </c>
-      <c r="I23" s="24" t="n"/>
+      <c r="I23" s="24" t="n">
+        <v>22</v>
+      </c>
       <c r="J23" s="24" t="n">
         <v>2026</v>
       </c>
@@ -11216,7 +12543,9 @@
       <c r="H24" s="24" t="n">
         <v>27.19</v>
       </c>
-      <c r="I24" s="24" t="n"/>
+      <c r="I24" s="24" t="n">
+        <v>13</v>
+      </c>
       <c r="J24" s="24" t="n">
         <v>2026</v>
       </c>
@@ -11244,7 +12573,9 @@
       <c r="H25" s="24" t="n">
         <v>27</v>
       </c>
-      <c r="I25" s="24" t="n"/>
+      <c r="I25" s="24" t="n">
+        <v>13</v>
+      </c>
       <c r="J25" s="24" t="n">
         <v>2026</v>
       </c>
@@ -11272,7 +12603,9 @@
       <c r="H26" s="24" t="n">
         <v>26.15</v>
       </c>
-      <c r="I26" s="24" t="n"/>
+      <c r="I26" s="24" t="n">
+        <v>9</v>
+      </c>
       <c r="J26" s="24" t="n">
         <v>2026</v>
       </c>
@@ -11300,7 +12633,9 @@
       <c r="H27" s="24" t="n">
         <v>27.12</v>
       </c>
-      <c r="I27" s="24" t="n"/>
+      <c r="I27" s="24" t="n">
+        <v>20</v>
+      </c>
       <c r="J27" s="24" t="n">
         <v>2026</v>
       </c>
@@ -11328,7 +12663,9 @@
       <c r="H28" s="24" t="n">
         <v>28.69</v>
       </c>
-      <c r="I28" s="24" t="n"/>
+      <c r="I28" s="24" t="n">
+        <v>6</v>
+      </c>
       <c r="J28" s="24" t="n">
         <v>2026</v>
       </c>
@@ -11356,7 +12693,9 @@
       <c r="H29" s="24" t="n">
         <v>29.81</v>
       </c>
-      <c r="I29" s="24" t="n"/>
+      <c r="I29" s="24" t="n">
+        <v>5</v>
+      </c>
       <c r="J29" s="24" t="n">
         <v>2026</v>
       </c>
@@ -11384,7 +12723,9 @@
       <c r="H30" s="24" t="n">
         <v>27.62</v>
       </c>
-      <c r="I30" s="24" t="n"/>
+      <c r="I30" s="24" t="n">
+        <v>4</v>
+      </c>
       <c r="J30" s="24" t="n">
         <v>2026</v>
       </c>
@@ -11412,7 +12753,9 @@
       <c r="H31" s="24" t="n">
         <v>26.19</v>
       </c>
-      <c r="I31" s="24" t="n"/>
+      <c r="I31" s="24" t="n">
+        <v>24</v>
+      </c>
       <c r="J31" s="24" t="n">
         <v>2026</v>
       </c>
@@ -11440,7 +12783,9 @@
       <c r="H32" s="24" t="n">
         <v>29.23</v>
       </c>
-      <c r="I32" s="24" t="n"/>
+      <c r="I32" s="24" t="n">
+        <v>8</v>
+      </c>
       <c r="J32" s="24" t="n">
         <v>2026</v>
       </c>
@@ -11468,7 +12813,9 @@
       <c r="H33" s="24" t="n">
         <v>27.96</v>
       </c>
-      <c r="I33" s="24" t="n"/>
+      <c r="I33" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="J33" s="24" t="n">
         <v>2026</v>
       </c>
@@ -11496,7 +12843,9 @@
       <c r="H34" s="24" t="n">
         <v>28.19</v>
       </c>
-      <c r="I34" s="24" t="n"/>
+      <c r="I34" s="24" t="n">
+        <v>16</v>
+      </c>
       <c r="J34" s="24" t="n">
         <v>2026</v>
       </c>
@@ -11524,7 +12873,9 @@
       <c r="H35" s="24" t="n">
         <v>26.58</v>
       </c>
-      <c r="I35" s="24" t="n"/>
+      <c r="I35" s="24" t="n">
+        <v>25</v>
+      </c>
       <c r="J35" s="24" t="n">
         <v>2026</v>
       </c>
@@ -11552,7 +12903,9 @@
       <c r="H36" s="24" t="n">
         <v>26.62</v>
       </c>
-      <c r="I36" s="24" t="n"/>
+      <c r="I36" s="24" t="n">
+        <v>19</v>
+      </c>
       <c r="J36" s="24" t="n">
         <v>2026</v>
       </c>
@@ -11580,7 +12933,9 @@
       <c r="H37" s="24" t="n">
         <v>26.65</v>
       </c>
-      <c r="I37" s="24" t="n"/>
+      <c r="I37" s="24" t="n">
+        <v>2</v>
+      </c>
       <c r="J37" s="24" t="n">
         <v>2026</v>
       </c>
@@ -11608,7 +12963,9 @@
       <c r="H38" s="24" t="n">
         <v>26.35</v>
       </c>
-      <c r="I38" s="24" t="n"/>
+      <c r="I38" s="24" t="n">
+        <v>15</v>
+      </c>
       <c r="J38" s="24" t="n">
         <v>2026</v>
       </c>
@@ -11636,7 +12993,9 @@
       <c r="H39" s="24" t="n">
         <v>28.62</v>
       </c>
-      <c r="I39" s="24" t="n"/>
+      <c r="I39" s="24" t="n">
+        <v>20</v>
+      </c>
       <c r="J39" s="24" t="n">
         <v>2026</v>
       </c>
@@ -11664,7 +13023,9 @@
       <c r="H40" s="24" t="n">
         <v>26.46</v>
       </c>
-      <c r="I40" s="24" t="n"/>
+      <c r="I40" s="24" t="n">
+        <v>17</v>
+      </c>
       <c r="J40" s="24" t="n">
         <v>2026</v>
       </c>
@@ -11692,7 +13053,9 @@
       <c r="H41" s="24" t="n">
         <v>28.12</v>
       </c>
-      <c r="I41" s="24" t="n"/>
+      <c r="I41" s="24" t="n">
+        <v>17</v>
+      </c>
       <c r="J41" s="24" t="n">
         <v>2026</v>
       </c>
@@ -11720,7 +13083,9 @@
       <c r="H42" s="24" t="n">
         <v>28.08</v>
       </c>
-      <c r="I42" s="24" t="n"/>
+      <c r="I42" s="24" t="n">
+        <v>1</v>
+      </c>
       <c r="J42" s="24" t="n">
         <v>2026</v>
       </c>
@@ -11748,7 +13113,9 @@
       <c r="H43" s="24" t="n">
         <v>27.54</v>
       </c>
-      <c r="I43" s="24" t="n"/>
+      <c r="I43" s="24" t="n">
+        <v>22</v>
+      </c>
       <c r="J43" s="24" t="n">
         <v>2026</v>
       </c>
@@ -11776,7 +13143,9 @@
       <c r="H44" s="24" t="n">
         <v>28.5</v>
       </c>
-      <c r="I44" s="24" t="n"/>
+      <c r="I44" s="24" t="n">
+        <v>13</v>
+      </c>
       <c r="J44" s="24" t="n">
         <v>2026</v>
       </c>
@@ -11804,7 +13173,9 @@
       <c r="H45" s="24" t="n">
         <v>27.96</v>
       </c>
-      <c r="I45" s="24" t="n"/>
+      <c r="I45" s="24" t="n">
+        <v>2</v>
+      </c>
       <c r="J45" s="24" t="n">
         <v>2026</v>
       </c>
@@ -11832,7 +13203,9 @@
       <c r="H46" s="24" t="n">
         <v>29.58</v>
       </c>
-      <c r="I46" s="24" t="n"/>
+      <c r="I46" s="24" t="n">
+        <v>15</v>
+      </c>
       <c r="J46" s="24" t="n">
         <v>2026</v>
       </c>
@@ -11860,7 +13233,9 @@
       <c r="H47" s="24" t="n">
         <v>26.62</v>
       </c>
-      <c r="I47" s="24" t="n"/>
+      <c r="I47" s="24" t="n">
+        <v>26</v>
+      </c>
       <c r="J47" s="24" t="n">
         <v>2026</v>
       </c>
@@ -11888,7 +13263,9 @@
       <c r="H48" s="24" t="n">
         <v>27.88</v>
       </c>
-      <c r="I48" s="24" t="n"/>
+      <c r="I48" s="24" t="n">
+        <v>19</v>
+      </c>
       <c r="J48" s="24" t="n">
         <v>2026</v>
       </c>
@@ -11916,7 +13293,9 @@
       <c r="H49" s="24" t="n">
         <v>26.42</v>
       </c>
-      <c r="I49" s="24" t="n"/>
+      <c r="I49" s="24" t="n">
+        <v>15</v>
+      </c>
       <c r="J49" s="24" t="n">
         <v>2026</v>
       </c>
@@ -11944,7 +13323,9 @@
       <c r="H50" s="24" t="n">
         <v>30</v>
       </c>
-      <c r="I50" s="24" t="n"/>
+      <c r="I50" s="24" t="n">
+        <v>3</v>
+      </c>
       <c r="J50" s="24" t="n">
         <v>2026</v>
       </c>
@@ -17572,17 +18953,15 @@
       <c r="B3" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="28" t="inlineStr">
-        <is>
-          <t>Sudáfrica</t>
-        </is>
+      <c r="C3" s="28">
+        <f>INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="A")*(Posiciones!$L$3:$L$50=2)*ROW(Posiciones!$A$3:$A$50))-2)</f>
+        <v/>
       </c>
       <c r="D3" s="24" t="n"/>
       <c r="E3" s="24" t="n"/>
-      <c r="F3" s="28" t="inlineStr">
-        <is>
-          <t>Canadá</t>
-        </is>
+      <c r="F3" s="28">
+        <f>INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="B")*(Posiciones!$L$3:$L$50=2)*ROW(Posiciones!$A$3:$A$50))-2)</f>
+        <v/>
       </c>
       <c r="G3" s="28" t="inlineStr">
         <is>
@@ -17609,17 +18988,15 @@
       <c r="B4" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="28" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
+      <c r="C4" s="28">
+        <f>INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="C")*(Posiciones!$L$3:$L$50=1)*ROW(Posiciones!$A$3:$A$50))-2)</f>
+        <v/>
       </c>
       <c r="D4" s="24" t="n"/>
       <c r="E4" s="24" t="n"/>
-      <c r="F4" s="28" t="inlineStr">
-        <is>
-          <t>Japón</t>
-        </is>
+      <c r="F4" s="28">
+        <f>INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="F")*(Posiciones!$L$3:$L$50=2)*ROW(Posiciones!$A$3:$A$50))-2)</f>
+        <v/>
       </c>
       <c r="G4" s="28" t="inlineStr">
         <is>
@@ -17646,10 +19023,9 @@
       <c r="B5" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="28" t="inlineStr">
-        <is>
-          <t>Alemania</t>
-        </is>
+      <c r="C5" s="28">
+        <f>INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="E")*(Posiciones!$L$3:$L$50=1)*ROW(Posiciones!$A$3:$A$50))-2)</f>
+        <v/>
       </c>
       <c r="D5" s="24" t="n"/>
       <c r="E5" s="24" t="n"/>
@@ -17683,17 +19059,15 @@
       <c r="B6" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="28" t="inlineStr">
-        <is>
-          <t>Países Bajos</t>
-        </is>
+      <c r="C6" s="28">
+        <f>INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="F")*(Posiciones!$L$3:$L$50=1)*ROW(Posiciones!$A$3:$A$50))-2)</f>
+        <v/>
       </c>
       <c r="D6" s="24" t="n"/>
       <c r="E6" s="24" t="n"/>
-      <c r="F6" s="28" t="inlineStr">
-        <is>
-          <t>Marruecos</t>
-        </is>
+      <c r="F6" s="28">
+        <f>INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="C")*(Posiciones!$L$3:$L$50=2)*ROW(Posiciones!$A$3:$A$50))-2)</f>
+        <v/>
       </c>
       <c r="G6" s="28" t="inlineStr">
         <is>
@@ -17720,17 +19094,15 @@
       <c r="B7" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="28" t="inlineStr">
-        <is>
-          <t>Costa de Marfil</t>
-        </is>
+      <c r="C7" s="28">
+        <f>INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="E")*(Posiciones!$L$3:$L$50=2)*ROW(Posiciones!$A$3:$A$50))-2)</f>
+        <v/>
       </c>
       <c r="D7" s="24" t="n"/>
       <c r="E7" s="24" t="n"/>
-      <c r="F7" s="28" t="inlineStr">
-        <is>
-          <t>Noruega</t>
-        </is>
+      <c r="F7" s="28">
+        <f>INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="I")*(Posiciones!$L$3:$L$50=2)*ROW(Posiciones!$A$3:$A$50))-2)</f>
+        <v/>
       </c>
       <c r="G7" s="28" t="inlineStr">
         <is>
@@ -17757,10 +19129,9 @@
       <c r="B8" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="28" t="inlineStr">
-        <is>
-          <t>Francia</t>
-        </is>
+      <c r="C8" s="28">
+        <f>INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="I")*(Posiciones!$L$3:$L$50=1)*ROW(Posiciones!$A$3:$A$50))-2)</f>
+        <v/>
       </c>
       <c r="D8" s="24" t="n"/>
       <c r="E8" s="24" t="n"/>
@@ -17794,10 +19165,9 @@
       <c r="B9" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="28" t="inlineStr">
-        <is>
-          <t>México</t>
-        </is>
+      <c r="C9" s="28">
+        <f>INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="A")*(Posiciones!$L$3:$L$50=1)*ROW(Posiciones!$A$3:$A$50))-2)</f>
+        <v/>
       </c>
       <c r="D9" s="24" t="n"/>
       <c r="E9" s="24" t="n"/>
@@ -17831,10 +19201,9 @@
       <c r="B10" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="28" t="inlineStr">
-        <is>
-          <t>Inglaterra</t>
-        </is>
+      <c r="C10" s="28">
+        <f>INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="L")*(Posiciones!$L$3:$L$50=1)*ROW(Posiciones!$A$3:$A$50))-2)</f>
+        <v/>
       </c>
       <c r="D10" s="24" t="n"/>
       <c r="E10" s="24" t="n"/>
@@ -17868,10 +19237,9 @@
       <c r="B11" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="28" t="inlineStr">
-        <is>
-          <t>Nueva Zelanda</t>
-        </is>
+      <c r="C11" s="28">
+        <f>INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="G")*(Posiciones!$L$3:$L$50=1)*ROW(Posiciones!$A$3:$A$50))-2)</f>
+        <v/>
       </c>
       <c r="D11" s="24" t="n"/>
       <c r="E11" s="24" t="n"/>
@@ -17905,10 +19273,9 @@
       <c r="B12" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="28" t="inlineStr">
-        <is>
-          <t>Estados Unidos</t>
-        </is>
+      <c r="C12" s="28">
+        <f>INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="D")*(Posiciones!$L$3:$L$50=1)*ROW(Posiciones!$A$3:$A$50))-2)</f>
+        <v/>
       </c>
       <c r="D12" s="24" t="n"/>
       <c r="E12" s="24" t="n"/>
@@ -17942,17 +19309,15 @@
       <c r="B13" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="28" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
+      <c r="C13" s="28">
+        <f>INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="H")*(Posiciones!$L$3:$L$50=1)*ROW(Posiciones!$A$3:$A$50))-2)</f>
+        <v/>
       </c>
       <c r="D13" s="24" t="n"/>
       <c r="E13" s="24" t="n"/>
-      <c r="F13" s="28" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
+      <c r="F13" s="28">
+        <f>INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="J")*(Posiciones!$L$3:$L$50=2)*ROW(Posiciones!$A$3:$A$50))-2)</f>
+        <v/>
       </c>
       <c r="G13" s="28" t="inlineStr">
         <is>
@@ -17979,17 +19344,15 @@
       <c r="B14" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="28" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
+      <c r="C14" s="28">
+        <f>INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="K")*(Posiciones!$L$3:$L$50=2)*ROW(Posiciones!$A$3:$A$50))-2)</f>
+        <v/>
       </c>
       <c r="D14" s="24" t="n"/>
       <c r="E14" s="24" t="n"/>
-      <c r="F14" s="28" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
+      <c r="F14" s="28">
+        <f>INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="L")*(Posiciones!$L$3:$L$50=2)*ROW(Posiciones!$A$3:$A$50))-2)</f>
+        <v/>
       </c>
       <c r="G14" s="28" t="inlineStr">
         <is>
@@ -18016,10 +19379,9 @@
       <c r="B15" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="28" t="inlineStr">
-        <is>
-          <t>Suiza</t>
-        </is>
+      <c r="C15" s="28">
+        <f>INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="B")*(Posiciones!$L$3:$L$50=1)*ROW(Posiciones!$A$3:$A$50))-2)</f>
+        <v/>
       </c>
       <c r="D15" s="24" t="n"/>
       <c r="E15" s="24" t="n"/>
@@ -18053,17 +19415,15 @@
       <c r="B16" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="28" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
+      <c r="C16" s="28">
+        <f>INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="D")*(Posiciones!$L$3:$L$50=2)*ROW(Posiciones!$A$3:$A$50))-2)</f>
+        <v/>
       </c>
       <c r="D16" s="24" t="n"/>
       <c r="E16" s="24" t="n"/>
-      <c r="F16" s="28" t="inlineStr">
-        <is>
-          <t>Irán</t>
-        </is>
+      <c r="F16" s="28">
+        <f>INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="G")*(Posiciones!$L$3:$L$50=2)*ROW(Posiciones!$A$3:$A$50))-2)</f>
+        <v/>
       </c>
       <c r="G16" s="28" t="inlineStr">
         <is>
@@ -18090,17 +19450,15 @@
       <c r="B17" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="28" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
+      <c r="C17" s="28">
+        <f>INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="J")*(Posiciones!$L$3:$L$50=1)*ROW(Posiciones!$A$3:$A$50))-2)</f>
+        <v/>
       </c>
       <c r="D17" s="24" t="n"/>
       <c r="E17" s="24" t="n"/>
-      <c r="F17" s="28" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
-        </is>
+      <c r="F17" s="28">
+        <f>INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="H")*(Posiciones!$L$3:$L$50=2)*ROW(Posiciones!$A$3:$A$50))-2)</f>
+        <v/>
       </c>
       <c r="G17" s="28" t="inlineStr">
         <is>
@@ -18127,10 +19485,9 @@
       <c r="B18" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="C18" s="28" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
+      <c r="C18" s="28">
+        <f>INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="K")*(Posiciones!$L$3:$L$50=1)*ROW(Posiciones!$A$3:$A$50))-2)</f>
+        <v/>
       </c>
       <c r="D18" s="24" t="n"/>
       <c r="E18" s="24" t="n"/>

--- a/Mundial_2026_fuente_datos.xlsx
+++ b/Mundial_2026_fuente_datos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sriverti\Desktop\INECO\Repositorios\ML_prediccion_mundial2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBFD5D38-9BB6-4D9F-AAEA-CEA727EE8B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4F2819E-5A1D-4CDC-935D-95C9239AEEF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Léeme" sheetId="1" r:id="rId1"/>
@@ -14163,19 +14163,23 @@
       <c r="E37" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="F37" s="24"/>
-      <c r="G37" s="24"/>
+      <c r="F37" s="24">
+        <v>3</v>
+      </c>
+      <c r="G37" s="24">
+        <v>1</v>
+      </c>
       <c r="H37" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I37" s="7" t="str">
+        <v>1</v>
+      </c>
+      <c r="I37" s="7">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J37" s="7" t="str">
+        <v>3</v>
+      </c>
+      <c r="J37" s="7">
         <f t="shared" si="5"/>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14194,19 +14198,23 @@
       <c r="E38" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
+      <c r="F38" s="25">
+        <v>1</v>
+      </c>
+      <c r="G38" s="25">
+        <v>1</v>
+      </c>
       <c r="H38" s="10">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I38" s="10" t="str">
+        <v>1</v>
+      </c>
+      <c r="I38" s="10">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J38" s="10" t="str">
+        <v>1</v>
+      </c>
+      <c r="J38" s="10">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16449,11 +16457,11 @@
       </c>
       <c r="D23" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C23)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C23)*Fixture_Grupos!$H$3:$H$74)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C23)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$F$3:$F$74&gt;Fixture_Grupos!$G$3:$G$74))+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C23)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$G$3:$G$74&gt;Fixture_Grupos!$F$3:$F$74))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C23)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$F$3:$F$74=Fixture_Grupos!$G$3:$G$74))+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C23)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$G$3:$G$74=Fixture_Grupos!$F$3:$F$74))</f>
@@ -16465,19 +16473,19 @@
       </c>
       <c r="H23" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C23)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$F$3:$F$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C23)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$G$3:$G$74)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I23" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C23)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$G$3:$G$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C23)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$F$3:$F$74)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J23" s="10">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K23" s="10">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L23" s="10">
         <f>SUMPRODUCT(--(($K$23:$K$26*1000+$J$23:$J$26*10+$H$23:$H$26)&gt;($K23*1000+$J23*10+$H23)))+1</f>
@@ -16496,7 +16504,7 @@
       </c>
       <c r="D24" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C24)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C24)*Fixture_Grupos!$H$3:$H$74)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C24)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$F$3:$F$74&gt;Fixture_Grupos!$G$3:$G$74))+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C24)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$G$3:$G$74&gt;Fixture_Grupos!$F$3:$F$74))</f>
@@ -16504,7 +16512,7 @@
       </c>
       <c r="F24" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C24)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$F$3:$F$74=Fixture_Grupos!$G$3:$G$74))+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C24)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$G$3:$G$74=Fixture_Grupos!$F$3:$F$74))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C24)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$F$3:$F$74&lt;Fixture_Grupos!$G$3:$G$74))+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C24)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$G$3:$G$74&lt;Fixture_Grupos!$F$3:$F$74))</f>
@@ -16512,11 +16520,11 @@
       </c>
       <c r="H24" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C24)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$F$3:$F$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C24)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$G$3:$G$74)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I24" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C24)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$G$3:$G$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C24)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$F$3:$F$74)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J24" s="10">
         <f t="shared" si="0"/>
@@ -16524,7 +16532,7 @@
       </c>
       <c r="K24" s="10">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L24" s="10">
         <f>SUMPRODUCT(--(($K$23:$K$26*1000+$J$23:$J$26*10+$H$23:$H$26)&gt;($K24*1000+$J24*10+$H24)))+1</f>
@@ -16543,7 +16551,7 @@
       </c>
       <c r="D25" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C25)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C25)*Fixture_Grupos!$H$3:$H$74)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C25)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$F$3:$F$74&gt;Fixture_Grupos!$G$3:$G$74))+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C25)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$G$3:$G$74&gt;Fixture_Grupos!$F$3:$F$74))</f>
@@ -16551,7 +16559,7 @@
       </c>
       <c r="F25" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C25)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$F$3:$F$74=Fixture_Grupos!$G$3:$G$74))+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C25)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$G$3:$G$74=Fixture_Grupos!$F$3:$F$74))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C25)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$F$3:$F$74&lt;Fixture_Grupos!$G$3:$G$74))+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C25)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$G$3:$G$74&lt;Fixture_Grupos!$F$3:$F$74))</f>
@@ -16559,11 +16567,11 @@
       </c>
       <c r="H25" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C25)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$F$3:$F$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C25)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$G$3:$G$74)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I25" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C25)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$G$3:$G$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C25)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$F$3:$F$74)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J25" s="10">
         <f t="shared" si="0"/>
@@ -16571,7 +16579,7 @@
       </c>
       <c r="K25" s="10">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L25" s="10">
         <f>SUMPRODUCT(--(($K$23:$K$26*1000+$J$23:$J$26*10+$H$23:$H$26)&gt;($K25*1000+$J25*10+$H25)))+1</f>
@@ -16590,7 +16598,7 @@
       </c>
       <c r="D26" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C26)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C26)*Fixture_Grupos!$H$3:$H$74)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C26)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$F$3:$F$74&gt;Fixture_Grupos!$G$3:$G$74))+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C26)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$G$3:$G$74&gt;Fixture_Grupos!$F$3:$F$74))</f>
@@ -16602,19 +16610,19 @@
       </c>
       <c r="G26" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C26)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$F$3:$F$74&lt;Fixture_Grupos!$G$3:$G$74))+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C26)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$G$3:$G$74&lt;Fixture_Grupos!$F$3:$F$74))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H26" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C26)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$F$3:$F$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C26)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$G$3:$G$74)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C26)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$G$3:$G$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C26)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$F$3:$F$74)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J26" s="10">
         <f t="shared" si="0"/>
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="K26" s="10">
         <f t="shared" si="1"/>

--- a/Mundial_2026_fuente_datos.xlsx
+++ b/Mundial_2026_fuente_datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sriverti\Desktop\INECO\Repositorios\ML_prediccion_mundial2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4F2819E-5A1D-4CDC-935D-95C9239AEEF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B438F53-9655-43C4-B5CB-C6B6CF30A8CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13751,19 +13751,23 @@
       <c r="E25" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="F25" s="24"/>
-      <c r="G25" s="24"/>
+      <c r="F25" s="24">
+        <v>2</v>
+      </c>
+      <c r="G25" s="24">
+        <v>3</v>
+      </c>
       <c r="H25" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I25" s="7" t="str">
+        <v>1</v>
+      </c>
+      <c r="I25" s="7">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J25" s="7" t="str">
+        <v>0</v>
+      </c>
+      <c r="J25" s="7">
         <f t="shared" si="2"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13782,19 +13786,23 @@
       <c r="E26" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
+      <c r="F26" s="25">
+        <v>0</v>
+      </c>
+      <c r="G26" s="25">
+        <v>0</v>
+      </c>
       <c r="H26" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I26" s="10" t="str">
+        <v>1</v>
+      </c>
+      <c r="I26" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J26" s="10" t="str">
+        <v>1</v>
+      </c>
+      <c r="J26" s="10">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16081,7 +16089,7 @@
       </c>
       <c r="D15" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C15)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C15)*Fixture_Grupos!$H$3:$H$74)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C15)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$F$3:$F$74&gt;Fixture_Grupos!$G$3:$G$74))+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C15)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$G$3:$G$74&gt;Fixture_Grupos!$F$3:$F$74))</f>
@@ -16093,19 +16101,19 @@
       </c>
       <c r="G15" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C15)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$F$3:$F$74&lt;Fixture_Grupos!$G$3:$G$74))+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C15)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$G$3:$G$74&lt;Fixture_Grupos!$F$3:$F$74))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C15)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$F$3:$F$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C15)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$G$3:$G$74)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I15" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C15)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$G$3:$G$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C15)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$F$3:$F$74)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J15" s="10">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K15" s="10">
         <f t="shared" si="1"/>
@@ -16128,7 +16136,7 @@
       </c>
       <c r="D16" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C16)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C16)*Fixture_Grupos!$H$3:$H$74)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C16)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$F$3:$F$74&gt;Fixture_Grupos!$G$3:$G$74))+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C16)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$G$3:$G$74&gt;Fixture_Grupos!$F$3:$F$74))</f>
@@ -16136,7 +16144,7 @@
       </c>
       <c r="F16" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C16)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$F$3:$F$74=Fixture_Grupos!$G$3:$G$74))+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C16)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$G$3:$G$74=Fixture_Grupos!$F$3:$F$74))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C16)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$F$3:$F$74&lt;Fixture_Grupos!$G$3:$G$74))+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C16)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$G$3:$G$74&lt;Fixture_Grupos!$F$3:$F$74))</f>
@@ -16156,7 +16164,7 @@
       </c>
       <c r="K16" s="10">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L16" s="10">
         <f>SUMPRODUCT(--(($K$15:$K$18*1000+$J$15:$J$18*10+$H$15:$H$18)&gt;($K16*1000+$J16*10+$H16)))+1</f>
@@ -16175,7 +16183,7 @@
       </c>
       <c r="D17" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C17)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C17)*Fixture_Grupos!$H$3:$H$74)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C17)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$F$3:$F$74&gt;Fixture_Grupos!$G$3:$G$74))+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C17)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$G$3:$G$74&gt;Fixture_Grupos!$F$3:$F$74))</f>
@@ -16183,7 +16191,7 @@
       </c>
       <c r="F17" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C17)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$F$3:$F$74=Fixture_Grupos!$G$3:$G$74))+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C17)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$G$3:$G$74=Fixture_Grupos!$F$3:$F$74))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C17)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$F$3:$F$74&lt;Fixture_Grupos!$G$3:$G$74))+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C17)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$G$3:$G$74&lt;Fixture_Grupos!$F$3:$F$74))</f>
@@ -16203,7 +16211,7 @@
       </c>
       <c r="K17" s="10">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L17" s="10">
         <f>SUMPRODUCT(--(($K$15:$K$18*1000+$J$15:$J$18*10+$H$15:$H$18)&gt;($K17*1000+$J17*10+$H17)))+1</f>
@@ -16222,11 +16230,11 @@
       </c>
       <c r="D18" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C18)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C18)*Fixture_Grupos!$H$3:$H$74)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C18)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$F$3:$F$74&gt;Fixture_Grupos!$G$3:$G$74))+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C18)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$G$3:$G$74&gt;Fixture_Grupos!$F$3:$F$74))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C18)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$F$3:$F$74=Fixture_Grupos!$G$3:$G$74))+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C18)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$G$3:$G$74=Fixture_Grupos!$F$3:$F$74))</f>
@@ -16238,19 +16246,19 @@
       </c>
       <c r="H18" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C18)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$F$3:$F$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C18)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$G$3:$G$74)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I18" s="10">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C18)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$G$3:$G$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C18)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$F$3:$F$74)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J18" s="10">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="K18" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L18" s="10">
         <f>SUMPRODUCT(--(($K$15:$K$18*1000+$J$15:$J$18*10+$H$15:$H$18)&gt;($K18*1000+$J18*10+$H18)))+1</f>

--- a/Mundial_2026_fuente_datos.xlsx
+++ b/Mundial_2026_fuente_datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sriverti\Desktop\INECO\Repositorios\ML_prediccion_mundial2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B438F53-9655-43C4-B5CB-C6B6CF30A8CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B23E84B-DDD0-43A8-A8DB-88244C35094E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14785,19 +14785,23 @@
       <c r="E55" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="F55" s="24"/>
-      <c r="G55" s="24"/>
+      <c r="F55" s="24">
+        <v>4</v>
+      </c>
+      <c r="G55" s="24">
+        <v>1</v>
+      </c>
       <c r="H55" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I55" s="7" t="str">
+        <v>1</v>
+      </c>
+      <c r="I55" s="7">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J55" s="7" t="str">
+        <v>3</v>
+      </c>
+      <c r="J55" s="7">
         <f t="shared" si="5"/>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14816,19 +14820,23 @@
       <c r="E56" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="F56" s="25"/>
-      <c r="G56" s="25"/>
+      <c r="F56" s="25">
+        <v>5</v>
+      </c>
+      <c r="G56" s="25">
+        <v>0</v>
+      </c>
       <c r="H56" s="10">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I56" s="10" t="str">
+        <v>1</v>
+      </c>
+      <c r="I56" s="10">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J56" s="10" t="str">
+        <v>3</v>
+      </c>
+      <c r="J56" s="10">
         <f t="shared" si="5"/>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17029,11 +17037,11 @@
       </c>
       <c r="D35" s="7">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C35)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C35)*Fixture_Grupos!$H$3:$H$74)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35" s="7">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C35)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$F$3:$F$74&gt;Fixture_Grupos!$G$3:$G$74))+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C35)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$G$3:$G$74&gt;Fixture_Grupos!$F$3:$F$74))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F35" s="7">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C35)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$F$3:$F$74=Fixture_Grupos!$G$3:$G$74))+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C35)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$G$3:$G$74=Fixture_Grupos!$F$3:$F$74))</f>
@@ -17045,19 +17053,19 @@
       </c>
       <c r="H35" s="7">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C35)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$F$3:$F$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C35)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$G$3:$G$74)</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I35" s="7">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C35)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$G$3:$G$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C35)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$F$3:$F$74)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J35" s="7">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K35" s="7">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L35" s="7">
         <f>SUMPRODUCT(--(($K$35:$K$38*1000+$J$35:$J$38*10+$H$35:$H$38)&gt;($K35*1000+$J35*10+$H35)))+1</f>
@@ -17076,11 +17084,11 @@
       </c>
       <c r="D36" s="7">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C36)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C36)*Fixture_Grupos!$H$3:$H$74)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36" s="7">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C36)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$F$3:$F$74&gt;Fixture_Grupos!$G$3:$G$74))+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C36)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$G$3:$G$74&gt;Fixture_Grupos!$F$3:$F$74))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="7">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C36)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$F$3:$F$74=Fixture_Grupos!$G$3:$G$74))+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C36)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$G$3:$G$74=Fixture_Grupos!$F$3:$F$74))</f>
@@ -17092,7 +17100,7 @@
       </c>
       <c r="H36" s="7">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C36)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$F$3:$F$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C36)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$G$3:$G$74)</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I36" s="7">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C36)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$G$3:$G$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C36)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$F$3:$F$74)</f>
@@ -17100,11 +17108,11 @@
       </c>
       <c r="J36" s="7">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="K36" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L36" s="7">
         <f>SUMPRODUCT(--(($K$35:$K$38*1000+$J$35:$J$38*10+$H$35:$H$38)&gt;($K36*1000+$J36*10+$H36)))+1</f>
@@ -17123,7 +17131,7 @@
       </c>
       <c r="D37" s="7">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C37)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C37)*Fixture_Grupos!$H$3:$H$74)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37" s="7">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C37)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$F$3:$F$74&gt;Fixture_Grupos!$G$3:$G$74))+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C37)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$G$3:$G$74&gt;Fixture_Grupos!$F$3:$F$74))</f>
@@ -17135,7 +17143,7 @@
       </c>
       <c r="G37" s="7">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C37)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$F$3:$F$74&lt;Fixture_Grupos!$G$3:$G$74))+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C37)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$G$3:$G$74&lt;Fixture_Grupos!$F$3:$F$74))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37" s="7">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C37)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$F$3:$F$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C37)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$G$3:$G$74)</f>
@@ -17143,11 +17151,11 @@
       </c>
       <c r="I37" s="7">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C37)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$G$3:$G$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C37)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$F$3:$F$74)</f>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J37" s="7">
         <f t="shared" si="0"/>
-        <v>-6</v>
+        <v>-11</v>
       </c>
       <c r="K37" s="7">
         <f t="shared" si="1"/>
@@ -17170,7 +17178,7 @@
       </c>
       <c r="D38" s="7">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C38)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C38)*Fixture_Grupos!$H$3:$H$74)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E38" s="7">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C38)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$F$3:$F$74&gt;Fixture_Grupos!$G$3:$G$74))+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C38)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$G$3:$G$74&gt;Fixture_Grupos!$F$3:$F$74))</f>
@@ -17182,19 +17190,19 @@
       </c>
       <c r="G38" s="7">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C38)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$F$3:$F$74&lt;Fixture_Grupos!$G$3:$G$74))+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C38)*Fixture_Grupos!$H$3:$H$74*(Fixture_Grupos!$G$3:$G$74&lt;Fixture_Grupos!$F$3:$F$74))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="7">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C38)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$F$3:$F$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C38)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$G$3:$G$74)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I38" s="7">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C38)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$G$3:$G$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C38)*Fixture_Grupos!$H$3:$H$74*Fixture_Grupos!$F$3:$F$74)</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J38" s="7">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K38" s="7">
         <f t="shared" si="1"/>

--- a/Mundial_2026_fuente_datos.xlsx
+++ b/Mundial_2026_fuente_datos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\santi\OneDrive\Escritorio\Repositorios\ML_prediccion_mundial2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sriverti\Desktop\INECO\Repositorios\ML_prediccion_mundial2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94DB8B49-6BD5-49C0-9B79-06B390A18496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48CF2E9F-0340-4B5C-9BD1-58447E343B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Léeme" sheetId="1" r:id="rId1"/>
@@ -26450,8 +26450,12 @@
         <f t="array" ref="C3">INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="A")*(Posiciones!$L$3:$L$50=2)*ROW(Posiciones!$A$3:$A$50))-2)</f>
         <v>Sudáfrica</v>
       </c>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
+      <c r="D3" s="26">
+        <v>0</v>
+      </c>
+      <c r="E3" s="26">
+        <v>1</v>
+      </c>
       <c r="F3" s="31" t="str">
         <f t="array" ref="F3">INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="B")*(Posiciones!$L$3:$L$50=2)*ROW(Posiciones!$A$3:$A$50))-2)</f>
         <v>Canadá</v>

--- a/Mundial_2026_fuente_datos.xlsx
+++ b/Mundial_2026_fuente_datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sriverti\Desktop\INECO\Repositorios\ML_prediccion_mundial2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48CF2E9F-0340-4B5C-9BD1-58447E343B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C64577FE-2C1A-43D4-9543-4C6500F99F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26481,8 +26481,12 @@
         <f t="array" ref="C4">INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="C")*(Posiciones!$L$3:$L$50=1)*ROW(Posiciones!$A$3:$A$50))-2)</f>
         <v>Brasil</v>
       </c>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
+      <c r="D4" s="26">
+        <v>2</v>
+      </c>
+      <c r="E4" s="26">
+        <v>1</v>
+      </c>
       <c r="F4" s="31" t="str">
         <f t="array" ref="F4">INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="F")*(Posiciones!$L$3:$L$50=2)*ROW(Posiciones!$A$3:$A$50))-2)</f>
         <v>Japón</v>

--- a/Mundial_2026_fuente_datos.xlsx
+++ b/Mundial_2026_fuente_datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sriverti\Desktop\INECO\Repositorios\ML_prediccion_mundial2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2743AC3F-C689-4E86-8308-752CBCA2C467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C5DEA48-875E-4A0C-BA09-0C8A89D68173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21897,11 +21897,11 @@
         <v>0</v>
       </c>
       <c r="H67" s="8">
-        <f t="shared" ref="H67:H98" si="6">IF(AND(ISNUMBER(F67),ISNUMBER(G67)),1,0)</f>
+        <f t="shared" ref="H67:H74" si="6">IF(AND(ISNUMBER(F67),ISNUMBER(G67)),1,0)</f>
         <v>1</v>
       </c>
       <c r="I67" s="8">
-        <f t="shared" ref="I67:I98" si="7">IF(H67=1,IF(F67&gt;G67,3,IF(F67=G67,1,0)),"")</f>
+        <f t="shared" ref="I67:I74" si="7">IF(H67=1,IF(F67&gt;G67,3,IF(F67=G67,1,0)),"")</f>
         <v>1</v>
       </c>
       <c r="J67" s="8">
@@ -26597,8 +26597,12 @@
         <f t="array" ref="C7">INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="E")*(Posiciones!$L$3:$L$50=2)*ROW(Posiciones!$A$3:$A$50))-2)</f>
         <v>Costa de Marfil</v>
       </c>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
+      <c r="D7" s="26">
+        <v>1</v>
+      </c>
+      <c r="E7" s="26">
+        <v>2</v>
+      </c>
       <c r="F7" s="31" t="str">
         <f t="array" ref="F7">INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="I")*(Posiciones!$L$3:$L$50=2)*ROW(Posiciones!$A$3:$A$50))-2)</f>
         <v>Noruega</v>

--- a/Mundial_2026_fuente_datos.xlsx
+++ b/Mundial_2026_fuente_datos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sriverti\Desktop\INECO\Repositorios\ML_prediccion_mundial2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\santi\OneDrive\Escritorio\Repositorios\ML_prediccion_mundial2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C5DEA48-875E-4A0C-BA09-0C8A89D68173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5EC742B-6F1B-4DB1-9CB6-CDAF5757117B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Léeme" sheetId="1" r:id="rId1"/>
@@ -26628,8 +26628,12 @@
         <f t="array" ref="C8">INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="I")*(Posiciones!$L$3:$L$50=1)*ROW(Posiciones!$A$3:$A$50))-2)</f>
         <v>Francia</v>
       </c>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
+      <c r="D8" s="26">
+        <v>3</v>
+      </c>
+      <c r="E8" s="26">
+        <v>0</v>
+      </c>
       <c r="F8" s="31" t="s">
         <v>26</v>
       </c>

--- a/Mundial_2026_fuente_datos.xlsx
+++ b/Mundial_2026_fuente_datos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\santi\OneDrive\Escritorio\Repositorios\ML_prediccion_mundial2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sriverti\Desktop\INECO\Repositorios\ML_prediccion_mundial2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5EC742B-6F1B-4DB1-9CB6-CDAF5757117B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5008A0F8-97DF-411C-9417-1CABCB9D40F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Léeme" sheetId="1" r:id="rId1"/>
@@ -26658,8 +26658,12 @@
         <f t="array" ref="C9">INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="A")*(Posiciones!$L$3:$L$50=1)*ROW(Posiciones!$A$3:$A$50))-2)</f>
         <v>México</v>
       </c>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
+      <c r="D9" s="26">
+        <v>2</v>
+      </c>
+      <c r="E9" s="26">
+        <v>0</v>
+      </c>
       <c r="F9" s="31" t="s">
         <v>29</v>
       </c>

--- a/Mundial_2026_fuente_datos.xlsx
+++ b/Mundial_2026_fuente_datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sriverti\Desktop\INECO\Repositorios\ML_prediccion_mundial2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5008A0F8-97DF-411C-9417-1CABCB9D40F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8E90EEB-F688-4D75-9A59-4346D338337E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26688,8 +26688,12 @@
         <f t="array" ref="C10">INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="L")*(Posiciones!$L$3:$L$50=1)*ROW(Posiciones!$A$3:$A$50))-2)</f>
         <v>Inglaterra</v>
       </c>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
+      <c r="D10" s="26">
+        <v>2</v>
+      </c>
+      <c r="E10" s="26">
+        <v>1</v>
+      </c>
       <c r="F10" s="31" t="s">
         <v>32</v>
       </c>
@@ -26714,8 +26718,12 @@
         <f t="array" ref="C11">INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="G")*(Posiciones!$L$3:$L$50=1)*ROW(Posiciones!$A$3:$A$50))-2)</f>
         <v>Bélgica</v>
       </c>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
+      <c r="D11" s="26">
+        <v>3</v>
+      </c>
+      <c r="E11" s="26">
+        <v>2</v>
+      </c>
       <c r="F11" s="31" t="s">
         <v>35</v>
       </c>
@@ -26740,8 +26748,12 @@
         <f t="array" ref="C12">INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="D")*(Posiciones!$L$3:$L$50=1)*ROW(Posiciones!$A$3:$A$50))-2)</f>
         <v>Estados Unidos</v>
       </c>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
+      <c r="D12" s="26">
+        <v>2</v>
+      </c>
+      <c r="E12" s="26">
+        <v>0</v>
+      </c>
       <c r="F12" s="31" t="s">
         <v>38</v>
       </c>

--- a/Mundial_2026_fuente_datos.xlsx
+++ b/Mundial_2026_fuente_datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sriverti\Desktop\INECO\Repositorios\ML_prediccion_mundial2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8E90EEB-F688-4D75-9A59-4346D338337E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC1B0A32-01A7-4799-A581-FC3C81FEAB11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26778,8 +26778,12 @@
         <f t="array" ref="C13">INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="H")*(Posiciones!$L$3:$L$50=1)*ROW(Posiciones!$A$3:$A$50))-2)</f>
         <v>España</v>
       </c>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
+      <c r="D13" s="26">
+        <v>3</v>
+      </c>
+      <c r="E13" s="26">
+        <v>0</v>
+      </c>
       <c r="F13" s="31" t="str">
         <f t="array" ref="F13">INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="J")*(Posiciones!$L$3:$L$50=2)*ROW(Posiciones!$A$3:$A$50))-2)</f>
         <v>Austria</v>
@@ -26805,8 +26809,12 @@
         <f t="array" ref="C14">INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="K")*(Posiciones!$L$3:$L$50=2)*ROW(Posiciones!$A$3:$A$50))-2)</f>
         <v>Portugal</v>
       </c>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
+      <c r="D14" s="26">
+        <v>2</v>
+      </c>
+      <c r="E14" s="26">
+        <v>1</v>
+      </c>
       <c r="F14" s="31" t="str">
         <f t="array" ref="F14">INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="L")*(Posiciones!$L$3:$L$50=2)*ROW(Posiciones!$A$3:$A$50))-2)</f>
         <v>Croacia</v>
@@ -26832,8 +26840,12 @@
         <f t="array" ref="C15">INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="B")*(Posiciones!$L$3:$L$50=1)*ROW(Posiciones!$A$3:$A$50))-2)</f>
         <v>Suiza</v>
       </c>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
+      <c r="D15" s="26">
+        <v>2</v>
+      </c>
+      <c r="E15" s="26">
+        <v>0</v>
+      </c>
       <c r="F15" s="31" t="s">
         <v>45</v>
       </c>

--- a/Mundial_2026_fuente_datos.xlsx
+++ b/Mundial_2026_fuente_datos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sriverti\Desktop\INECO\Repositorios\ML_prediccion_mundial2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\santi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC1B0A32-01A7-4799-A581-FC3C81FEAB11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52624F40-37B0-4138-8F8D-4C2B69B0FDA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Léeme" sheetId="1" r:id="rId1"/>
@@ -26870,8 +26870,12 @@
         <f t="array" ref="C16">INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="D")*(Posiciones!$L$3:$L$50=2)*ROW(Posiciones!$A$3:$A$50))-2)</f>
         <v>Australia</v>
       </c>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
+      <c r="D16" s="26">
+        <v>1</v>
+      </c>
+      <c r="E16" s="26">
+        <v>1</v>
+      </c>
       <c r="F16" s="31" t="str">
         <f t="array" ref="F16">INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="G")*(Posiciones!$L$3:$L$50=2)*ROW(Posiciones!$A$3:$A$50))-2)</f>
         <v>Egipto</v>
@@ -26885,6 +26889,12 @@
       <c r="J16" s="23" t="s">
         <v>49</v>
       </c>
+      <c r="K16">
+        <v>2</v>
+      </c>
+      <c r="L16">
+        <v>4</v>
+      </c>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
@@ -26897,8 +26907,12 @@
         <f t="array" ref="C17">INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="J")*(Posiciones!$L$3:$L$50=1)*ROW(Posiciones!$A$3:$A$50))-2)</f>
         <v>Argentina</v>
       </c>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
+      <c r="D17" s="26">
+        <v>3</v>
+      </c>
+      <c r="E17" s="26">
+        <v>2</v>
+      </c>
       <c r="F17" s="31" t="str">
         <f t="array" ref="F17">INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="H")*(Posiciones!$L$3:$L$50=2)*ROW(Posiciones!$A$3:$A$50))-2)</f>
         <v>Cabo Verde</v>
@@ -26924,8 +26938,12 @@
         <f t="array" ref="C18">INDEX(Posiciones!$C$3:$C$50,SUMPRODUCT((Posiciones!$A$3:$A$50="K")*(Posiciones!$L$3:$L$50=1)*ROW(Posiciones!$A$3:$A$50))-2)</f>
         <v>Colombia</v>
       </c>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
+      <c r="D18" s="26">
+        <v>1</v>
+      </c>
+      <c r="E18" s="26">
+        <v>0</v>
+      </c>
       <c r="F18" s="31" t="s">
         <v>52</v>
       </c>

--- a/Mundial_2026_fuente_datos.xlsx
+++ b/Mundial_2026_fuente_datos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\santi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sriverti\Desktop\INECO\Repositorios\ML_prediccion_mundial2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52624F40-37B0-4138-8F8D-4C2B69B0FDA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_4ADEC7E3981F1F4C5539D8A0FD356DEC10FBA236" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Léeme" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1469" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1485" uniqueCount="490">
   <si>
     <t>Fase eliminatoria — plantilla para cargar a mano (32avos → final)</t>
   </si>
@@ -210,6 +210,12 @@
   </si>
   <si>
     <t>16avos de final</t>
+  </si>
+  <si>
+    <t>Resultado real cargado (prensa, jul-2026).</t>
+  </si>
+  <si>
+    <t>Equipo definido por formula (ganador de la ronda anterior); se actualiza solo al cargar goles.</t>
   </si>
   <si>
     <t>Cuartos de final</t>
@@ -1996,194 +2002,194 @@
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="34" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C1" s="33"/>
     </row>
     <row r="2" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C4" s="5"/>
     </row>
     <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C11" s="5"/>
     </row>
     <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C17" s="5"/>
     </row>
     <row r="18" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3180,32 +3186,32 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D3" s="23">
         <v>2240</v>
@@ -3213,13 +3219,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="23" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D4" s="23">
         <v>1560</v>
@@ -3227,13 +3233,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D5" s="23">
         <v>500</v>
@@ -3241,13 +3247,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="23" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D6" s="23">
         <v>76</v>
@@ -3255,13 +3261,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="23" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D7" s="23">
         <v>0</v>
@@ -3269,13 +3275,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="23" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D8" s="23">
         <v>3</v>
@@ -3283,13 +3289,13 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D9" s="23">
         <v>150</v>
@@ -3297,13 +3303,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="23" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D10" s="23">
         <v>30</v>
@@ -3311,13 +3317,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="23" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D11" s="23">
         <v>270</v>
@@ -3325,13 +3331,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="23" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D12" s="23">
         <v>5</v>
@@ -3339,13 +3345,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="23" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D13" s="23">
         <v>15</v>
@@ -3353,13 +3359,13 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="23" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D14" s="23">
         <v>12</v>
@@ -3367,13 +3373,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="23" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D15" s="23">
         <v>320</v>
@@ -3381,13 +3387,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="23" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D16" s="23">
         <v>30</v>
@@ -3395,13 +3401,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="23" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D17" s="23">
         <v>2</v>
@@ -3409,13 +3415,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="23" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D18" s="23">
         <v>30</v>
@@ -4425,7 +4431,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="34" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
@@ -4440,37 +4446,37 @@
     </row>
     <row r="2" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I2" s="7" t="s">
         <v>8</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4478,19 +4484,19 @@
         <v>1</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E3" s="8">
         <v>1</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G3" s="8">
         <v>15</v>
@@ -4499,10 +4505,10 @@
         <v>1675.74</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K3" s="8">
         <v>0</v>
@@ -4513,19 +4519,19 @@
         <v>2</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E4" s="11">
         <v>2</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G4" s="11">
         <v>61</v>
@@ -4534,10 +4540,10 @@
         <v>1427.3</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K4" s="11">
         <v>0</v>
@@ -4548,19 +4554,19 @@
         <v>3</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E5" s="8">
         <v>3</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G5" s="8">
         <v>22</v>
@@ -4569,10 +4575,10 @@
         <v>1599.45</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K5" s="8">
         <v>0</v>
@@ -4583,19 +4589,19 @@
         <v>4</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E6" s="11">
         <v>4</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G6" s="11">
         <v>44</v>
@@ -4604,10 +4610,10 @@
         <v>1487</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K6" s="11">
         <v>0</v>
@@ -4618,19 +4624,19 @@
         <v>5</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E7" s="8">
         <v>1</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G7" s="8">
         <v>27</v>
@@ -4639,10 +4645,10 @@
         <v>1559.16</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K7" s="8">
         <v>0</v>
@@ -4656,16 +4662,16 @@
         <v>38</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E8" s="11">
         <v>2</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G8" s="11">
         <v>71</v>
@@ -4674,10 +4680,10 @@
         <v>1393.9</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K8" s="11">
         <v>0</v>
@@ -4688,19 +4694,19 @@
         <v>7</v>
       </c>
       <c r="B9" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>136</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>134</v>
       </c>
       <c r="E9" s="8">
         <v>3</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G9" s="8">
         <v>51</v>
@@ -4709,10 +4715,10 @@
         <v>1461.6</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K9" s="8">
         <v>0</v>
@@ -4723,19 +4729,19 @@
         <v>8</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E10" s="11">
         <v>4</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G10" s="11">
         <v>17</v>
@@ -4744,10 +4750,10 @@
         <v>1654.69</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K10" s="11">
         <v>0</v>
@@ -4758,19 +4764,19 @@
         <v>9</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E11" s="8">
         <v>1</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G11" s="8">
         <v>5</v>
@@ -4779,10 +4785,10 @@
         <v>1760.46</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K11" s="8">
         <v>5</v>
@@ -4793,19 +4799,19 @@
         <v>10</v>
       </c>
       <c r="B12" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>144</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>142</v>
       </c>
       <c r="E12" s="11">
         <v>2</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G12" s="11">
         <v>11</v>
@@ -4814,10 +4820,10 @@
         <v>1713.12</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K12" s="11">
         <v>0</v>
@@ -4828,19 +4834,19 @@
         <v>11</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E13" s="8">
         <v>3</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G13" s="8">
         <v>84</v>
@@ -4849,10 +4855,10 @@
         <v>1350.5</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K13" s="8">
         <v>0</v>
@@ -4863,19 +4869,19 @@
         <v>12</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E14" s="11">
         <v>4</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G14" s="11">
         <v>36</v>
@@ -4884,10 +4890,10 @@
         <v>1506.77</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K14" s="11">
         <v>0</v>
@@ -4898,19 +4904,19 @@
         <v>13</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E15" s="8">
         <v>1</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G15" s="8">
         <v>14</v>
@@ -4919,10 +4925,10 @@
         <v>1681.88</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K15" s="8">
         <v>0</v>
@@ -4936,16 +4942,16 @@
         <v>19</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E16" s="11">
         <v>2</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G16" s="11">
         <v>39</v>
@@ -4954,10 +4960,10 @@
         <v>1501.5</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K16" s="11">
         <v>0</v>
@@ -4968,19 +4974,19 @@
         <v>15</v>
       </c>
       <c r="B17" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>154</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>152</v>
       </c>
       <c r="E17" s="8">
         <v>3</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G17" s="8">
         <v>26</v>
@@ -4989,10 +4995,10 @@
         <v>1574.01</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K17" s="8">
         <v>0</v>
@@ -5003,19 +5009,19 @@
         <v>16</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E18" s="11">
         <v>4</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G18" s="11">
         <v>25</v>
@@ -5024,10 +5030,10 @@
         <v>1582.69</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K18" s="11">
         <v>0</v>
@@ -5038,19 +5044,19 @@
         <v>17</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E19" s="8">
         <v>1</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G19" s="8">
         <v>9</v>
@@ -5059,10 +5065,10 @@
         <v>1724.14</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K19" s="8">
         <v>4</v>
@@ -5073,19 +5079,19 @@
         <v>18</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C20" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>162</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>160</v>
       </c>
       <c r="E20" s="11">
         <v>2</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G20" s="11">
         <v>82</v>
@@ -5094,10 +5100,10 @@
         <v>1357.1</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K20" s="11">
         <v>0</v>
@@ -5108,19 +5114,19 @@
         <v>19</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E21" s="8">
         <v>3</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G21" s="8">
         <v>42</v>
@@ -5129,10 +5135,10 @@
         <v>1489.59</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K21" s="8">
         <v>0</v>
@@ -5146,16 +5152,16 @@
         <v>29</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E22" s="11">
         <v>4</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G22" s="11">
         <v>23</v>
@@ -5164,10 +5170,10 @@
         <v>1591.73</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K22" s="11">
         <v>0</v>
@@ -5178,19 +5184,19 @@
         <v>21</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E23" s="8">
         <v>1</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G23" s="8">
         <v>7</v>
@@ -5199,10 +5205,10 @@
         <v>1756.26</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K23" s="8">
         <v>0</v>
@@ -5213,19 +5219,19 @@
         <v>22</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C24" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="D24" s="11" t="s">
         <v>170</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>168</v>
       </c>
       <c r="E24" s="11">
         <v>2</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G24" s="11">
         <v>18</v>
@@ -5234,10 +5240,10 @@
         <v>1650.11</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K24" s="11">
         <v>0</v>
@@ -5251,16 +5257,16 @@
         <v>26</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E25" s="8">
         <v>3</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G25" s="8">
         <v>43</v>
@@ -5269,10 +5275,10 @@
         <v>1487.13</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K25" s="8">
         <v>0</v>
@@ -5283,19 +5289,19 @@
         <v>24</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E26" s="11">
         <v>4</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G26" s="11">
         <v>40</v>
@@ -5304,10 +5310,10 @@
         <v>1497.13</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K26" s="11">
         <v>0</v>
@@ -5318,19 +5324,19 @@
         <v>25</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E27" s="8">
         <v>1</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G27" s="8">
         <v>8</v>
@@ -5339,10 +5345,10 @@
         <v>1730.71</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K27" s="8">
         <v>0</v>
@@ -5353,19 +5359,19 @@
         <v>26</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C28" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="D28" s="11" t="s">
         <v>178</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>176</v>
       </c>
       <c r="E28" s="11">
         <v>2</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G28" s="11">
         <v>34</v>
@@ -5374,10 +5380,10 @@
         <v>1520.68</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K28" s="11">
         <v>0</v>
@@ -5388,19 +5394,19 @@
         <v>27</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E29" s="8">
         <v>3</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G29" s="8">
         <v>20</v>
@@ -5409,10 +5415,10 @@
         <v>1617.03</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K29" s="8">
         <v>0</v>
@@ -5423,19 +5429,19 @@
         <v>28</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E30" s="11">
         <v>4</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G30" s="11">
         <v>86</v>
@@ -5444,10 +5450,10 @@
         <v>1343.8</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K30" s="11">
         <v>0</v>
@@ -5458,19 +5464,19 @@
         <v>29</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E31" s="8">
         <v>1</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G31" s="8">
         <v>1</v>
@@ -5479,10 +5485,10 @@
         <v>1877.17</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K31" s="8">
         <v>1</v>
@@ -5493,19 +5499,19 @@
         <v>30</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C32" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="D32" s="11" t="s">
         <v>188</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>186</v>
       </c>
       <c r="E32" s="11">
         <v>2</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G32" s="11">
         <v>68</v>
@@ -5514,10 +5520,10 @@
         <v>1403.9</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K32" s="11">
         <v>0</v>
@@ -5528,19 +5534,19 @@
         <v>31</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E33" s="8">
         <v>3</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G33" s="15">
         <v>60</v>
@@ -5549,10 +5555,10 @@
         <v>1430.6</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J33" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K33" s="8">
         <v>0</v>
@@ -5563,19 +5569,19 @@
         <v>32</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E34" s="11">
         <v>4</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G34" s="11">
         <v>16</v>
@@ -5584,10 +5590,10 @@
         <v>1672.61</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K34" s="11">
         <v>2</v>
@@ -5598,19 +5604,19 @@
         <v>33</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E35" s="8">
         <v>1</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G35" s="8">
         <v>3</v>
@@ -5619,10 +5625,10 @@
         <v>1870</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K35" s="8">
         <v>2</v>
@@ -5636,16 +5642,16 @@
         <v>35</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E36" s="11">
         <v>2</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G36" s="11">
         <v>19</v>
@@ -5654,10 +5660,10 @@
         <v>1648.06</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K36" s="11">
         <v>0</v>
@@ -5668,19 +5674,19 @@
         <v>35</v>
       </c>
       <c r="B37" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D37" s="8" t="s">
         <v>197</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>195</v>
       </c>
       <c r="E37" s="8">
         <v>3</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G37" s="15">
         <v>58</v>
@@ -5689,10 +5695,10 @@
         <v>1437.3</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J37" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K37" s="8">
         <v>0</v>
@@ -5703,19 +5709,19 @@
         <v>36</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E38" s="11">
         <v>4</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G38" s="11">
         <v>29</v>
@@ -5724,10 +5730,10 @@
         <v>1553.13</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K38" s="11">
         <v>0</v>
@@ -5738,19 +5744,19 @@
         <v>37</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E39" s="8">
         <v>1</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G39" s="8">
         <v>2</v>
@@ -5759,10 +5765,10 @@
         <v>1873.32</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J39" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K39" s="8">
         <v>3</v>
@@ -5776,16 +5782,16 @@
         <v>45</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E40" s="11">
         <v>2</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G40" s="11">
         <v>35</v>
@@ -5794,10 +5800,10 @@
         <v>1516.37</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K40" s="11">
         <v>0</v>
@@ -5808,19 +5814,19 @@
         <v>39</v>
       </c>
       <c r="B41" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="D41" s="8" t="s">
         <v>205</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>203</v>
       </c>
       <c r="E41" s="8">
         <v>3</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G41" s="8">
         <v>24</v>
@@ -5829,10 +5835,10 @@
         <v>1585.5</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J41" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K41" s="8">
         <v>0</v>
@@ -5843,19 +5849,19 @@
         <v>40</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E42" s="11">
         <v>4</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G42" s="11">
         <v>66</v>
@@ -5864,10 +5870,10 @@
         <v>1410.6</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K42" s="11">
         <v>0</v>
@@ -5878,19 +5884,19 @@
         <v>41</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E43" s="8">
         <v>1</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G43" s="8">
         <v>6</v>
@@ -5899,10 +5905,10 @@
         <v>1760.39</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K43" s="8">
         <v>0</v>
@@ -5916,16 +5922,16 @@
         <v>32</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E44" s="11">
         <v>2</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G44" s="11">
         <v>56</v>
@@ -5934,10 +5940,10 @@
         <v>1442.51</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K44" s="11">
         <v>0</v>
@@ -5948,19 +5954,19 @@
         <v>43</v>
       </c>
       <c r="B45" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="D45" s="8" t="s">
         <v>213</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>211</v>
       </c>
       <c r="E45" s="8">
         <v>3</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G45" s="15">
         <v>50</v>
@@ -5969,10 +5975,10 @@
         <v>1464</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K45" s="8">
         <v>0</v>
@@ -5983,19 +5989,19 @@
         <v>44</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E46" s="11">
         <v>4</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G46" s="11">
         <v>13</v>
@@ -6004,10 +6010,10 @@
         <v>1701.29</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K46" s="11">
         <v>0</v>
@@ -6018,19 +6024,19 @@
         <v>45</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E47" s="8">
         <v>1</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G47" s="8">
         <v>4</v>
@@ -6039,10 +6045,10 @@
         <v>1834.11</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J47" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K47" s="8">
         <v>1</v>
@@ -6053,19 +6059,19 @@
         <v>46</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C48" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="D48" s="11" t="s">
         <v>221</v>
-      </c>
-      <c r="D48" s="11" t="s">
-        <v>219</v>
       </c>
       <c r="E48" s="11">
         <v>2</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G48" s="11">
         <v>10</v>
@@ -6074,10 +6080,10 @@
         <v>1716.89</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K48" s="11">
         <v>0</v>
@@ -6091,16 +6097,16 @@
         <v>52</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E49" s="8">
         <v>3</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G49" s="8">
         <v>72</v>
@@ -6109,10 +6115,10 @@
         <v>1390.5</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K49" s="8">
         <v>0</v>
@@ -6123,19 +6129,19 @@
         <v>48</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E50" s="11">
         <v>4</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G50" s="11">
         <v>30</v>
@@ -6144,10 +6150,10 @@
         <v>1540.42</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K50" s="11">
         <v>0</v>
@@ -6156,7 +6162,7 @@
     <row r="51" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="32" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C52" s="33"/>
       <c r="D52" s="33"/>
@@ -7148,7 +7154,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="35" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
@@ -7170,58 +7176,58 @@
     </row>
     <row r="2" spans="1:18" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H2" s="16" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I2" s="16" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J2" s="16" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K2" s="16" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L2" s="16" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M2" s="16" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="N2" s="16" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O2" s="16" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="P2" s="16" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q2" s="16" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R2" s="16" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7229,10 +7235,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D3" s="8">
         <v>18</v>
@@ -7241,7 +7247,7 @@
         <v>1930</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="G3" s="8">
         <v>0</v>
@@ -7288,10 +7294,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D4" s="8">
         <v>4</v>
@@ -7300,7 +7306,7 @@
         <v>1998</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G4" s="8">
         <v>0</v>
@@ -7347,10 +7353,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D5" s="8">
         <v>12</v>
@@ -7359,7 +7365,7 @@
         <v>1954</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="G5" s="8">
         <v>0</v>
@@ -7406,10 +7412,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D6" s="8">
         <v>10</v>
@@ -7418,7 +7424,7 @@
         <v>1934</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G6" s="8">
         <v>0</v>
@@ -7465,10 +7471,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D7" s="11">
         <v>3</v>
@@ -7477,7 +7483,7 @@
         <v>1986</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G7" s="11">
         <v>0</v>
@@ -7527,7 +7533,7 @@
         <v>38</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D8" s="11">
         <v>2</v>
@@ -7536,7 +7542,7 @@
         <v>2014</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G8" s="11">
         <v>0</v>
@@ -7583,10 +7589,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D9" s="11">
         <v>2</v>
@@ -7595,7 +7601,7 @@
         <v>2022</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G9" s="11">
         <v>0</v>
@@ -7642,10 +7648,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D10" s="11">
         <v>13</v>
@@ -7654,7 +7660,7 @@
         <v>1934</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="G10" s="11">
         <v>0</v>
@@ -7701,10 +7707,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D11" s="8">
         <v>23</v>
@@ -7713,7 +7719,7 @@
         <v>1930</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G11" s="8">
         <v>5</v>
@@ -7760,10 +7766,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D12" s="8">
         <v>7</v>
@@ -7772,7 +7778,7 @@
         <v>1970</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="G12" s="8">
         <v>0</v>
@@ -7819,10 +7825,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D13" s="8">
         <v>2</v>
@@ -7831,7 +7837,7 @@
         <v>1974</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G13" s="8">
         <v>0</v>
@@ -7878,10 +7884,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D14" s="8">
         <v>9</v>
@@ -7890,7 +7896,7 @@
         <v>1954</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G14" s="8">
         <v>0</v>
@@ -7937,10 +7943,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D15" s="11">
         <v>12</v>
@@ -7949,7 +7955,7 @@
         <v>1930</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G15" s="11">
         <v>0</v>
@@ -7999,7 +8005,7 @@
         <v>19</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D16" s="11">
         <v>9</v>
@@ -8008,7 +8014,7 @@
         <v>1930</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G16" s="11">
         <v>0</v>
@@ -8055,10 +8061,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D17" s="11">
         <v>7</v>
@@ -8067,7 +8073,7 @@
         <v>1974</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G17" s="11">
         <v>0</v>
@@ -8114,10 +8120,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D18" s="11">
         <v>3</v>
@@ -8126,7 +8132,7 @@
         <v>1954</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="G18" s="11">
         <v>0</v>
@@ -8173,10 +8179,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D19" s="8">
         <v>21</v>
@@ -8185,7 +8191,7 @@
         <v>1934</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G19" s="8">
         <v>4</v>
@@ -8232,10 +8238,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D20" s="8">
         <v>1</v>
@@ -8244,7 +8250,7 @@
         <v>2026</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="G20" s="8">
         <v>0</v>
@@ -8291,10 +8297,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D21" s="8">
         <v>4</v>
@@ -8303,7 +8309,7 @@
         <v>2006</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G21" s="8">
         <v>0</v>
@@ -8353,7 +8359,7 @@
         <v>29</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D22" s="8">
         <v>5</v>
@@ -8362,7 +8368,7 @@
         <v>2002</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="G22" s="8">
         <v>0</v>
@@ -8409,10 +8415,10 @@
         <v>21</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D23" s="11">
         <v>12</v>
@@ -8421,7 +8427,7 @@
         <v>1934</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="G23" s="11">
         <v>0</v>
@@ -8468,10 +8474,10 @@
         <v>22</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D24" s="11">
         <v>8</v>
@@ -8480,7 +8486,7 @@
         <v>1998</v>
       </c>
       <c r="F24" s="20" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="G24" s="11">
         <v>0</v>
@@ -8530,7 +8536,7 @@
         <v>26</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D25" s="11">
         <v>13</v>
@@ -8539,7 +8545,7 @@
         <v>1934</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="G25" s="11">
         <v>0</v>
@@ -8586,10 +8592,10 @@
         <v>24</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D26" s="11">
         <v>7</v>
@@ -8598,7 +8604,7 @@
         <v>1978</v>
       </c>
       <c r="F26" s="20" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G26" s="11">
         <v>0</v>
@@ -8645,10 +8651,10 @@
         <v>25</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D27" s="8">
         <v>15</v>
@@ -8657,7 +8663,7 @@
         <v>1930</v>
       </c>
       <c r="F27" s="17" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="G27" s="8">
         <v>0</v>
@@ -8704,10 +8710,10 @@
         <v>26</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D28" s="8">
         <v>4</v>
@@ -8716,7 +8722,7 @@
         <v>1934</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G28" s="8">
         <v>0</v>
@@ -8763,10 +8769,10 @@
         <v>27</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D29" s="8">
         <v>7</v>
@@ -8775,7 +8781,7 @@
         <v>1978</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G29" s="8">
         <v>0</v>
@@ -8822,10 +8828,10 @@
         <v>28</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D30" s="8">
         <v>3</v>
@@ -8834,7 +8840,7 @@
         <v>1982</v>
       </c>
       <c r="F30" s="17" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G30" s="8">
         <v>0</v>
@@ -8881,10 +8887,10 @@
         <v>29</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D31" s="11">
         <v>17</v>
@@ -8893,7 +8899,7 @@
         <v>1934</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G31" s="11">
         <v>1</v>
@@ -8940,10 +8946,10 @@
         <v>30</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D32" s="11">
         <v>1</v>
@@ -8952,7 +8958,7 @@
         <v>2026</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="G32" s="11">
         <v>0</v>
@@ -8999,10 +9005,10 @@
         <v>31</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D33" s="11">
         <v>7</v>
@@ -9011,7 +9017,7 @@
         <v>1994</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G33" s="11">
         <v>0</v>
@@ -9058,10 +9064,10 @@
         <v>32</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D34" s="11">
         <v>15</v>
@@ -9070,7 +9076,7 @@
         <v>1930</v>
       </c>
       <c r="F34" s="20" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G34" s="11">
         <v>2</v>
@@ -9117,10 +9123,10 @@
         <v>33</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D35" s="8">
         <v>17</v>
@@ -9129,7 +9135,7 @@
         <v>1930</v>
       </c>
       <c r="F35" s="17" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="G35" s="8">
         <v>2</v>
@@ -9179,7 +9185,7 @@
         <v>35</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D36" s="8">
         <v>4</v>
@@ -9188,7 +9194,7 @@
         <v>2002</v>
       </c>
       <c r="F36" s="17" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="G36" s="8">
         <v>0</v>
@@ -9235,10 +9241,10 @@
         <v>35</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D37" s="8">
         <v>2</v>
@@ -9247,7 +9253,7 @@
         <v>1986</v>
       </c>
       <c r="F37" s="17" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G37" s="8">
         <v>0</v>
@@ -9294,10 +9300,10 @@
         <v>36</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D38" s="8">
         <v>4</v>
@@ -9306,7 +9312,7 @@
         <v>1938</v>
       </c>
       <c r="F38" s="17" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="G38" s="8">
         <v>0</v>
@@ -9353,10 +9359,10 @@
         <v>37</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D39" s="11">
         <v>19</v>
@@ -9365,7 +9371,7 @@
         <v>1930</v>
       </c>
       <c r="F39" s="20" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="G39" s="11">
         <v>3</v>
@@ -9415,7 +9421,7 @@
         <v>45</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D40" s="11">
         <v>5</v>
@@ -9424,7 +9430,7 @@
         <v>1982</v>
       </c>
       <c r="F40" s="20" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="G40" s="11">
         <v>0</v>
@@ -9471,10 +9477,10 @@
         <v>39</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D41" s="11">
         <v>8</v>
@@ -9483,7 +9489,7 @@
         <v>1934</v>
       </c>
       <c r="F41" s="20" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G41" s="11">
         <v>0</v>
@@ -9530,10 +9536,10 @@
         <v>40</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D42" s="11">
         <v>1</v>
@@ -9542,7 +9548,7 @@
         <v>2026</v>
       </c>
       <c r="F42" s="20" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="G42" s="11">
         <v>0</v>
@@ -9589,10 +9595,10 @@
         <v>41</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D43" s="8">
         <v>9</v>
@@ -9601,7 +9607,7 @@
         <v>1966</v>
       </c>
       <c r="F43" s="17" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G43" s="8">
         <v>0</v>
@@ -9651,7 +9657,7 @@
         <v>32</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D44" s="8">
         <v>2</v>
@@ -9660,7 +9666,7 @@
         <v>1974</v>
       </c>
       <c r="F44" s="17" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G44" s="8">
         <v>0</v>
@@ -9707,10 +9713,10 @@
         <v>43</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D45" s="8">
         <v>1</v>
@@ -9719,7 +9725,7 @@
         <v>2026</v>
       </c>
       <c r="F45" s="17" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="G45" s="8">
         <v>0</v>
@@ -9766,10 +9772,10 @@
         <v>44</v>
       </c>
       <c r="B46" s="17" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D46" s="8">
         <v>7</v>
@@ -9778,7 +9784,7 @@
         <v>1962</v>
       </c>
       <c r="F46" s="17" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G46" s="8">
         <v>0</v>
@@ -9825,10 +9831,10 @@
         <v>45</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D47" s="11">
         <v>17</v>
@@ -9837,7 +9843,7 @@
         <v>1950</v>
       </c>
       <c r="F47" s="20" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G47" s="11">
         <v>1</v>
@@ -9884,10 +9890,10 @@
         <v>46</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D48" s="11">
         <v>7</v>
@@ -9896,7 +9902,7 @@
         <v>1998</v>
       </c>
       <c r="F48" s="20" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G48" s="11">
         <v>0</v>
@@ -9946,7 +9952,7 @@
         <v>52</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D49" s="11">
         <v>5</v>
@@ -9955,7 +9961,7 @@
         <v>2006</v>
       </c>
       <c r="F49" s="20" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G49" s="11">
         <v>0</v>
@@ -10002,10 +10008,10 @@
         <v>48</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D50" s="11">
         <v>2</v>
@@ -10014,7 +10020,7 @@
         <v>2018</v>
       </c>
       <c r="F50" s="20" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G50" s="11">
         <v>0</v>
@@ -10059,7 +10065,7 @@
     <row r="51" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="36" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C52" s="33"/>
       <c r="D52" s="33"/>
@@ -11088,7 +11094,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="35" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
@@ -11099,34 +11105,34 @@
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H2" s="23" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I2" s="23" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="J2" s="23" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11134,22 +11140,22 @@
         <v>1</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E3" s="8">
         <v>2024</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="H3" s="23">
         <v>24</v>
@@ -11166,22 +11172,22 @@
         <v>2</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E4" s="8">
         <v>2021</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="H4" s="23">
         <v>30</v>
@@ -11198,22 +11204,22 @@
         <v>3</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E5" s="8">
         <v>2024</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="H5" s="23">
         <v>18</v>
@@ -11230,19 +11236,19 @@
         <v>4</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E6" s="8">
         <v>2024</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="G6" s="9"/>
       <c r="H6" s="23">
@@ -11260,22 +11266,22 @@
         <v>5</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E7" s="11">
         <v>2024</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="H7" s="23">
         <v>14</v>
@@ -11295,7 +11301,7 @@
         <v>38</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>38</v>
@@ -11304,10 +11310,10 @@
         <v>2024</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="H8" s="23">
         <v>6</v>
@@ -11324,22 +11330,22 @@
         <v>7</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E9" s="11">
         <v>2025</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="H9" s="23">
         <v>18</v>
@@ -11356,19 +11362,19 @@
         <v>8</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E10" s="11">
         <v>2021</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="G10" s="12"/>
       <c r="H10" s="23">
@@ -11386,22 +11392,22 @@
         <v>9</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E11" s="8">
         <v>2025</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H11" s="23">
         <v>8</v>
@@ -11418,22 +11424,22 @@
         <v>10</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E12" s="8">
         <v>2026</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="H12" s="23">
         <v>12</v>
@@ -11450,22 +11456,22 @@
         <v>11</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E13" s="8">
         <v>2024</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H13" s="23">
         <v>12</v>
@@ -11482,22 +11488,22 @@
         <v>12</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E14" s="8">
         <v>2019</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H14" s="23">
         <v>22</v>
@@ -11514,22 +11520,22 @@
         <v>13</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E15" s="11">
         <v>2024</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H15" s="23">
         <v>12</v>
@@ -11549,16 +11555,16 @@
         <v>19</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E16" s="11">
         <v>2024</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G16" s="12"/>
       <c r="H16" s="23">
@@ -11576,19 +11582,19 @@
         <v>15</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E17" s="11">
         <v>2024</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G17" s="12"/>
       <c r="H17" s="23">
@@ -11606,22 +11612,22 @@
         <v>16</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E18" s="11">
         <v>2023</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H18" s="23">
         <v>16</v>
@@ -11638,22 +11644,22 @@
         <v>17</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E19" s="8">
         <v>2023</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H19" s="23">
         <v>22</v>
@@ -11670,22 +11676,22 @@
         <v>18</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E20" s="8">
         <v>2024</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="H20" s="23">
         <v>30</v>
@@ -11702,22 +11708,22 @@
         <v>19</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E21" s="8">
         <v>2024</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H21" s="23">
         <v>26</v>
@@ -11737,16 +11743,16 @@
         <v>29</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E22" s="8">
         <v>2024</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="G22" s="9"/>
       <c r="H22" s="23">
@@ -11764,22 +11770,22 @@
         <v>21</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E23" s="11">
         <v>2023</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="H23" s="23">
         <v>26</v>
@@ -11796,22 +11802,22 @@
         <v>22</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E24" s="11">
         <v>2018</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="H24" s="23">
         <v>24</v>
@@ -11831,19 +11837,19 @@
         <v>26</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E25" s="11">
         <v>2025</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H25" s="23">
         <v>8</v>
@@ -11860,22 +11866,22 @@
         <v>24</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E26" s="11">
         <v>2025</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="H26" s="23">
         <v>14</v>
@@ -11892,22 +11898,22 @@
         <v>25</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E27" s="8">
         <v>2025</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="H27" s="23">
         <v>8</v>
@@ -11924,22 +11930,22 @@
         <v>26</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E28" s="8">
         <v>2024</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="H28" s="23">
         <v>16</v>
@@ -11956,22 +11962,22 @@
         <v>27</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E29" s="8">
         <v>2023</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="H29" s="23">
         <v>18</v>
@@ -11988,19 +11994,19 @@
         <v>28</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E30" s="8">
         <v>2023</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="G30" s="9"/>
       <c r="H30" s="23">
@@ -12018,22 +12024,22 @@
         <v>29</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E31" s="11">
         <v>2022</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="H31" s="23">
         <v>34</v>
@@ -12050,22 +12056,22 @@
         <v>30</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E32" s="11">
         <v>2020</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H32" s="23">
         <v>14</v>
@@ -12082,22 +12088,22 @@
         <v>31</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E33" s="11">
         <v>2025</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="H33" s="23">
         <v>8</v>
@@ -12114,22 +12120,22 @@
         <v>32</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E34" s="11">
         <v>2023</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H34" s="23">
         <v>30</v>
@@ -12146,22 +12152,22 @@
         <v>33</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E35" s="8">
         <v>2012</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H35" s="23">
         <v>50</v>
@@ -12181,7 +12187,7 @@
         <v>35</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D36" s="9" t="s">
         <v>35</v>
@@ -12190,7 +12196,7 @@
         <v>2024</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="G36" s="9"/>
       <c r="H36" s="23">
@@ -12208,22 +12214,22 @@
         <v>35</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E37" s="8">
         <v>2025</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="H37" s="23">
         <v>20</v>
@@ -12240,19 +12246,19 @@
         <v>36</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E38" s="8">
         <v>2020</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G38" s="9"/>
       <c r="H38" s="23">
@@ -12270,22 +12276,22 @@
         <v>37</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E39" s="11">
         <v>2018</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H39" s="23">
         <v>48</v>
@@ -12305,7 +12311,7 @@
         <v>45</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D40" s="12" t="s">
         <v>38</v>
@@ -12314,10 +12320,10 @@
         <v>2024</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H40" s="23">
         <v>26</v>
@@ -12334,22 +12340,22 @@
         <v>39</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E41" s="11">
         <v>2022</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="H41" s="23">
         <v>22</v>
@@ -12366,22 +12372,22 @@
         <v>40</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E42" s="11">
         <v>2024</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="G42" s="12" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="H42" s="23">
         <v>16</v>
@@ -12398,22 +12404,22 @@
         <v>41</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E43" s="8">
         <v>2023</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="H43" s="23">
         <v>28</v>
@@ -12433,16 +12439,16 @@
         <v>32</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E44" s="8">
         <v>2022</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="G44" s="9"/>
       <c r="H44" s="23">
@@ -12460,22 +12466,22 @@
         <v>43</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E45" s="8">
         <v>2025</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="H45" s="23">
         <v>8</v>
@@ -12492,22 +12498,22 @@
         <v>44</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E46" s="8">
         <v>2022</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="H46" s="23">
         <v>22</v>
@@ -12524,22 +12530,22 @@
         <v>45</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E47" s="11">
         <v>2025</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G47" s="12" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="H47" s="23">
         <v>12</v>
@@ -12556,22 +12562,22 @@
         <v>46</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E48" s="11">
         <v>2017</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="G48" s="12" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="H48" s="23">
         <v>36</v>
@@ -12591,19 +12597,19 @@
         <v>52</v>
       </c>
       <c r="C49" s="24" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E49" s="11">
         <v>2026</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="G49" s="12" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="H49" s="23">
         <v>28</v>
@@ -12620,22 +12626,22 @@
         <v>48</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E50" s="11">
         <v>2020</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="G50" s="12" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="H50" s="23">
         <v>18</v>
@@ -12650,7 +12656,7 @@
     <row r="51" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="36" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C52" s="33"/>
       <c r="D52" s="33"/>
@@ -13641,7 +13647,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="34" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
@@ -13659,52 +13665,52 @@
     </row>
     <row r="2" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H2" s="25" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J2" s="25" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="K2" s="25" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L2" s="25" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="M2" s="25" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="N2" s="25" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="O2" s="23" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="P2" s="23" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13712,10 +13718,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D3" s="26"/>
       <c r="E3" s="26"/>
@@ -13755,10 +13761,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D4" s="26">
         <v>10</v>
@@ -13810,10 +13816,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D5" s="26">
         <v>10</v>
@@ -13865,10 +13871,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D6" s="26">
         <v>8</v>
@@ -13920,10 +13926,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D7" s="26"/>
       <c r="E7" s="26"/>
@@ -13966,7 +13972,7 @@
         <v>38</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D8" s="26">
         <v>8</v>
@@ -14018,10 +14024,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D9" s="26">
         <v>10</v>
@@ -14073,10 +14079,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D10" s="26">
         <v>8</v>
@@ -14128,10 +14134,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D11" s="26">
         <v>18</v>
@@ -14183,10 +14189,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D12" s="26">
         <v>10</v>
@@ -14238,10 +14244,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D13" s="26">
         <v>10</v>
@@ -14293,10 +14299,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D14" s="26">
         <v>8</v>
@@ -14348,10 +14354,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D15" s="26"/>
       <c r="E15" s="26"/>
@@ -14394,7 +14400,7 @@
         <v>19</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D16" s="26">
         <v>18</v>
@@ -14446,10 +14452,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D17" s="26">
         <v>10</v>
@@ -14501,10 +14507,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D18" s="26">
         <v>8</v>
@@ -14556,10 +14562,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D19" s="26">
         <v>8</v>
@@ -14611,10 +14617,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D20" s="26">
         <v>10</v>
@@ -14666,10 +14672,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D21" s="26">
         <v>10</v>
@@ -14724,7 +14730,7 @@
         <v>29</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D22" s="26">
         <v>18</v>
@@ -14776,10 +14782,10 @@
         <v>21</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D23" s="26">
         <v>8</v>
@@ -14831,10 +14837,10 @@
         <v>22</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D24" s="26">
         <v>10</v>
@@ -14889,7 +14895,7 @@
         <v>26</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D25" s="26">
         <v>8</v>
@@ -14941,10 +14947,10 @@
         <v>24</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D26" s="26">
         <v>10</v>
@@ -14996,10 +15002,10 @@
         <v>25</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D27" s="26">
         <v>8</v>
@@ -15051,10 +15057,10 @@
         <v>26</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D28" s="26">
         <v>10</v>
@@ -15106,10 +15112,10 @@
         <v>27</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D29" s="26">
         <v>10</v>
@@ -15161,10 +15167,10 @@
         <v>28</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D30" s="26">
         <v>8</v>
@@ -15216,10 +15222,10 @@
         <v>29</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D31" s="26">
         <v>8</v>
@@ -15271,10 +15277,10 @@
         <v>30</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D32" s="26">
         <v>10</v>
@@ -15326,10 +15332,10 @@
         <v>31</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D33" s="26">
         <v>12</v>
@@ -15381,10 +15387,10 @@
         <v>32</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D34" s="26">
         <v>18</v>
@@ -15436,10 +15442,10 @@
         <v>33</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D35" s="26">
         <v>8</v>
@@ -15494,7 +15500,7 @@
         <v>35</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D36" s="26">
         <v>10</v>
@@ -15546,10 +15552,10 @@
         <v>35</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D37" s="26">
         <v>12</v>
@@ -15601,10 +15607,10 @@
         <v>36</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D38" s="26">
         <v>8</v>
@@ -15656,10 +15662,10 @@
         <v>37</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D39" s="26">
         <v>18</v>
@@ -15714,7 +15720,7 @@
         <v>45</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D40" s="26">
         <v>10</v>
@@ -15766,10 +15772,10 @@
         <v>39</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D41" s="26">
         <v>8</v>
@@ -15821,10 +15827,10 @@
         <v>40</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D42" s="26">
         <v>10</v>
@@ -15876,10 +15882,10 @@
         <v>41</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D43" s="26">
         <v>8</v>
@@ -15934,7 +15940,7 @@
         <v>32</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D44" s="26">
         <v>10</v>
@@ -15986,10 +15992,10 @@
         <v>43</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D45" s="26">
         <v>10</v>
@@ -16041,10 +16047,10 @@
         <v>44</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D46" s="26">
         <v>18</v>
@@ -16096,10 +16102,10 @@
         <v>45</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D47" s="26">
         <v>8</v>
@@ -16151,10 +16157,10 @@
         <v>46</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D48" s="26">
         <v>8</v>
@@ -16209,7 +16215,7 @@
         <v>52</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D49" s="26">
         <v>10</v>
@@ -16261,10 +16267,10 @@
         <v>48</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D50" s="26">
         <v>10</v>
@@ -16314,7 +16320,7 @@
     <row r="51" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="32" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C52" s="33"/>
       <c r="D52" s="33"/>
@@ -17307,7 +17313,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="34" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
@@ -17321,34 +17327,34 @@
     </row>
     <row r="2" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="H2" s="25" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="J2" s="25" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17356,10 +17362,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D3" s="26"/>
       <c r="E3" s="26"/>
@@ -17382,10 +17388,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D4" s="26"/>
       <c r="E4" s="26"/>
@@ -17408,10 +17414,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D5" s="26"/>
       <c r="E5" s="26"/>
@@ -17434,10 +17440,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
@@ -17460,10 +17466,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D7" s="26"/>
       <c r="E7" s="26"/>
@@ -17489,7 +17495,7 @@
         <v>38</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D8" s="26"/>
       <c r="E8" s="26"/>
@@ -17512,10 +17518,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D9" s="26"/>
       <c r="E9" s="26"/>
@@ -17538,10 +17544,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D10" s="26"/>
       <c r="E10" s="26"/>
@@ -17564,10 +17570,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D11" s="26"/>
       <c r="E11" s="26"/>
@@ -17590,10 +17596,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D12" s="26"/>
       <c r="E12" s="26"/>
@@ -17616,10 +17622,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D13" s="26"/>
       <c r="E13" s="26"/>
@@ -17642,10 +17648,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D14" s="26"/>
       <c r="E14" s="26"/>
@@ -17668,10 +17674,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D15" s="26"/>
       <c r="E15" s="26"/>
@@ -17697,7 +17703,7 @@
         <v>19</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D16" s="26"/>
       <c r="E16" s="26"/>
@@ -17720,10 +17726,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D17" s="26"/>
       <c r="E17" s="26"/>
@@ -17746,10 +17752,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D18" s="26"/>
       <c r="E18" s="26"/>
@@ -17772,10 +17778,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="26"/>
@@ -17798,10 +17804,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D20" s="26"/>
       <c r="E20" s="26"/>
@@ -17824,10 +17830,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D21" s="26"/>
       <c r="E21" s="26"/>
@@ -17853,7 +17859,7 @@
         <v>29</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D22" s="26"/>
       <c r="E22" s="26"/>
@@ -17876,10 +17882,10 @@
         <v>21</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D23" s="26"/>
       <c r="E23" s="26"/>
@@ -17902,10 +17908,10 @@
         <v>22</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D24" s="26"/>
       <c r="E24" s="26"/>
@@ -17931,7 +17937,7 @@
         <v>26</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D25" s="26"/>
       <c r="E25" s="26"/>
@@ -17954,10 +17960,10 @@
         <v>24</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D26" s="26"/>
       <c r="E26" s="26"/>
@@ -17980,10 +17986,10 @@
         <v>25</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D27" s="26"/>
       <c r="E27" s="26"/>
@@ -18006,10 +18012,10 @@
         <v>26</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="26"/>
@@ -18032,10 +18038,10 @@
         <v>27</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="26"/>
@@ -18058,10 +18064,10 @@
         <v>28</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D30" s="26"/>
       <c r="E30" s="26"/>
@@ -18084,10 +18090,10 @@
         <v>29</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D31" s="26"/>
       <c r="E31" s="26"/>
@@ -18110,10 +18116,10 @@
         <v>30</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D32" s="26"/>
       <c r="E32" s="26"/>
@@ -18136,10 +18142,10 @@
         <v>31</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D33" s="26"/>
       <c r="E33" s="26"/>
@@ -18162,10 +18168,10 @@
         <v>32</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D34" s="26"/>
       <c r="E34" s="26"/>
@@ -18188,10 +18194,10 @@
         <v>33</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D35" s="26"/>
       <c r="E35" s="26"/>
@@ -18217,7 +18223,7 @@
         <v>35</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D36" s="26"/>
       <c r="E36" s="26"/>
@@ -18240,10 +18246,10 @@
         <v>35</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D37" s="26"/>
       <c r="E37" s="26"/>
@@ -18266,10 +18272,10 @@
         <v>36</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D38" s="26"/>
       <c r="E38" s="26"/>
@@ -18292,10 +18298,10 @@
         <v>37</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D39" s="26"/>
       <c r="E39" s="26"/>
@@ -18321,7 +18327,7 @@
         <v>45</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D40" s="26"/>
       <c r="E40" s="26"/>
@@ -18344,10 +18350,10 @@
         <v>39</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D41" s="26"/>
       <c r="E41" s="26"/>
@@ -18370,10 +18376,10 @@
         <v>40</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D42" s="26"/>
       <c r="E42" s="26"/>
@@ -18396,10 +18402,10 @@
         <v>41</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D43" s="26"/>
       <c r="E43" s="26"/>
@@ -18425,7 +18431,7 @@
         <v>32</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D44" s="26"/>
       <c r="E44" s="26"/>
@@ -18448,10 +18454,10 @@
         <v>43</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D45" s="26"/>
       <c r="E45" s="26"/>
@@ -18474,10 +18480,10 @@
         <v>44</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D46" s="26"/>
       <c r="E46" s="26"/>
@@ -18500,10 +18506,10 @@
         <v>45</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D47" s="26"/>
       <c r="E47" s="26"/>
@@ -18526,10 +18532,10 @@
         <v>46</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D48" s="26"/>
       <c r="E48" s="26"/>
@@ -18555,7 +18561,7 @@
         <v>52</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D49" s="26"/>
       <c r="E49" s="26"/>
@@ -18578,10 +18584,10 @@
         <v>48</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D50" s="26"/>
       <c r="E50" s="26"/>
@@ -18602,7 +18608,7 @@
     <row r="51" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="32" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C52" s="33"/>
       <c r="D52" s="33"/>
@@ -19587,7 +19593,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="34" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
@@ -19601,34 +19607,34 @@
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="K2" s="27" t="s">
         <v>8</v>
@@ -19639,16 +19645,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3" s="8">
+        <v>1</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="C3" s="8">
-        <v>1</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>117</v>
-      </c>
       <c r="E3" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F3" s="26">
         <v>2</v>
@@ -19674,16 +19680,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C4" s="11">
         <v>1</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F4" s="28">
         <v>2</v>
@@ -19709,16 +19715,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C5" s="8">
         <v>2</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F5" s="26">
         <v>1</v>
@@ -19744,16 +19750,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C6" s="11">
         <v>2</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F6" s="28">
         <v>1</v>
@@ -19779,16 +19785,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C7" s="8">
         <v>3</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F7" s="26">
         <v>3</v>
@@ -19814,16 +19820,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C8" s="11">
         <v>3</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F8" s="28">
         <v>1</v>
@@ -19849,13 +19855,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="C9" s="8">
+        <v>1</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>134</v>
-      </c>
-      <c r="C9" s="8">
-        <v>1</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>132</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>38</v>
@@ -19884,16 +19890,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C10" s="11">
         <v>1</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F10" s="28">
         <v>1</v>
@@ -19919,16 +19925,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C11" s="8">
         <v>2</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F11" s="26">
         <v>6</v>
@@ -19954,7 +19960,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C12" s="11">
         <v>2</v>
@@ -19963,7 +19969,7 @@
         <v>38</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F12" s="28">
         <v>1</v>
@@ -19989,16 +19995,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C13" s="8">
         <v>3</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F13" s="26">
         <v>1</v>
@@ -20024,7 +20030,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C14" s="11">
         <v>3</v>
@@ -20033,7 +20039,7 @@
         <v>38</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F14" s="28">
         <v>3</v>
@@ -20059,16 +20065,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C15" s="8">
+        <v>1</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="C15" s="8">
-        <v>1</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>140</v>
-      </c>
       <c r="E15" s="9" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F15" s="26">
         <v>1</v>
@@ -20094,16 +20100,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C16" s="11">
         <v>1</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F16" s="28">
         <v>0</v>
@@ -20129,16 +20135,16 @@
         <v>15</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C17" s="8">
         <v>2</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F17" s="26">
         <v>3</v>
@@ -20164,16 +20170,16 @@
         <v>16</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C18" s="11">
         <v>2</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F18" s="28">
         <v>1</v>
@@ -20199,16 +20205,16 @@
         <v>17</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C19" s="8">
         <v>3</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F19" s="26">
         <v>3</v>
@@ -20234,16 +20240,16 @@
         <v>18</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C20" s="11">
         <v>3</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F20" s="28">
         <v>4</v>
@@ -20269,13 +20275,13 @@
         <v>19</v>
       </c>
       <c r="B21" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C21" s="8">
+        <v>1</v>
+      </c>
+      <c r="D21" s="9" t="s">
         <v>152</v>
-      </c>
-      <c r="C21" s="8">
-        <v>1</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>150</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>19</v>
@@ -20304,16 +20310,16 @@
         <v>20</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C22" s="11">
         <v>1</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F22" s="28">
         <v>2</v>
@@ -20339,16 +20345,16 @@
         <v>21</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C23" s="8">
         <v>2</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F23" s="26">
         <v>2</v>
@@ -20374,7 +20380,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C24" s="11">
         <v>2</v>
@@ -20383,7 +20389,7 @@
         <v>19</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F24" s="28">
         <v>1</v>
@@ -20409,16 +20415,16 @@
         <v>23</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C25" s="8">
         <v>3</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F25" s="26">
         <v>2</v>
@@ -20444,7 +20450,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C26" s="11">
         <v>3</v>
@@ -20453,7 +20459,7 @@
         <v>19</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F26" s="28">
         <v>0</v>
@@ -20479,16 +20485,16 @@
         <v>25</v>
       </c>
       <c r="B27" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="C27" s="8">
+        <v>1</v>
+      </c>
+      <c r="D27" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="C27" s="8">
-        <v>1</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>158</v>
-      </c>
       <c r="E27" s="9" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F27" s="26">
         <v>7</v>
@@ -20514,13 +20520,13 @@
         <v>26</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C28" s="11">
         <v>1</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E28" s="12" t="s">
         <v>29</v>
@@ -20549,16 +20555,16 @@
         <v>27</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C29" s="8">
         <v>2</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F29" s="26">
         <v>2</v>
@@ -20584,13 +20590,13 @@
         <v>28</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C30" s="11">
         <v>2</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E30" s="12" t="s">
         <v>29</v>
@@ -20619,13 +20625,13 @@
         <v>29</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C31" s="8">
         <v>3</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>29</v>
@@ -20654,16 +20660,16 @@
         <v>30</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C32" s="11">
         <v>3</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F32" s="28">
         <v>0</v>
@@ -20689,16 +20695,16 @@
         <v>31</v>
       </c>
       <c r="B33" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="C33" s="8">
+        <v>1</v>
+      </c>
+      <c r="D33" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="C33" s="8">
-        <v>1</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>166</v>
-      </c>
       <c r="E33" s="9" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F33" s="26">
         <v>2</v>
@@ -20724,7 +20730,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C34" s="11">
         <v>1</v>
@@ -20733,7 +20739,7 @@
         <v>26</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F34" s="28">
         <v>5</v>
@@ -20759,13 +20765,13 @@
         <v>33</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C35" s="8">
         <v>2</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>26</v>
@@ -20794,16 +20800,16 @@
         <v>34</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C36" s="11">
         <v>2</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F36" s="28">
         <v>4</v>
@@ -20829,16 +20835,16 @@
         <v>35</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C37" s="8">
         <v>3</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F37" s="26">
         <v>3</v>
@@ -20864,13 +20870,13 @@
         <v>36</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C38" s="11">
         <v>3</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E38" s="12" t="s">
         <v>26</v>
@@ -20899,16 +20905,16 @@
         <v>37</v>
       </c>
       <c r="B39" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="C39" s="8">
+        <v>1</v>
+      </c>
+      <c r="D39" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="C39" s="8">
-        <v>1</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>174</v>
-      </c>
       <c r="E39" s="9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F39" s="26">
         <v>1</v>
@@ -20934,16 +20940,16 @@
         <v>38</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C40" s="11">
         <v>1</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F40" s="28">
         <v>2</v>
@@ -20969,16 +20975,16 @@
         <v>39</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C41" s="8">
         <v>2</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F41" s="26">
         <v>0</v>
@@ -21004,16 +21010,16 @@
         <v>40</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C42" s="11">
         <v>2</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F42" s="28">
         <v>3</v>
@@ -21039,16 +21045,16 @@
         <v>41</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C43" s="8">
         <v>3</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F43" s="26">
         <v>5</v>
@@ -21074,16 +21080,16 @@
         <v>42</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C44" s="11">
         <v>3</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F44" s="28">
         <v>1</v>
@@ -21109,16 +21115,16 @@
         <v>43</v>
       </c>
       <c r="B45" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="C45" s="8">
+        <v>1</v>
+      </c>
+      <c r="D45" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="C45" s="8">
-        <v>1</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>184</v>
-      </c>
       <c r="E45" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F45" s="26">
         <v>0</v>
@@ -21144,16 +21150,16 @@
         <v>44</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C46" s="11">
         <v>1</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F46" s="28">
         <v>1</v>
@@ -21179,16 +21185,16 @@
         <v>45</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C47" s="8">
         <v>2</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F47" s="26">
         <v>4</v>
@@ -21214,16 +21220,16 @@
         <v>46</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C48" s="11">
         <v>2</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F48" s="28">
         <v>2</v>
@@ -21249,16 +21255,16 @@
         <v>47</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C49" s="8">
         <v>3</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F49" s="26">
         <v>1</v>
@@ -21284,16 +21290,16 @@
         <v>48</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C50" s="11">
         <v>3</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F50" s="28">
         <v>0</v>
@@ -21319,13 +21325,13 @@
         <v>49</v>
       </c>
       <c r="B51" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="C51" s="8">
+        <v>1</v>
+      </c>
+      <c r="D51" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="C51" s="8">
-        <v>1</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>193</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>35</v>
@@ -21354,16 +21360,16 @@
         <v>50</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C52" s="11">
         <v>1</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F52" s="28">
         <v>1</v>
@@ -21389,16 +21395,16 @@
         <v>51</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C53" s="8">
         <v>2</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F53" s="26">
         <v>3</v>
@@ -21424,7 +21430,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C54" s="11">
         <v>2</v>
@@ -21433,7 +21439,7 @@
         <v>35</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F54" s="28">
         <v>2</v>
@@ -21459,16 +21465,16 @@
         <v>53</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C55" s="8">
         <v>3</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F55" s="26">
         <v>4</v>
@@ -21494,7 +21500,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C56" s="11">
         <v>3</v>
@@ -21503,7 +21509,7 @@
         <v>35</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F56" s="28">
         <v>5</v>
@@ -21529,13 +21535,13 @@
         <v>55</v>
       </c>
       <c r="B57" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="C57" s="8">
+        <v>1</v>
+      </c>
+      <c r="D57" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="C57" s="8">
-        <v>1</v>
-      </c>
-      <c r="D57" s="9" t="s">
-        <v>201</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>45</v>
@@ -21564,16 +21570,16 @@
         <v>56</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C58" s="11">
         <v>1</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F58" s="28">
         <v>3</v>
@@ -21599,16 +21605,16 @@
         <v>57</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C59" s="8">
         <v>2</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F59" s="26">
         <v>2</v>
@@ -21634,7 +21640,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C60" s="11">
         <v>2</v>
@@ -21643,7 +21649,7 @@
         <v>45</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F60" s="28">
         <v>2</v>
@@ -21669,16 +21675,16 @@
         <v>59</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C61" s="8">
         <v>3</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F61" s="26">
         <v>3</v>
@@ -21704,7 +21710,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C62" s="11">
         <v>3</v>
@@ -21713,7 +21719,7 @@
         <v>45</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F62" s="28">
         <v>3</v>
@@ -21739,13 +21745,13 @@
         <v>61</v>
       </c>
       <c r="B63" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="C63" s="8">
+        <v>1</v>
+      </c>
+      <c r="D63" s="9" t="s">
         <v>211</v>
-      </c>
-      <c r="C63" s="8">
-        <v>1</v>
-      </c>
-      <c r="D63" s="9" t="s">
-        <v>209</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>32</v>
@@ -21774,16 +21780,16 @@
         <v>62</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C64" s="11">
         <v>1</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F64" s="28">
         <v>1</v>
@@ -21809,16 +21815,16 @@
         <v>63</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C65" s="8">
         <v>2</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F65" s="26">
         <v>5</v>
@@ -21844,7 +21850,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C66" s="11">
         <v>2</v>
@@ -21853,7 +21859,7 @@
         <v>32</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F66" s="28">
         <v>0</v>
@@ -21879,16 +21885,16 @@
         <v>65</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C67" s="8">
         <v>3</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F67" s="26">
         <v>0</v>
@@ -21897,11 +21903,11 @@
         <v>0</v>
       </c>
       <c r="H67" s="8">
-        <f t="shared" ref="H67:H74" si="6">IF(AND(ISNUMBER(F67),ISNUMBER(G67)),1,0)</f>
+        <f t="shared" ref="H67:H98" si="6">IF(AND(ISNUMBER(F67),ISNUMBER(G67)),1,0)</f>
         <v>1</v>
       </c>
       <c r="I67" s="8">
-        <f t="shared" ref="I67:I74" si="7">IF(H67=1,IF(F67&gt;G67,3,IF(F67=G67,1,0)),"")</f>
+        <f t="shared" ref="I67:I98" si="7">IF(H67=1,IF(F67&gt;G67,3,IF(F67=G67,1,0)),"")</f>
         <v>1</v>
       </c>
       <c r="J67" s="8">
@@ -21914,7 +21920,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C68" s="11">
         <v>3</v>
@@ -21923,7 +21929,7 @@
         <v>32</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F68" s="28">
         <v>3</v>
@@ -21949,16 +21955,16 @@
         <v>67</v>
       </c>
       <c r="B69" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="C69" s="8">
+        <v>1</v>
+      </c>
+      <c r="D69" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="C69" s="8">
-        <v>1</v>
-      </c>
-      <c r="D69" s="9" t="s">
-        <v>217</v>
-      </c>
       <c r="E69" s="9" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F69" s="26">
         <v>4</v>
@@ -21984,7 +21990,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C70" s="11">
         <v>1</v>
@@ -21993,7 +21999,7 @@
         <v>52</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F70" s="28">
         <v>1</v>
@@ -22019,13 +22025,13 @@
         <v>69</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C71" s="8">
         <v>2</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>52</v>
@@ -22054,16 +22060,16 @@
         <v>70</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C72" s="11">
         <v>2</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F72" s="28">
         <v>1</v>
@@ -22089,16 +22095,16 @@
         <v>71</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C73" s="8">
         <v>3</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F73" s="26">
         <v>2</v>
@@ -22124,13 +22130,13 @@
         <v>72</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C74" s="11">
         <v>3</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E74" s="12" t="s">
         <v>52</v>
@@ -23105,7 +23111,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="34" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
@@ -23121,51 +23127,51 @@
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>449</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>108</v>
-      </c>
       <c r="D2" s="7" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="B3" s="8">
+        <v>1</v>
+      </c>
+      <c r="C3" s="29" t="s">
         <v>119</v>
-      </c>
-      <c r="B3" s="8">
-        <v>1</v>
-      </c>
-      <c r="C3" s="29" t="s">
-        <v>117</v>
       </c>
       <c r="D3" s="8">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C3)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C3)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -23206,13 +23212,13 @@
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B4" s="8">
         <v>2</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D4" s="8">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C4)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C4)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -23253,13 +23259,13 @@
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B5" s="8">
         <v>3</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D5" s="8">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C5)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C5)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -23300,13 +23306,13 @@
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B6" s="8">
         <v>4</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D6" s="8">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C6)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C6)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -23347,13 +23353,13 @@
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="B7" s="11">
+        <v>1</v>
+      </c>
+      <c r="C7" s="30" t="s">
         <v>134</v>
-      </c>
-      <c r="B7" s="11">
-        <v>1</v>
-      </c>
-      <c r="C7" s="30" t="s">
-        <v>132</v>
       </c>
       <c r="D7" s="11">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C7)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C7)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -23394,7 +23400,7 @@
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B8" s="11">
         <v>2</v>
@@ -23441,13 +23447,13 @@
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B9" s="11">
         <v>3</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D9" s="11">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C9)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C9)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -23488,13 +23494,13 @@
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B10" s="11">
         <v>4</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D10" s="11">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C10)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C10)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -23535,13 +23541,13 @@
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="B11" s="8">
+        <v>1</v>
+      </c>
+      <c r="C11" s="29" t="s">
         <v>142</v>
-      </c>
-      <c r="B11" s="8">
-        <v>1</v>
-      </c>
-      <c r="C11" s="29" t="s">
-        <v>140</v>
       </c>
       <c r="D11" s="8">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C11)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C11)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -23582,13 +23588,13 @@
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B12" s="8">
         <v>2</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D12" s="8">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C12)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C12)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -23629,13 +23635,13 @@
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B13" s="8">
         <v>3</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D13" s="8">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C13)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C13)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -23676,13 +23682,13 @@
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B14" s="8">
         <v>4</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D14" s="8">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C14)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C14)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -23723,13 +23729,13 @@
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="B15" s="11">
+        <v>1</v>
+      </c>
+      <c r="C15" s="30" t="s">
         <v>152</v>
-      </c>
-      <c r="B15" s="11">
-        <v>1</v>
-      </c>
-      <c r="C15" s="30" t="s">
-        <v>150</v>
       </c>
       <c r="D15" s="11">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C15)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C15)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -23770,7 +23776,7 @@
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B16" s="11">
         <v>2</v>
@@ -23817,13 +23823,13 @@
     </row>
     <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B17" s="11">
         <v>3</v>
       </c>
       <c r="C17" s="30" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D17" s="11">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C17)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C17)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -23864,13 +23870,13 @@
     </row>
     <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B18" s="11">
         <v>4</v>
       </c>
       <c r="C18" s="30" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D18" s="11">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C18)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C18)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -23911,13 +23917,13 @@
     </row>
     <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="B19" s="8">
+        <v>1</v>
+      </c>
+      <c r="C19" s="29" t="s">
         <v>160</v>
-      </c>
-      <c r="B19" s="8">
-        <v>1</v>
-      </c>
-      <c r="C19" s="29" t="s">
-        <v>158</v>
       </c>
       <c r="D19" s="8">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C19)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C19)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -23958,13 +23964,13 @@
     </row>
     <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B20" s="8">
         <v>2</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D20" s="8">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C20)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C20)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -24005,13 +24011,13 @@
     </row>
     <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B21" s="8">
         <v>3</v>
       </c>
       <c r="C21" s="29" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D21" s="8">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C21)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C21)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -24052,7 +24058,7 @@
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B22" s="8">
         <v>4</v>
@@ -24099,13 +24105,13 @@
     </row>
     <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="B23" s="11">
+        <v>1</v>
+      </c>
+      <c r="C23" s="30" t="s">
         <v>168</v>
-      </c>
-      <c r="B23" s="11">
-        <v>1</v>
-      </c>
-      <c r="C23" s="30" t="s">
-        <v>166</v>
       </c>
       <c r="D23" s="11">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C23)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C23)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -24146,13 +24152,13 @@
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B24" s="11">
         <v>2</v>
       </c>
       <c r="C24" s="30" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D24" s="11">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C24)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C24)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -24193,7 +24199,7 @@
     </row>
     <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B25" s="11">
         <v>3</v>
@@ -24240,13 +24246,13 @@
     </row>
     <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B26" s="11">
         <v>4</v>
       </c>
       <c r="C26" s="30" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D26" s="11">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C26)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C26)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -24287,13 +24293,13 @@
     </row>
     <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="B27" s="8">
+        <v>1</v>
+      </c>
+      <c r="C27" s="29" t="s">
         <v>176</v>
-      </c>
-      <c r="B27" s="8">
-        <v>1</v>
-      </c>
-      <c r="C27" s="29" t="s">
-        <v>174</v>
       </c>
       <c r="D27" s="8">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C27)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C27)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -24334,13 +24340,13 @@
     </row>
     <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B28" s="8">
         <v>2</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D28" s="8">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C28)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C28)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -24381,13 +24387,13 @@
     </row>
     <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B29" s="8">
         <v>3</v>
       </c>
       <c r="C29" s="29" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D29" s="8">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C29)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C29)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -24428,13 +24434,13 @@
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B30" s="8">
         <v>4</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D30" s="8">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C30)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C30)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -24475,13 +24481,13 @@
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="B31" s="11">
+        <v>1</v>
+      </c>
+      <c r="C31" s="30" t="s">
         <v>186</v>
-      </c>
-      <c r="B31" s="11">
-        <v>1</v>
-      </c>
-      <c r="C31" s="30" t="s">
-        <v>184</v>
       </c>
       <c r="D31" s="11">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C31)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C31)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -24522,13 +24528,13 @@
     </row>
     <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B32" s="11">
         <v>2</v>
       </c>
       <c r="C32" s="30" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D32" s="11">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C32)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C32)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -24569,13 +24575,13 @@
     </row>
     <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B33" s="11">
         <v>3</v>
       </c>
       <c r="C33" s="30" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D33" s="11">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C33)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C33)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -24616,13 +24622,13 @@
     </row>
     <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B34" s="11">
         <v>4</v>
       </c>
       <c r="C34" s="30" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D34" s="11">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C34)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C34)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -24663,13 +24669,13 @@
     </row>
     <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="B35" s="8">
+        <v>1</v>
+      </c>
+      <c r="C35" s="29" t="s">
         <v>195</v>
-      </c>
-      <c r="B35" s="8">
-        <v>1</v>
-      </c>
-      <c r="C35" s="29" t="s">
-        <v>193</v>
       </c>
       <c r="D35" s="8">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C35)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C35)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -24710,7 +24716,7 @@
     </row>
     <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B36" s="8">
         <v>2</v>
@@ -24757,13 +24763,13 @@
     </row>
     <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B37" s="8">
         <v>3</v>
       </c>
       <c r="C37" s="29" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D37" s="8">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C37)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C37)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -24804,13 +24810,13 @@
     </row>
     <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B38" s="8">
         <v>4</v>
       </c>
       <c r="C38" s="29" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D38" s="8">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C38)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C38)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -24851,13 +24857,13 @@
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="B39" s="11">
+        <v>1</v>
+      </c>
+      <c r="C39" s="30" t="s">
         <v>203</v>
-      </c>
-      <c r="B39" s="11">
-        <v>1</v>
-      </c>
-      <c r="C39" s="30" t="s">
-        <v>201</v>
       </c>
       <c r="D39" s="11">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C39)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C39)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -24898,7 +24904,7 @@
     </row>
     <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B40" s="11">
         <v>2</v>
@@ -24945,13 +24951,13 @@
     </row>
     <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B41" s="11">
         <v>3</v>
       </c>
       <c r="C41" s="30" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D41" s="11">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C41)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C41)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -24992,13 +24998,13 @@
     </row>
     <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B42" s="11">
         <v>4</v>
       </c>
       <c r="C42" s="30" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D42" s="11">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C42)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C42)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -25039,13 +25045,13 @@
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="B43" s="8">
+        <v>1</v>
+      </c>
+      <c r="C43" s="29" t="s">
         <v>211</v>
-      </c>
-      <c r="B43" s="8">
-        <v>1</v>
-      </c>
-      <c r="C43" s="29" t="s">
-        <v>209</v>
       </c>
       <c r="D43" s="8">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C43)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C43)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -25086,7 +25092,7 @@
     </row>
     <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B44" s="8">
         <v>2</v>
@@ -25133,13 +25139,13 @@
     </row>
     <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B45" s="8">
         <v>3</v>
       </c>
       <c r="C45" s="29" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D45" s="8">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C45)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C45)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -25180,13 +25186,13 @@
     </row>
     <row r="46" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B46" s="8">
         <v>4</v>
       </c>
       <c r="C46" s="29" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D46" s="8">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C46)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C46)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -25227,13 +25233,13 @@
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="B47" s="11">
+        <v>1</v>
+      </c>
+      <c r="C47" s="30" t="s">
         <v>219</v>
-      </c>
-      <c r="B47" s="11">
-        <v>1</v>
-      </c>
-      <c r="C47" s="30" t="s">
-        <v>217</v>
       </c>
       <c r="D47" s="11">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C47)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C47)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -25274,13 +25280,13 @@
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B48" s="11">
         <v>2</v>
       </c>
       <c r="C48" s="30" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D48" s="11">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C48)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C48)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -25321,7 +25327,7 @@
     </row>
     <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B49" s="11">
         <v>3</v>
@@ -25368,13 +25374,13 @@
     </row>
     <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B50" s="11">
         <v>4</v>
       </c>
       <c r="C50" s="30" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D50" s="11">
         <f>SUMPRODUCT((Fixture_Grupos!$D$3:$D$74=$C50)*Fixture_Grupos!$H$3:$H$74)+SUMPRODUCT((Fixture_Grupos!$E$3:$E$74=$C50)*Fixture_Grupos!$H$3:$H$74)</f>
@@ -25416,7 +25422,7 @@
     <row r="51" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="32" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B52" s="33"/>
       <c r="C52" s="33"/>
@@ -26964,11 +26970,23 @@
       <c r="B19" s="8">
         <v>1</v>
       </c>
-      <c r="C19" s="31"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
+      <c r="C19" s="31" t="str">
+        <f>IF(OR(C5="",F5=""),"",IF(OR(D5="",E5=""),"",IF(D5&gt;E5,C5,IF(D5&lt;E5,F5,IF(AND(K5&lt;&gt;"",L5&lt;&gt;""),IF(K5&gt;L5,C5,F5),"")))))</f>
+        <v>Paraguay</v>
+      </c>
+      <c r="D19" s="26">
+        <v>0</v>
+      </c>
+      <c r="E19" s="26">
+        <v>1</v>
+      </c>
+      <c r="F19" s="31" t="str">
+        <f>IF(OR(C8="",F8=""),"",IF(OR(D8="",E8=""),"",IF(D8&gt;E8,C8,IF(D8&lt;E8,F8,IF(AND(K8&lt;&gt;"",L8&lt;&gt;""),IF(K8&gt;L8,C8,F8),"")))))</f>
+        <v>Francia</v>
+      </c>
+      <c r="G19" s="31" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
@@ -26977,11 +26995,23 @@
       <c r="B20" s="8">
         <v>2</v>
       </c>
-      <c r="C20" s="31"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
+      <c r="C20" s="31" t="str">
+        <f>IF(OR(C3="",F3=""),"",IF(OR(D3="",E3=""),"",IF(D3&gt;E3,C3,IF(D3&lt;E3,F3,IF(AND(K3&lt;&gt;"",L3&lt;&gt;""),IF(K3&gt;L3,C3,F3),"")))))</f>
+        <v>Canadá</v>
+      </c>
+      <c r="D20" s="26">
+        <v>0</v>
+      </c>
+      <c r="E20" s="26">
+        <v>3</v>
+      </c>
+      <c r="F20" s="31" t="str">
+        <f>IF(OR(C6="",F6=""),"",IF(OR(D6="",E6=""),"",IF(D6&gt;E6,C6,IF(D6&lt;E6,F6,IF(AND(K6&lt;&gt;"",L6&lt;&gt;""),IF(K6&gt;L6,C6,F6),"")))))</f>
+        <v>Marruecos</v>
+      </c>
+      <c r="G20" s="31" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
@@ -26990,11 +27020,19 @@
       <c r="B21" s="8">
         <v>3</v>
       </c>
-      <c r="C21" s="31"/>
+      <c r="C21" s="31" t="str">
+        <f>IF(OR(C14="",F14=""),"",IF(OR(D14="",E14=""),"",IF(D14&gt;E14,C14,IF(D14&lt;E14,F14,IF(AND(K14&lt;&gt;"",L14&lt;&gt;""),IF(K14&gt;L14,C14,F14),"")))))</f>
+        <v>Portugal</v>
+      </c>
       <c r="D21" s="26"/>
       <c r="E21" s="26"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
+      <c r="F21" s="31" t="str">
+        <f>IF(OR(C13="",F13=""),"",IF(OR(D13="",E13=""),"",IF(D13&gt;E13,C13,IF(D13&lt;E13,F13,IF(AND(K13&lt;&gt;"",L13&lt;&gt;""),IF(K13&gt;L13,C13,F13),"")))))</f>
+        <v>España</v>
+      </c>
+      <c r="G21" s="31" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
@@ -27003,11 +27041,19 @@
       <c r="B22" s="8">
         <v>4</v>
       </c>
-      <c r="C22" s="31"/>
+      <c r="C22" s="31" t="str">
+        <f>IF(OR(C12="",F12=""),"",IF(OR(D12="",E12=""),"",IF(D12&gt;E12,C12,IF(D12&lt;E12,F12,IF(AND(K12&lt;&gt;"",L12&lt;&gt;""),IF(K12&gt;L12,C12,F12),"")))))</f>
+        <v>Estados Unidos</v>
+      </c>
       <c r="D22" s="26"/>
       <c r="E22" s="26"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
+      <c r="F22" s="31" t="str">
+        <f>IF(OR(C11="",F11=""),"",IF(OR(D11="",E11=""),"",IF(D11&gt;E11,C11,IF(D11&lt;E11,F11,IF(AND(K11&lt;&gt;"",L11&lt;&gt;""),IF(K11&gt;L11,C11,F11),"")))))</f>
+        <v>Bélgica</v>
+      </c>
+      <c r="G22" s="31" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
@@ -27016,11 +27062,23 @@
       <c r="B23" s="8">
         <v>5</v>
       </c>
-      <c r="C23" s="31"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="31"/>
+      <c r="C23" s="31" t="str">
+        <f>IF(OR(C4="",F4=""),"",IF(OR(D4="",E4=""),"",IF(D4&gt;E4,C4,IF(D4&lt;E4,F4,IF(AND(K4&lt;&gt;"",L4&lt;&gt;""),IF(K4&gt;L4,C4,F4),"")))))</f>
+        <v>Brasil</v>
+      </c>
+      <c r="D23" s="26">
+        <v>1</v>
+      </c>
+      <c r="E23" s="26">
+        <v>2</v>
+      </c>
+      <c r="F23" s="31" t="str">
+        <f>IF(OR(C7="",F7=""),"",IF(OR(D7="",E7=""),"",IF(D7&gt;E7,C7,IF(D7&lt;E7,F7,IF(AND(K7&lt;&gt;"",L7&lt;&gt;""),IF(K7&gt;L7,C7,F7),"")))))</f>
+        <v>Noruega</v>
+      </c>
+      <c r="G23" s="31" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
@@ -27029,11 +27087,23 @@
       <c r="B24" s="8">
         <v>6</v>
       </c>
-      <c r="C24" s="31"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="31"/>
+      <c r="C24" s="31" t="str">
+        <f>IF(OR(C9="",F9=""),"",IF(OR(D9="",E9=""),"",IF(D9&gt;E9,C9,IF(D9&lt;E9,F9,IF(AND(K9&lt;&gt;"",L9&lt;&gt;""),IF(K9&gt;L9,C9,F9),"")))))</f>
+        <v>México</v>
+      </c>
+      <c r="D24" s="26">
+        <v>2</v>
+      </c>
+      <c r="E24" s="26">
+        <v>3</v>
+      </c>
+      <c r="F24" s="31" t="str">
+        <f>IF(OR(C10="",F10=""),"",IF(OR(D10="",E10=""),"",IF(D10&gt;E10,C10,IF(D10&lt;E10,F10,IF(AND(K10&lt;&gt;"",L10&lt;&gt;""),IF(K10&gt;L10,C10,F10),"")))))</f>
+        <v>Inglaterra</v>
+      </c>
+      <c r="G24" s="31" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
@@ -27042,11 +27112,19 @@
       <c r="B25" s="8">
         <v>7</v>
       </c>
-      <c r="C25" s="31"/>
+      <c r="C25" s="31" t="str">
+        <f>IF(OR(C17="",F17=""),"",IF(OR(D17="",E17=""),"",IF(D17&gt;E17,C17,IF(D17&lt;E17,F17,IF(AND(K17&lt;&gt;"",L17&lt;&gt;""),IF(K17&gt;L17,C17,F17),"")))))</f>
+        <v>Argentina</v>
+      </c>
       <c r="D25" s="26"/>
       <c r="E25" s="26"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
+      <c r="F25" s="31" t="str">
+        <f>IF(OR(C16="",F16=""),"",IF(OR(D16="",E16=""),"",IF(D16&gt;E16,C16,IF(D16&lt;E16,F16,IF(AND(K16&lt;&gt;"",L16&lt;&gt;""),IF(K16&gt;L16,C16,F16),"")))))</f>
+        <v>Egipto</v>
+      </c>
+      <c r="G25" s="31" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
@@ -27055,120 +27133,192 @@
       <c r="B26" s="8">
         <v>8</v>
       </c>
-      <c r="C26" s="31"/>
+      <c r="C26" s="31" t="str">
+        <f>IF(OR(C15="",F15=""),"",IF(OR(D15="",E15=""),"",IF(D15&gt;E15,C15,IF(D15&lt;E15,F15,IF(AND(K15&lt;&gt;"",L15&lt;&gt;""),IF(K15&gt;L15,C15,F15),"")))))</f>
+        <v>Suiza</v>
+      </c>
       <c r="D26" s="26"/>
       <c r="E26" s="26"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
+      <c r="F26" s="31" t="str">
+        <f>IF(OR(C18="",F18=""),"",IF(OR(D18="",E18=""),"",IF(D18&gt;E18,C18,IF(D18&lt;E18,F18,IF(AND(K18&lt;&gt;"",L18&lt;&gt;""),IF(K18&gt;L18,C18,F18),"")))))</f>
+        <v>Colombia</v>
+      </c>
+      <c r="G26" s="31" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B27" s="8">
         <v>1</v>
       </c>
-      <c r="C27" s="31"/>
+      <c r="C27" s="31" t="str">
+        <f>IF(OR(C19="",F19=""),"",IF(OR(D19="",E19=""),"",IF(D19&gt;E19,C19,IF(D19&lt;E19,F19,IF(AND(K19&lt;&gt;"",L19&lt;&gt;""),IF(K19&gt;L19,C19,F19),"")))))</f>
+        <v>Francia</v>
+      </c>
       <c r="D27" s="26"/>
       <c r="E27" s="26"/>
-      <c r="F27" s="31"/>
-      <c r="G27" s="31"/>
+      <c r="F27" s="31" t="str">
+        <f>IF(OR(C20="",F20=""),"",IF(OR(D20="",E20=""),"",IF(D20&gt;E20,C20,IF(D20&lt;E20,F20,IF(AND(K20&lt;&gt;"",L20&lt;&gt;""),IF(K20&gt;L20,C20,F20),"")))))</f>
+        <v>Marruecos</v>
+      </c>
+      <c r="G27" s="31" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B28" s="8">
         <v>2</v>
       </c>
-      <c r="C28" s="31"/>
+      <c r="C28" s="31" t="str">
+        <f>IF(OR(C21="",F21=""),"",IF(OR(D21="",E21=""),"",IF(D21&gt;E21,C21,IF(D21&lt;E21,F21,IF(AND(K21&lt;&gt;"",L21&lt;&gt;""),IF(K21&gt;L21,C21,F21),"")))))</f>
+        <v/>
+      </c>
       <c r="D28" s="26"/>
       <c r="E28" s="26"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
+      <c r="F28" s="31" t="str">
+        <f>IF(OR(C22="",F22=""),"",IF(OR(D22="",E22=""),"",IF(D22&gt;E22,C22,IF(D22&lt;E22,F22,IF(AND(K22&lt;&gt;"",L22&lt;&gt;""),IF(K22&gt;L22,C22,F22),"")))))</f>
+        <v/>
+      </c>
+      <c r="G28" s="31" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B29" s="8">
         <v>3</v>
       </c>
-      <c r="C29" s="31"/>
+      <c r="C29" s="31" t="str">
+        <f>IF(OR(C23="",F23=""),"",IF(OR(D23="",E23=""),"",IF(D23&gt;E23,C23,IF(D23&lt;E23,F23,IF(AND(K23&lt;&gt;"",L23&lt;&gt;""),IF(K23&gt;L23,C23,F23),"")))))</f>
+        <v>Noruega</v>
+      </c>
       <c r="D29" s="26"/>
       <c r="E29" s="26"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="31"/>
+      <c r="F29" s="31" t="str">
+        <f>IF(OR(C24="",F24=""),"",IF(OR(D24="",E24=""),"",IF(D24&gt;E24,C24,IF(D24&lt;E24,F24,IF(AND(K24&lt;&gt;"",L24&lt;&gt;""),IF(K24&gt;L24,C24,F24),"")))))</f>
+        <v>Inglaterra</v>
+      </c>
+      <c r="G29" s="31" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B30" s="8">
         <v>4</v>
       </c>
-      <c r="C30" s="31"/>
+      <c r="C30" s="31" t="str">
+        <f>IF(OR(C25="",F25=""),"",IF(OR(D25="",E25=""),"",IF(D25&gt;E25,C25,IF(D25&lt;E25,F25,IF(AND(K25&lt;&gt;"",L25&lt;&gt;""),IF(K25&gt;L25,C25,F25),"")))))</f>
+        <v/>
+      </c>
       <c r="D30" s="26"/>
       <c r="E30" s="26"/>
-      <c r="F30" s="31"/>
-      <c r="G30" s="31"/>
+      <c r="F30" s="31" t="str">
+        <f>IF(OR(C26="",F26=""),"",IF(OR(D26="",E26=""),"",IF(D26&gt;E26,C26,IF(D26&lt;E26,F26,IF(AND(K26&lt;&gt;"",L26&lt;&gt;""),IF(K26&gt;L26,C26,F26),"")))))</f>
+        <v/>
+      </c>
+      <c r="G30" s="31" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B31" s="8">
         <v>1</v>
       </c>
-      <c r="C31" s="31"/>
+      <c r="C31" s="31" t="str">
+        <f>IF(OR(C27="",F27=""),"",IF(OR(D27="",E27=""),"",IF(D27&gt;E27,C27,IF(D27&lt;E27,F27,IF(AND(K27&lt;&gt;"",L27&lt;&gt;""),IF(K27&gt;L27,C27,F27),"")))))</f>
+        <v/>
+      </c>
       <c r="D31" s="26"/>
       <c r="E31" s="26"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="31"/>
+      <c r="F31" s="31" t="str">
+        <f>IF(OR(C28="",F28=""),"",IF(OR(D28="",E28=""),"",IF(D28&gt;E28,C28,IF(D28&lt;E28,F28,IF(AND(K28&lt;&gt;"",L28&lt;&gt;""),IF(K28&gt;L28,C28,F28),"")))))</f>
+        <v/>
+      </c>
+      <c r="G31" s="31" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B32" s="8">
         <v>2</v>
       </c>
-      <c r="C32" s="31"/>
+      <c r="C32" s="31" t="str">
+        <f>IF(OR(C29="",F29=""),"",IF(OR(D29="",E29=""),"",IF(D29&gt;E29,C29,IF(D29&lt;E29,F29,IF(AND(K29&lt;&gt;"",L29&lt;&gt;""),IF(K29&gt;L29,C29,F29),"")))))</f>
+        <v/>
+      </c>
       <c r="D32" s="26"/>
       <c r="E32" s="26"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
+      <c r="F32" s="31" t="str">
+        <f>IF(OR(C30="",F30=""),"",IF(OR(D30="",E30=""),"",IF(D30&gt;E30,C30,IF(D30&lt;E30,F30,IF(AND(K30&lt;&gt;"",L30&lt;&gt;""),IF(K30&gt;L30,C30,F30),"")))))</f>
+        <v/>
+      </c>
+      <c r="G32" s="31" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="33" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B33" s="8">
         <v>1</v>
       </c>
-      <c r="C33" s="31"/>
+      <c r="C33" s="31" t="str">
+        <f>IF(OR(C31="",F31=""),"",IF(OR(D31="",E31=""),"",IF(D31&gt;E31,F31,IF(D31&lt;E31,C31,IF(AND(K31&lt;&gt;"",L31&lt;&gt;""),IF(K31&gt;L31,F31,C31),"")))))</f>
+        <v/>
+      </c>
       <c r="D33" s="26"/>
       <c r="E33" s="26"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="31"/>
+      <c r="F33" s="31" t="str">
+        <f>IF(OR(C32="",F32=""),"",IF(OR(D32="",E32=""),"",IF(D32&gt;E32,F32,IF(D32&lt;E32,C32,IF(AND(K32&lt;&gt;"",L32&lt;&gt;""),IF(K32&gt;L32,F32,C32),"")))))</f>
+        <v/>
+      </c>
+      <c r="G33" s="31" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B34" s="8">
         <v>1</v>
       </c>
-      <c r="C34" s="31"/>
+      <c r="C34" s="31" t="str">
+        <f>IF(OR(C31="",F31=""),"",IF(OR(D31="",E31=""),"",IF(D31&gt;E31,C31,IF(D31&lt;E31,F31,IF(AND(K31&lt;&gt;"",L31&lt;&gt;""),IF(K31&gt;L31,C31,F31),"")))))</f>
+        <v/>
+      </c>
       <c r="D34" s="26"/>
       <c r="E34" s="26"/>
-      <c r="F34" s="31"/>
-      <c r="G34" s="31"/>
+      <c r="F34" s="31" t="str">
+        <f>IF(OR(C32="",F32=""),"",IF(OR(D32="",E32=""),"",IF(D32&gt;E32,C32,IF(D32&lt;E32,F32,IF(AND(K32&lt;&gt;"",L32&lt;&gt;""),IF(K32&gt;L32,C32,F32),"")))))</f>
+        <v/>
+      </c>
+      <c r="G34" s="31" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="32" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B36" s="33"/>
       <c r="C36" s="33"/>

--- a/Mundial_2026_fuente_datos.xlsx
+++ b/Mundial_2026_fuente_datos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sriverti\Desktop\INECO\Repositorios\ML_prediccion_mundial2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_4ADEC7E3981F1F4C5539D8A0FD356DEC10FBA236" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156EB6A3-A640-42D7-A45F-F01D11525A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Léeme" sheetId="1" r:id="rId1"/>
@@ -21903,11 +21903,11 @@
         <v>0</v>
       </c>
       <c r="H67" s="8">
-        <f t="shared" ref="H67:H98" si="6">IF(AND(ISNUMBER(F67),ISNUMBER(G67)),1,0)</f>
+        <f t="shared" ref="H67:H74" si="6">IF(AND(ISNUMBER(F67),ISNUMBER(G67)),1,0)</f>
         <v>1</v>
       </c>
       <c r="I67" s="8">
-        <f t="shared" ref="I67:I98" si="7">IF(H67=1,IF(F67&gt;G67,3,IF(F67=G67,1,0)),"")</f>
+        <f t="shared" ref="I67:I74" si="7">IF(H67=1,IF(F67&gt;G67,3,IF(F67=G67,1,0)),"")</f>
         <v>1</v>
       </c>
       <c r="J67" s="8">
@@ -27024,8 +27024,12 @@
         <f>IF(OR(C14="",F14=""),"",IF(OR(D14="",E14=""),"",IF(D14&gt;E14,C14,IF(D14&lt;E14,F14,IF(AND(K14&lt;&gt;"",L14&lt;&gt;""),IF(K14&gt;L14,C14,F14),"")))))</f>
         <v>Portugal</v>
       </c>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
+      <c r="D21" s="26">
+        <v>0</v>
+      </c>
+      <c r="E21" s="26">
+        <v>1</v>
+      </c>
       <c r="F21" s="31" t="str">
         <f>IF(OR(C13="",F13=""),"",IF(OR(D13="",E13=""),"",IF(D13&gt;E13,C13,IF(D13&lt;E13,F13,IF(AND(K13&lt;&gt;"",L13&lt;&gt;""),IF(K13&gt;L13,C13,F13),"")))))</f>
         <v>España</v>
@@ -27045,8 +27049,12 @@
         <f>IF(OR(C12="",F12=""),"",IF(OR(D12="",E12=""),"",IF(D12&gt;E12,C12,IF(D12&lt;E12,F12,IF(AND(K12&lt;&gt;"",L12&lt;&gt;""),IF(K12&gt;L12,C12,F12),"")))))</f>
         <v>Estados Unidos</v>
       </c>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
+      <c r="D22" s="26">
+        <v>1</v>
+      </c>
+      <c r="E22" s="26">
+        <v>4</v>
+      </c>
       <c r="F22" s="31" t="str">
         <f>IF(OR(C11="",F11=""),"",IF(OR(D11="",E11=""),"",IF(D11&gt;E11,C11,IF(D11&lt;E11,F11,IF(AND(K11&lt;&gt;"",L11&lt;&gt;""),IF(K11&gt;L11,C11,F11),"")))))</f>
         <v>Bélgica</v>
@@ -27177,13 +27185,13 @@
       </c>
       <c r="C28" s="31" t="str">
         <f>IF(OR(C21="",F21=""),"",IF(OR(D21="",E21=""),"",IF(D21&gt;E21,C21,IF(D21&lt;E21,F21,IF(AND(K21&lt;&gt;"",L21&lt;&gt;""),IF(K21&gt;L21,C21,F21),"")))))</f>
-        <v/>
+        <v>España</v>
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="26"/>
       <c r="F28" s="31" t="str">
         <f>IF(OR(C22="",F22=""),"",IF(OR(D22="",E22=""),"",IF(D22&gt;E22,C22,IF(D22&lt;E22,F22,IF(AND(K22&lt;&gt;"",L22&lt;&gt;""),IF(K22&gt;L22,C22,F22),"")))))</f>
-        <v/>
+        <v>Bélgica</v>
       </c>
       <c r="G28" s="31" t="s">
         <v>57</v>

--- a/Mundial_2026_fuente_datos.xlsx
+++ b/Mundial_2026_fuente_datos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sriverti\Desktop\INECO\Repositorios\ML_prediccion_mundial2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156EB6A3-A640-42D7-A45F-F01D11525A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF577C1C-CC9A-49A6-B0EB-2960C4E9C145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Léeme" sheetId="1" r:id="rId1"/>
@@ -1764,11 +1764,11 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2001,7 +2001,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="32" t="s">
         <v>63</v>
       </c>
       <c r="C1" s="33"/>
@@ -4430,7 +4430,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="32" t="s">
         <v>108</v>
       </c>
       <c r="B1" s="33"/>
@@ -6161,7 +6161,7 @@
     </row>
     <row r="51" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="32" t="s">
+      <c r="B52" s="34" t="s">
         <v>227</v>
       </c>
       <c r="C52" s="33"/>
@@ -13646,7 +13646,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="32" t="s">
         <v>423</v>
       </c>
       <c r="B1" s="33"/>
@@ -16319,7 +16319,7 @@
     </row>
     <row r="51" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="32" t="s">
+      <c r="B52" s="34" t="s">
         <v>430</v>
       </c>
       <c r="C52" s="33"/>
@@ -17312,7 +17312,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="32" t="s">
         <v>431</v>
       </c>
       <c r="B1" s="33"/>
@@ -18607,7 +18607,7 @@
     </row>
     <row r="51" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="32" t="s">
+      <c r="B52" s="34" t="s">
         <v>439</v>
       </c>
       <c r="C52" s="33"/>
@@ -19592,7 +19592,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="32" t="s">
         <v>440</v>
       </c>
       <c r="B1" s="33"/>
@@ -23110,7 +23110,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="32" t="s">
         <v>450</v>
       </c>
       <c r="B1" s="33"/>
@@ -25421,7 +25421,7 @@
     </row>
     <row r="51" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="32" t="s">
+      <c r="A52" s="34" t="s">
         <v>453</v>
       </c>
       <c r="B52" s="33"/>
@@ -26409,7 +26409,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="33"/>
@@ -26902,7 +26902,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>13</v>
       </c>
@@ -26933,7 +26933,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>13</v>
       </c>
@@ -26963,7 +26963,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>55</v>
       </c>
@@ -26988,7 +26988,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>55</v>
       </c>
@@ -27013,7 +27013,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>55</v>
       </c>
@@ -27038,7 +27038,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>55</v>
       </c>
@@ -27063,7 +27063,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>55</v>
       </c>
@@ -27088,7 +27088,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>55</v>
       </c>
@@ -27113,7 +27113,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>55</v>
       </c>
@@ -27124,8 +27124,12 @@
         <f>IF(OR(C17="",F17=""),"",IF(OR(D17="",E17=""),"",IF(D17&gt;E17,C17,IF(D17&lt;E17,F17,IF(AND(K17&lt;&gt;"",L17&lt;&gt;""),IF(K17&gt;L17,C17,F17),"")))))</f>
         <v>Argentina</v>
       </c>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
+      <c r="D25" s="26">
+        <v>3</v>
+      </c>
+      <c r="E25" s="26">
+        <v>2</v>
+      </c>
       <c r="F25" s="31" t="str">
         <f>IF(OR(C16="",F16=""),"",IF(OR(D16="",E16=""),"",IF(D16&gt;E16,C16,IF(D16&lt;E16,F16,IF(AND(K16&lt;&gt;"",L16&lt;&gt;""),IF(K16&gt;L16,C16,F16),"")))))</f>
         <v>Egipto</v>
@@ -27134,7 +27138,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>55</v>
       </c>
@@ -27145,8 +27149,12 @@
         <f>IF(OR(C15="",F15=""),"",IF(OR(D15="",E15=""),"",IF(D15&gt;E15,C15,IF(D15&lt;E15,F15,IF(AND(K15&lt;&gt;"",L15&lt;&gt;""),IF(K15&gt;L15,C15,F15),"")))))</f>
         <v>Suiza</v>
       </c>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
+      <c r="D26" s="26">
+        <v>0</v>
+      </c>
+      <c r="E26" s="26">
+        <v>0</v>
+      </c>
       <c r="F26" s="31" t="str">
         <f>IF(OR(C18="",F18=""),"",IF(OR(D18="",E18=""),"",IF(D18&gt;E18,C18,IF(D18&lt;E18,F18,IF(AND(K18&lt;&gt;"",L18&lt;&gt;""),IF(K18&gt;L18,C18,F18),"")))))</f>
         <v>Colombia</v>
@@ -27154,8 +27162,14 @@
       <c r="G26" s="31" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K26">
+        <v>4</v>
+      </c>
+      <c r="L26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>58</v>
       </c>
@@ -27176,7 +27190,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>58</v>
       </c>
@@ -27197,7 +27211,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
         <v>58</v>
       </c>
@@ -27218,7 +27232,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>58</v>
       </c>
@@ -27227,19 +27241,19 @@
       </c>
       <c r="C30" s="31" t="str">
         <f>IF(OR(C25="",F25=""),"",IF(OR(D25="",E25=""),"",IF(D25&gt;E25,C25,IF(D25&lt;E25,F25,IF(AND(K25&lt;&gt;"",L25&lt;&gt;""),IF(K25&gt;L25,C25,F25),"")))))</f>
-        <v/>
+        <v>Argentina</v>
       </c>
       <c r="D30" s="26"/>
       <c r="E30" s="26"/>
       <c r="F30" s="31" t="str">
         <f>IF(OR(C26="",F26=""),"",IF(OR(D26="",E26=""),"",IF(D26&gt;E26,C26,IF(D26&lt;E26,F26,IF(AND(K26&lt;&gt;"",L26&lt;&gt;""),IF(K26&gt;L26,C26,F26),"")))))</f>
-        <v/>
+        <v>Suiza</v>
       </c>
       <c r="G30" s="31" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>59</v>
       </c>
@@ -27260,7 +27274,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
         <v>59</v>
       </c>
@@ -27325,7 +27339,7 @@
     </row>
     <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="32" t="s">
+      <c r="A36" s="34" t="s">
         <v>62</v>
       </c>
       <c r="B36" s="33"/>

--- a/Mundial_2026_fuente_datos.xlsx
+++ b/Mundial_2026_fuente_datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sriverti\Desktop\INECO\Repositorios\ML_prediccion_mundial2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF577C1C-CC9A-49A6-B0EB-2960C4E9C145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE2F0859-04B5-4BAE-82B6-A3C8FD34DFA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1764,11 +1764,11 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2001,7 +2001,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="34" t="s">
         <v>63</v>
       </c>
       <c r="C1" s="33"/>
@@ -4430,7 +4430,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="34" t="s">
         <v>108</v>
       </c>
       <c r="B1" s="33"/>
@@ -6161,7 +6161,7 @@
     </row>
     <row r="51" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="34" t="s">
+      <c r="B52" s="32" t="s">
         <v>227</v>
       </c>
       <c r="C52" s="33"/>
@@ -13646,7 +13646,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="34" t="s">
         <v>423</v>
       </c>
       <c r="B1" s="33"/>
@@ -16319,7 +16319,7 @@
     </row>
     <row r="51" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="34" t="s">
+      <c r="B52" s="32" t="s">
         <v>430</v>
       </c>
       <c r="C52" s="33"/>
@@ -17312,7 +17312,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="34" t="s">
         <v>431</v>
       </c>
       <c r="B1" s="33"/>
@@ -18607,7 +18607,7 @@
     </row>
     <row r="51" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="34" t="s">
+      <c r="B52" s="32" t="s">
         <v>439</v>
       </c>
       <c r="C52" s="33"/>
@@ -19592,7 +19592,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="34" t="s">
         <v>440</v>
       </c>
       <c r="B1" s="33"/>
@@ -23110,7 +23110,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="34" t="s">
         <v>450</v>
       </c>
       <c r="B1" s="33"/>
@@ -25421,7 +25421,7 @@
     </row>
     <row r="51" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="34" t="s">
+      <c r="A52" s="32" t="s">
         <v>453</v>
       </c>
       <c r="B52" s="33"/>
@@ -26409,7 +26409,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="33"/>
@@ -27180,8 +27180,12 @@
         <f>IF(OR(C19="",F19=""),"",IF(OR(D19="",E19=""),"",IF(D19&gt;E19,C19,IF(D19&lt;E19,F19,IF(AND(K19&lt;&gt;"",L19&lt;&gt;""),IF(K19&gt;L19,C19,F19),"")))))</f>
         <v>Francia</v>
       </c>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
+      <c r="D27" s="26">
+        <v>2</v>
+      </c>
+      <c r="E27" s="26">
+        <v>0</v>
+      </c>
       <c r="F27" s="31" t="str">
         <f>IF(OR(C20="",F20=""),"",IF(OR(D20="",E20=""),"",IF(D20&gt;E20,C20,IF(D20&lt;E20,F20,IF(AND(K20&lt;&gt;"",L20&lt;&gt;""),IF(K20&gt;L20,C20,F20),"")))))</f>
         <v>Marruecos</v>
@@ -27262,7 +27266,7 @@
       </c>
       <c r="C31" s="31" t="str">
         <f>IF(OR(C27="",F27=""),"",IF(OR(D27="",E27=""),"",IF(D27&gt;E27,C27,IF(D27&lt;E27,F27,IF(AND(K27&lt;&gt;"",L27&lt;&gt;""),IF(K27&gt;L27,C27,F27),"")))))</f>
-        <v/>
+        <v>Francia</v>
       </c>
       <c r="D31" s="26"/>
       <c r="E31" s="26"/>
@@ -27339,7 +27343,7 @@
     </row>
     <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="34" t="s">
+      <c r="A36" s="32" t="s">
         <v>62</v>
       </c>
       <c r="B36" s="33"/>

--- a/Mundial_2026_fuente_datos.xlsx
+++ b/Mundial_2026_fuente_datos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sriverti\Desktop\INECO\Repositorios\ML_prediccion_mundial2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\santi\OneDrive\Escritorio\Repositorios\ML_prediccion_mundial2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE2F0859-04B5-4BAE-82B6-A3C8FD34DFA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD80A1D-3124-48CA-B4B9-3EA7AA46A893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Léeme" sheetId="1" r:id="rId1"/>
@@ -27205,8 +27205,12 @@
         <f>IF(OR(C21="",F21=""),"",IF(OR(D21="",E21=""),"",IF(D21&gt;E21,C21,IF(D21&lt;E21,F21,IF(AND(K21&lt;&gt;"",L21&lt;&gt;""),IF(K21&gt;L21,C21,F21),"")))))</f>
         <v>España</v>
       </c>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
+      <c r="D28" s="26">
+        <v>2</v>
+      </c>
+      <c r="E28" s="26">
+        <v>1</v>
+      </c>
       <c r="F28" s="31" t="str">
         <f>IF(OR(C22="",F22=""),"",IF(OR(D22="",E22=""),"",IF(D22&gt;E22,C22,IF(D22&lt;E22,F22,IF(AND(K22&lt;&gt;"",L22&lt;&gt;""),IF(K22&gt;L22,C22,F22),"")))))</f>
         <v>Bélgica</v>
@@ -27226,8 +27230,12 @@
         <f>IF(OR(C23="",F23=""),"",IF(OR(D23="",E23=""),"",IF(D23&gt;E23,C23,IF(D23&lt;E23,F23,IF(AND(K23&lt;&gt;"",L23&lt;&gt;""),IF(K23&gt;L23,C23,F23),"")))))</f>
         <v>Noruega</v>
       </c>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
+      <c r="D29" s="26">
+        <v>1</v>
+      </c>
+      <c r="E29" s="26">
+        <v>2</v>
+      </c>
       <c r="F29" s="31" t="str">
         <f>IF(OR(C24="",F24=""),"",IF(OR(D24="",E24=""),"",IF(D24&gt;E24,C24,IF(D24&lt;E24,F24,IF(AND(K24&lt;&gt;"",L24&lt;&gt;""),IF(K24&gt;L24,C24,F24),"")))))</f>
         <v>Inglaterra</v>
@@ -27272,7 +27280,7 @@
       <c r="E31" s="26"/>
       <c r="F31" s="31" t="str">
         <f>IF(OR(C28="",F28=""),"",IF(OR(D28="",E28=""),"",IF(D28&gt;E28,C28,IF(D28&lt;E28,F28,IF(AND(K28&lt;&gt;"",L28&lt;&gt;""),IF(K28&gt;L28,C28,F28),"")))))</f>
-        <v/>
+        <v>España</v>
       </c>
       <c r="G31" s="31" t="s">
         <v>57</v>
@@ -27287,7 +27295,7 @@
       </c>
       <c r="C32" s="31" t="str">
         <f>IF(OR(C29="",F29=""),"",IF(OR(D29="",E29=""),"",IF(D29&gt;E29,C29,IF(D29&lt;E29,F29,IF(AND(K29&lt;&gt;"",L29&lt;&gt;""),IF(K29&gt;L29,C29,F29),"")))))</f>
-        <v/>
+        <v>Inglaterra</v>
       </c>
       <c r="D32" s="26"/>
       <c r="E32" s="26"/>

--- a/Mundial_2026_fuente_datos.xlsx
+++ b/Mundial_2026_fuente_datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\santi\OneDrive\Escritorio\Repositorios\ML_prediccion_mundial2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD80A1D-3124-48CA-B4B9-3EA7AA46A893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57CF7C2B-5786-4C46-8BC5-A8A8D173DABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27255,8 +27255,12 @@
         <f>IF(OR(C25="",F25=""),"",IF(OR(D25="",E25=""),"",IF(D25&gt;E25,C25,IF(D25&lt;E25,F25,IF(AND(K25&lt;&gt;"",L25&lt;&gt;""),IF(K25&gt;L25,C25,F25),"")))))</f>
         <v>Argentina</v>
       </c>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
+      <c r="D30" s="26">
+        <v>3</v>
+      </c>
+      <c r="E30" s="26">
+        <v>1</v>
+      </c>
       <c r="F30" s="31" t="str">
         <f>IF(OR(C26="",F26=""),"",IF(OR(D26="",E26=""),"",IF(D26&gt;E26,C26,IF(D26&lt;E26,F26,IF(AND(K26&lt;&gt;"",L26&lt;&gt;""),IF(K26&gt;L26,C26,F26),"")))))</f>
         <v>Suiza</v>
@@ -27301,7 +27305,7 @@
       <c r="E32" s="26"/>
       <c r="F32" s="31" t="str">
         <f>IF(OR(C30="",F30=""),"",IF(OR(D30="",E30=""),"",IF(D30&gt;E30,C30,IF(D30&lt;E30,F30,IF(AND(K30&lt;&gt;"",L30&lt;&gt;""),IF(K30&gt;L30,C30,F30),"")))))</f>
-        <v/>
+        <v>Argentina</v>
       </c>
       <c r="G32" s="31" t="s">
         <v>57</v>

--- a/Mundial_2026_fuente_datos.xlsx
+++ b/Mundial_2026_fuente_datos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\santi\OneDrive\Escritorio\Repositorios\ML_prediccion_mundial2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\santi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57CF7C2B-5786-4C46-8BC5-A8A8D173DABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF8BA110-62E6-400A-81A2-D0C14508D16C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27280,8 +27280,12 @@
         <f>IF(OR(C27="",F27=""),"",IF(OR(D27="",E27=""),"",IF(D27&gt;E27,C27,IF(D27&lt;E27,F27,IF(AND(K27&lt;&gt;"",L27&lt;&gt;""),IF(K27&gt;L27,C27,F27),"")))))</f>
         <v>Francia</v>
       </c>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
+      <c r="D31" s="26">
+        <v>0</v>
+      </c>
+      <c r="E31" s="26">
+        <v>2</v>
+      </c>
       <c r="F31" s="31" t="str">
         <f>IF(OR(C28="",F28=""),"",IF(OR(D28="",E28=""),"",IF(D28&gt;E28,C28,IF(D28&lt;E28,F28,IF(AND(K28&lt;&gt;"",L28&lt;&gt;""),IF(K28&gt;L28,C28,F28),"")))))</f>
         <v>España</v>
@@ -27320,7 +27324,7 @@
       </c>
       <c r="C33" s="31" t="str">
         <f>IF(OR(C31="",F31=""),"",IF(OR(D31="",E31=""),"",IF(D31&gt;E31,F31,IF(D31&lt;E31,C31,IF(AND(K31&lt;&gt;"",L31&lt;&gt;""),IF(K31&gt;L31,F31,C31),"")))))</f>
-        <v/>
+        <v>Francia</v>
       </c>
       <c r="D33" s="26"/>
       <c r="E33" s="26"/>
@@ -27341,7 +27345,7 @@
       </c>
       <c r="C34" s="31" t="str">
         <f>IF(OR(C31="",F31=""),"",IF(OR(D31="",E31=""),"",IF(D31&gt;E31,C31,IF(D31&lt;E31,F31,IF(AND(K31&lt;&gt;"",L31&lt;&gt;""),IF(K31&gt;L31,C31,F31),"")))))</f>
-        <v/>
+        <v>España</v>
       </c>
       <c r="D34" s="26"/>
       <c r="E34" s="26"/>

--- a/Mundial_2026_fuente_datos.xlsx
+++ b/Mundial_2026_fuente_datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\santi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF8BA110-62E6-400A-81A2-D0C14508D16C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD2CCB4-667D-4105-BCD3-AEDDE156B049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27305,8 +27305,12 @@
         <f>IF(OR(C29="",F29=""),"",IF(OR(D29="",E29=""),"",IF(D29&gt;E29,C29,IF(D29&lt;E29,F29,IF(AND(K29&lt;&gt;"",L29&lt;&gt;""),IF(K29&gt;L29,C29,F29),"")))))</f>
         <v>Inglaterra</v>
       </c>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
+      <c r="D32" s="26">
+        <v>1</v>
+      </c>
+      <c r="E32" s="26">
+        <v>2</v>
+      </c>
       <c r="F32" s="31" t="str">
         <f>IF(OR(C30="",F30=""),"",IF(OR(D30="",E30=""),"",IF(D30&gt;E30,C30,IF(D30&lt;E30,F30,IF(AND(K30&lt;&gt;"",L30&lt;&gt;""),IF(K30&gt;L30,C30,F30),"")))))</f>
         <v>Argentina</v>
@@ -27330,7 +27334,7 @@
       <c r="E33" s="26"/>
       <c r="F33" s="31" t="str">
         <f>IF(OR(C32="",F32=""),"",IF(OR(D32="",E32=""),"",IF(D32&gt;E32,F32,IF(D32&lt;E32,C32,IF(AND(K32&lt;&gt;"",L32&lt;&gt;""),IF(K32&gt;L32,F32,C32),"")))))</f>
-        <v/>
+        <v>Inglaterra</v>
       </c>
       <c r="G33" s="31" t="s">
         <v>57</v>
@@ -27351,7 +27355,7 @@
       <c r="E34" s="26"/>
       <c r="F34" s="31" t="str">
         <f>IF(OR(C32="",F32=""),"",IF(OR(D32="",E32=""),"",IF(D32&gt;E32,C32,IF(D32&lt;E32,F32,IF(AND(K32&lt;&gt;"",L32&lt;&gt;""),IF(K32&gt;L32,C32,F32),"")))))</f>
-        <v/>
+        <v>Argentina</v>
       </c>
       <c r="G34" s="31" t="s">
         <v>57</v>

--- a/Mundial_2026_fuente_datos.xlsx
+++ b/Mundial_2026_fuente_datos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\santi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\santi\Downloads\Repositorios\ML_prediccion_mundial2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD2CCB4-667D-4105-BCD3-AEDDE156B049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{995A7F04-2BBE-4A5E-A53F-A0009D303442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27330,8 +27330,12 @@
         <f>IF(OR(C31="",F31=""),"",IF(OR(D31="",E31=""),"",IF(D31&gt;E31,F31,IF(D31&lt;E31,C31,IF(AND(K31&lt;&gt;"",L31&lt;&gt;""),IF(K31&gt;L31,F31,C31),"")))))</f>
         <v>Francia</v>
       </c>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
+      <c r="D33" s="26">
+        <v>4</v>
+      </c>
+      <c r="E33" s="26">
+        <v>6</v>
+      </c>
       <c r="F33" s="31" t="str">
         <f>IF(OR(C32="",F32=""),"",IF(OR(D32="",E32=""),"",IF(D32&gt;E32,F32,IF(D32&lt;E32,C32,IF(AND(K32&lt;&gt;"",L32&lt;&gt;""),IF(K32&gt;L32,F32,C32),"")))))</f>
         <v>Inglaterra</v>
@@ -27351,8 +27355,12 @@
         <f>IF(OR(C31="",F31=""),"",IF(OR(D31="",E31=""),"",IF(D31&gt;E31,C31,IF(D31&lt;E31,F31,IF(AND(K31&lt;&gt;"",L31&lt;&gt;""),IF(K31&gt;L31,C31,F31),"")))))</f>
         <v>España</v>
       </c>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
+      <c r="D34" s="26">
+        <v>1</v>
+      </c>
+      <c r="E34" s="26">
+        <v>0</v>
+      </c>
       <c r="F34" s="31" t="str">
         <f>IF(OR(C32="",F32=""),"",IF(OR(D32="",E32=""),"",IF(D32&gt;E32,C32,IF(D32&lt;E32,F32,IF(AND(K32&lt;&gt;"",L32&lt;&gt;""),IF(K32&gt;L32,C32,F32),"")))))</f>
         <v>Argentina</v>
